--- a/resources/topic/银行从业初级个人贷款_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级个人贷款_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rd8320e99030f4e35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R8524df1910e54a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R2d15f2566ba74a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R1388fef3d0b94d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Re38ad42ad626401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rd450ad67dab34db3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+  </x:numFmts>
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -39,6 +42,11 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -53,7 +61,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -181,11 +189,39 @@
         <x:color rgb="FFB4C6E7"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB4C6E7"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="double">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB4C6E7"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="double">
+        <x:color rgb="FF1F4E78"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB4C6E7"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -266,6 +302,42 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -487,7 +559,7 @@
     <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="60" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -616,7 +688,7 @@
       <x:c r="R2" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S2" s="9" t="n">
+      <x:c r="S2" s="9" t="str">
         <x:v>5151894</x:v>
       </x:c>
       <x:c r="T2" s="10" t="str">
@@ -677,7 +749,7 @@
       <x:c r="R3" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S3" s="9" t="n">
+      <x:c r="S3" s="9" t="str">
         <x:v>5155402</x:v>
       </x:c>
       <x:c r="T3" s="10" t="str">
@@ -738,7 +810,7 @@
       <x:c r="R4" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S4" s="9" t="n">
+      <x:c r="S4" s="9" t="str">
         <x:v>5155408</x:v>
       </x:c>
       <x:c r="T4" s="10" t="str">
@@ -799,7 +871,7 @@
       <x:c r="R5" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S5" s="9" t="n">
+      <x:c r="S5" s="9" t="str">
         <x:v>5155420</x:v>
       </x:c>
       <x:c r="T5" s="10" t="str">
@@ -860,7 +932,7 @@
       <x:c r="R6" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S6" s="9" t="n">
+      <x:c r="S6" s="9" t="str">
         <x:v>5155421</x:v>
       </x:c>
       <x:c r="T6" s="10" t="str">
@@ -921,7 +993,7 @@
       <x:c r="R7" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S7" s="9" t="n">
+      <x:c r="S7" s="9" t="str">
         <x:v>5155427</x:v>
       </x:c>
       <x:c r="T7" s="10" t="str">
@@ -982,7 +1054,7 @@
       <x:c r="R8" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S8" s="9" t="n">
+      <x:c r="S8" s="9" t="str">
         <x:v>5155432</x:v>
       </x:c>
       <x:c r="T8" s="10" t="str">
@@ -1043,7 +1115,7 @@
       <x:c r="R9" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S9" s="9" t="n">
+      <x:c r="S9" s="9" t="str">
         <x:v>5155435</x:v>
       </x:c>
       <x:c r="T9" s="10" t="str">
@@ -1104,7 +1176,7 @@
       <x:c r="R10" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S10" s="9" t="n">
+      <x:c r="S10" s="9" t="str">
         <x:v>5155439</x:v>
       </x:c>
       <x:c r="T10" s="10" t="str">
@@ -1165,7 +1237,7 @@
       <x:c r="R11" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S11" s="9" t="n">
+      <x:c r="S11" s="9" t="str">
         <x:v>5155445</x:v>
       </x:c>
       <x:c r="T11" s="10" t="str">
@@ -1226,7 +1298,7 @@
       <x:c r="R12" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S12" s="9" t="n">
+      <x:c r="S12" s="9" t="str">
         <x:v>5155447</x:v>
       </x:c>
       <x:c r="T12" s="10" t="str">
@@ -1287,7 +1359,7 @@
       <x:c r="R13" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S13" s="9" t="n">
+      <x:c r="S13" s="9" t="str">
         <x:v>5155448</x:v>
       </x:c>
       <x:c r="T13" s="10" t="str">
@@ -1348,7 +1420,7 @@
       <x:c r="R14" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S14" s="9" t="n">
+      <x:c r="S14" s="9" t="str">
         <x:v>5155450</x:v>
       </x:c>
       <x:c r="T14" s="10" t="str">
@@ -1409,7 +1481,7 @@
       <x:c r="R15" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S15" s="9" t="n">
+      <x:c r="S15" s="9" t="str">
         <x:v>5155454</x:v>
       </x:c>
       <x:c r="T15" s="10" t="str">
@@ -1470,7 +1542,7 @@
       <x:c r="R16" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S16" s="9" t="n">
+      <x:c r="S16" s="9" t="str">
         <x:v>5155456</x:v>
       </x:c>
       <x:c r="T16" s="10" t="str">
@@ -1534,7 +1606,7 @@
       <x:c r="R17" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S17" s="9" t="n">
+      <x:c r="S17" s="9" t="str">
         <x:v>5155457</x:v>
       </x:c>
       <x:c r="T17" s="10" t="str">
@@ -1595,7 +1667,7 @@
       <x:c r="R18" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S18" s="9" t="n">
+      <x:c r="S18" s="9" t="str">
         <x:v>5155459</x:v>
       </x:c>
       <x:c r="T18" s="10" t="str">
@@ -1656,7 +1728,7 @@
       <x:c r="R19" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S19" s="9" t="n">
+      <x:c r="S19" s="9" t="str">
         <x:v>5155460</x:v>
       </x:c>
       <x:c r="T19" s="10" t="str">
@@ -1717,7 +1789,7 @@
       <x:c r="R20" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S20" s="9" t="n">
+      <x:c r="S20" s="9" t="str">
         <x:v>5155462</x:v>
       </x:c>
       <x:c r="T20" s="10" t="str">
@@ -1778,7 +1850,7 @@
       <x:c r="R21" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S21" s="9" t="n">
+      <x:c r="S21" s="9" t="str">
         <x:v>5155684</x:v>
       </x:c>
       <x:c r="T21" s="10" t="str">
@@ -1839,7 +1911,7 @@
       <x:c r="R22" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S22" s="9" t="n">
+      <x:c r="S22" s="9" t="str">
         <x:v>5377819</x:v>
       </x:c>
       <x:c r="T22" s="10" t="str">
@@ -1900,7 +1972,7 @@
       <x:c r="R23" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S23" s="9" t="n">
+      <x:c r="S23" s="9" t="str">
         <x:v>5155403</x:v>
       </x:c>
       <x:c r="T23" s="10" t="str">
@@ -1961,7 +2033,7 @@
       <x:c r="R24" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S24" s="9" t="n">
+      <x:c r="S24" s="9" t="str">
         <x:v>5155407</x:v>
       </x:c>
       <x:c r="T24" s="10" t="str">
@@ -2025,7 +2097,7 @@
       <x:c r="R25" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S25" s="9" t="n">
+      <x:c r="S25" s="9" t="str">
         <x:v>5155414</x:v>
       </x:c>
       <x:c r="T25" s="10" t="str">
@@ -2086,7 +2158,7 @@
       <x:c r="R26" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S26" s="9" t="n">
+      <x:c r="S26" s="9" t="str">
         <x:v>5155417</x:v>
       </x:c>
       <x:c r="T26" s="10" t="str">
@@ -2150,7 +2222,7 @@
       <x:c r="R27" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S27" s="9" t="n">
+      <x:c r="S27" s="9" t="str">
         <x:v>5155418</x:v>
       </x:c>
       <x:c r="T27" s="10" t="str">
@@ -2211,7 +2283,7 @@
       <x:c r="R28" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S28" s="9" t="n">
+      <x:c r="S28" s="9" t="str">
         <x:v>5155436</x:v>
       </x:c>
       <x:c r="T28" s="10" t="str">
@@ -2272,7 +2344,7 @@
       <x:c r="R29" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S29" s="9" t="n">
+      <x:c r="S29" s="9" t="str">
         <x:v>5155444</x:v>
       </x:c>
       <x:c r="T29" s="10" t="str">
@@ -2333,7 +2405,7 @@
       <x:c r="R30" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S30" s="9" t="n">
+      <x:c r="S30" s="9" t="str">
         <x:v>5376249</x:v>
       </x:c>
       <x:c r="T30" s="10" t="str">
@@ -2394,7 +2466,7 @@
       <x:c r="R31" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S31" s="9" t="n">
+      <x:c r="S31" s="9" t="str">
         <x:v>5151132</x:v>
       </x:c>
       <x:c r="T31" s="10" t="str">
@@ -2455,7 +2527,7 @@
       <x:c r="R32" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S32" s="9" t="n">
+      <x:c r="S32" s="9" t="str">
         <x:v>5151616</x:v>
       </x:c>
       <x:c r="T32" s="10" t="str">
@@ -2516,7 +2588,7 @@
       <x:c r="R33" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S33" s="9" t="n">
+      <x:c r="S33" s="9" t="str">
         <x:v>5151923</x:v>
       </x:c>
       <x:c r="T33" s="10" t="str">
@@ -2577,7 +2649,7 @@
       <x:c r="R34" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S34" s="9" t="n">
+      <x:c r="S34" s="9" t="str">
         <x:v>5151927</x:v>
       </x:c>
       <x:c r="T34" s="10" t="str">
@@ -2638,7 +2710,7 @@
       <x:c r="R35" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S35" s="9" t="n">
+      <x:c r="S35" s="9" t="str">
         <x:v>5155399</x:v>
       </x:c>
       <x:c r="T35" s="10" t="str">
@@ -2699,7 +2771,7 @@
       <x:c r="R36" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S36" s="9" t="n">
+      <x:c r="S36" s="9" t="str">
         <x:v>5155401</x:v>
       </x:c>
       <x:c r="T36" s="10" t="str">
@@ -2760,7 +2832,7 @@
       <x:c r="R37" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S37" s="9" t="n">
+      <x:c r="S37" s="9" t="str">
         <x:v>5155404</x:v>
       </x:c>
       <x:c r="T37" s="10" t="str">
@@ -2821,7 +2893,7 @@
       <x:c r="R38" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S38" s="9" t="n">
+      <x:c r="S38" s="9" t="str">
         <x:v>5155405</x:v>
       </x:c>
       <x:c r="T38" s="10" t="str">
@@ -2882,7 +2954,7 @@
       <x:c r="R39" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S39" s="9" t="n">
+      <x:c r="S39" s="9" t="str">
         <x:v>5155406</x:v>
       </x:c>
       <x:c r="T39" s="10" t="str">
@@ -2946,7 +3018,7 @@
       <x:c r="R40" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S40" s="9" t="n">
+      <x:c r="S40" s="9" t="str">
         <x:v>5155409</x:v>
       </x:c>
       <x:c r="T40" s="10" t="str">
@@ -3007,7 +3079,7 @@
       <x:c r="R41" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S41" s="9" t="n">
+      <x:c r="S41" s="9" t="str">
         <x:v>5155410</x:v>
       </x:c>
       <x:c r="T41" s="10" t="str">
@@ -3068,7 +3140,7 @@
       <x:c r="R42" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S42" s="9" t="n">
+      <x:c r="S42" s="9" t="str">
         <x:v>5155412</x:v>
       </x:c>
       <x:c r="T42" s="10" t="str">
@@ -3129,7 +3201,7 @@
       <x:c r="R43" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S43" s="9" t="n">
+      <x:c r="S43" s="9" t="str">
         <x:v>5155413</x:v>
       </x:c>
       <x:c r="T43" s="10" t="str">
@@ -3190,7 +3262,7 @@
       <x:c r="R44" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S44" s="9" t="n">
+      <x:c r="S44" s="9" t="str">
         <x:v>5155415</x:v>
       </x:c>
       <x:c r="T44" s="10" t="str">
@@ -3254,7 +3326,7 @@
       <x:c r="R45" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S45" s="9" t="n">
+      <x:c r="S45" s="9" t="str">
         <x:v>5155424</x:v>
       </x:c>
       <x:c r="T45" s="10" t="str">
@@ -3318,7 +3390,7 @@
       <x:c r="R46" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S46" s="9" t="n">
+      <x:c r="S46" s="9" t="str">
         <x:v>5155426</x:v>
       </x:c>
       <x:c r="T46" s="10" t="str">
@@ -3379,7 +3451,7 @@
       <x:c r="R47" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S47" s="9" t="n">
+      <x:c r="S47" s="9" t="str">
         <x:v>5155428</x:v>
       </x:c>
       <x:c r="T47" s="10" t="str">
@@ -3440,7 +3512,7 @@
       <x:c r="R48" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S48" s="9" t="n">
+      <x:c r="S48" s="9" t="str">
         <x:v>5155430</x:v>
       </x:c>
       <x:c r="T48" s="10" t="str">
@@ -3501,7 +3573,7 @@
       <x:c r="R49" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S49" s="9" t="n">
+      <x:c r="S49" s="9" t="str">
         <x:v>5155431</x:v>
       </x:c>
       <x:c r="T49" s="10" t="str">
@@ -3565,7 +3637,7 @@
       <x:c r="R50" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S50" s="9" t="n">
+      <x:c r="S50" s="9" t="str">
         <x:v>5155438</x:v>
       </x:c>
       <x:c r="T50" s="10" t="str">
@@ -3628,7 +3700,7 @@
       <x:c r="R51" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S51" s="9" t="n">
+      <x:c r="S51" s="9" t="str">
         <x:v>5155441</x:v>
       </x:c>
       <x:c r="T51" s="10" t="str">
@@ -3690,7 +3762,7 @@
       <x:c r="R52" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S52" s="9" t="n">
+      <x:c r="S52" s="9" t="str">
         <x:v>5155443</x:v>
       </x:c>
       <x:c r="T52" s="10" t="str">
@@ -3751,7 +3823,7 @@
       <x:c r="R53" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S53" s="9" t="n">
+      <x:c r="S53" s="9" t="str">
         <x:v>5155446</x:v>
       </x:c>
       <x:c r="T53" s="10" t="str">
@@ -3812,7 +3884,7 @@
       <x:c r="R54" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S54" s="9" t="n">
+      <x:c r="S54" s="9" t="str">
         <x:v>5155453</x:v>
       </x:c>
       <x:c r="T54" s="10" t="str">
@@ -3873,7 +3945,7 @@
       <x:c r="R55" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S55" s="9" t="n">
+      <x:c r="S55" s="9" t="str">
         <x:v>5155458</x:v>
       </x:c>
       <x:c r="T55" s="10" t="str">
@@ -3934,7 +4006,7 @@
       <x:c r="R56" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S56" s="9" t="n">
+      <x:c r="S56" s="9" t="str">
         <x:v>5155461</x:v>
       </x:c>
       <x:c r="T56" s="10" t="str">
@@ -3998,7 +4070,7 @@
       <x:c r="R57" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S57" s="9" t="n">
+      <x:c r="S57" s="9" t="str">
         <x:v>5155465</x:v>
       </x:c>
       <x:c r="T57" s="10" t="str">
@@ -4059,7 +4131,7 @@
       <x:c r="R58" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S58" s="9" t="n">
+      <x:c r="S58" s="9" t="str">
         <x:v>5155707</x:v>
       </x:c>
       <x:c r="T58" s="10" t="str">
@@ -4120,7 +4192,7 @@
       <x:c r="R59" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S59" s="9" t="n">
+      <x:c r="S59" s="9" t="str">
         <x:v>5155826</x:v>
       </x:c>
       <x:c r="T59" s="10" t="str">
@@ -4184,7 +4256,7 @@
       <x:c r="R60" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S60" s="9" t="n">
+      <x:c r="S60" s="9" t="str">
         <x:v>5151942</x:v>
       </x:c>
       <x:c r="T60" s="10" t="str">
@@ -4248,7 +4320,7 @@
       <x:c r="R61" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S61" s="9" t="n">
+      <x:c r="S61" s="9" t="str">
         <x:v>5155468</x:v>
       </x:c>
       <x:c r="T61" s="10" t="str">
@@ -4310,7 +4382,7 @@
       <x:c r="R62" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S62" s="9" t="n">
+      <x:c r="S62" s="9" t="str">
         <x:v>5155470</x:v>
       </x:c>
       <x:c r="T62" s="10" t="str">
@@ -4374,7 +4446,7 @@
       <x:c r="R63" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S63" s="9" t="n">
+      <x:c r="S63" s="9" t="str">
         <x:v>5155474</x:v>
       </x:c>
       <x:c r="T63" s="10" t="str">
@@ -4438,7 +4510,7 @@
       <x:c r="R64" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S64" s="9" t="n">
+      <x:c r="S64" s="9" t="str">
         <x:v>5155479</x:v>
       </x:c>
       <x:c r="T64" s="10" t="str">
@@ -4502,7 +4574,7 @@
       <x:c r="R65" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S65" s="9" t="n">
+      <x:c r="S65" s="9" t="str">
         <x:v>5155480</x:v>
       </x:c>
       <x:c r="T65" s="10" t="str">
@@ -4566,7 +4638,7 @@
       <x:c r="R66" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S66" s="9" t="n">
+      <x:c r="S66" s="9" t="str">
         <x:v>5155481</x:v>
       </x:c>
       <x:c r="T66" s="10" t="str">
@@ -4632,7 +4704,7 @@
       <x:c r="R67" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S67" s="9" t="n">
+      <x:c r="S67" s="9" t="str">
         <x:v>5155484</x:v>
       </x:c>
       <x:c r="T67" s="10" t="str">
@@ -4696,7 +4768,7 @@
       <x:c r="R68" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S68" s="9" t="n">
+      <x:c r="S68" s="9" t="str">
         <x:v>5155486</x:v>
       </x:c>
       <x:c r="T68" s="10" t="str">
@@ -4763,7 +4835,7 @@
       <x:c r="R69" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S69" s="9" t="n">
+      <x:c r="S69" s="9" t="str">
         <x:v>5155488</x:v>
       </x:c>
       <x:c r="T69" s="10" t="str">
@@ -4829,7 +4901,7 @@
       <x:c r="R70" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S70" s="9" t="n">
+      <x:c r="S70" s="9" t="str">
         <x:v>5155490</x:v>
       </x:c>
       <x:c r="T70" s="10" t="str">
@@ -4893,7 +4965,7 @@
       <x:c r="R71" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S71" s="9" t="n">
+      <x:c r="S71" s="9" t="str">
         <x:v>5155491</x:v>
       </x:c>
       <x:c r="T71" s="10" t="str">
@@ -4957,7 +5029,7 @@
       <x:c r="R72" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S72" s="9" t="n">
+      <x:c r="S72" s="9" t="str">
         <x:v>5155493</x:v>
       </x:c>
       <x:c r="T72" s="10" t="str">
@@ -5021,7 +5093,7 @@
       <x:c r="R73" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S73" s="9" t="n">
+      <x:c r="S73" s="9" t="str">
         <x:v>5155497</x:v>
       </x:c>
       <x:c r="T73" s="10" t="str">
@@ -5085,7 +5157,7 @@
       <x:c r="R74" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S74" s="9" t="n">
+      <x:c r="S74" s="9" t="str">
         <x:v>5376302</x:v>
       </x:c>
       <x:c r="T74" s="10" t="str">
@@ -5150,7 +5222,7 @@
       <x:c r="R75" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S75" s="9" t="n">
+      <x:c r="S75" s="9" t="str">
         <x:v>5376310</x:v>
       </x:c>
       <x:c r="T75" s="10" t="str">
@@ -5214,7 +5286,7 @@
       <x:c r="R76" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S76" s="9" t="n">
+      <x:c r="S76" s="9" t="str">
         <x:v>5155473</x:v>
       </x:c>
       <x:c r="T76" s="10" t="str">
@@ -5278,7 +5350,7 @@
       <x:c r="R77" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S77" s="9" t="n">
+      <x:c r="S77" s="9" t="str">
         <x:v>5151591</x:v>
       </x:c>
       <x:c r="T77" s="10" t="str">
@@ -5343,7 +5415,7 @@
       <x:c r="R78" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S78" s="9" t="n">
+      <x:c r="S78" s="9" t="str">
         <x:v>5151812</x:v>
       </x:c>
       <x:c r="T78" s="10" t="str">
@@ -5412,7 +5484,7 @@
       <x:c r="R79" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S79" s="9" t="n">
+      <x:c r="S79" s="9" t="str">
         <x:v>5152048</x:v>
       </x:c>
       <x:c r="T79" s="10" t="str">
@@ -5478,7 +5550,7 @@
       <x:c r="R80" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S80" s="9" t="n">
+      <x:c r="S80" s="9" t="str">
         <x:v>5155466</x:v>
       </x:c>
       <x:c r="T80" s="10" t="str">
@@ -5542,7 +5614,7 @@
       <x:c r="R81" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S81" s="9" t="n">
+      <x:c r="S81" s="9" t="str">
         <x:v>5155467</x:v>
       </x:c>
       <x:c r="T81" s="10" t="str">
@@ -5606,7 +5678,7 @@
       <x:c r="R82" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S82" s="9" t="n">
+      <x:c r="S82" s="9" t="str">
         <x:v>5155469</x:v>
       </x:c>
       <x:c r="T82" s="10" t="str">
@@ -5673,7 +5745,7 @@
       <x:c r="R83" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S83" s="9" t="n">
+      <x:c r="S83" s="9" t="str">
         <x:v>5155472</x:v>
       </x:c>
       <x:c r="T83" s="10" t="str">
@@ -5739,7 +5811,7 @@
       <x:c r="R84" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S84" s="9" t="n">
+      <x:c r="S84" s="9" t="str">
         <x:v>5155476</x:v>
       </x:c>
       <x:c r="T84" s="10" t="str">
@@ -5805,7 +5877,7 @@
       <x:c r="R85" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S85" s="9" t="n">
+      <x:c r="S85" s="9" t="str">
         <x:v>5155477</x:v>
       </x:c>
       <x:c r="T85" s="10" t="str">
@@ -5869,7 +5941,7 @@
       <x:c r="R86" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S86" s="9" t="n">
+      <x:c r="S86" s="9" t="str">
         <x:v>5155478</x:v>
       </x:c>
       <x:c r="T86" s="10" t="str">
@@ -5934,7 +6006,7 @@
       <x:c r="R87" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S87" s="9" t="n">
+      <x:c r="S87" s="9" t="str">
         <x:v>5155483</x:v>
       </x:c>
       <x:c r="T87" s="10" t="str">
@@ -6001,7 +6073,7 @@
       <x:c r="R88" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S88" s="9" t="n">
+      <x:c r="S88" s="9" t="str">
         <x:v>5155485</x:v>
       </x:c>
       <x:c r="T88" s="10" t="str">
@@ -6067,7 +6139,7 @@
       <x:c r="R89" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S89" s="9" t="n">
+      <x:c r="S89" s="9" t="str">
         <x:v>5155487</x:v>
       </x:c>
       <x:c r="T89" s="10" t="str">
@@ -6131,7 +6203,7 @@
       <x:c r="R90" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S90" s="9" t="n">
+      <x:c r="S90" s="9" t="str">
         <x:v>5155489</x:v>
       </x:c>
       <x:c r="T90" s="10" t="str">
@@ -6196,7 +6268,7 @@
       <x:c r="R91" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S91" s="9" t="n">
+      <x:c r="S91" s="9" t="str">
         <x:v>5155492</x:v>
       </x:c>
       <x:c r="T91" s="10" t="str">
@@ -6260,7 +6332,7 @@
       <x:c r="R92" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S92" s="9" t="n">
+      <x:c r="S92" s="9" t="str">
         <x:v>5155496</x:v>
       </x:c>
       <x:c r="T92" s="10" t="str">
@@ -6315,7 +6387,7 @@
       <x:c r="R93" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S93" s="9" t="n">
+      <x:c r="S93" s="9" t="str">
         <x:v>5155499</x:v>
       </x:c>
       <x:c r="T93" s="10" t="str">
@@ -6370,7 +6442,7 @@
       <x:c r="R94" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S94" s="9" t="n">
+      <x:c r="S94" s="9" t="str">
         <x:v>5155500</x:v>
       </x:c>
       <x:c r="T94" s="10" t="str">
@@ -6425,7 +6497,7 @@
       <x:c r="R95" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S95" s="9" t="n">
+      <x:c r="S95" s="9" t="str">
         <x:v>5155506</x:v>
       </x:c>
       <x:c r="T95" s="10" t="str">
@@ -6480,7 +6552,7 @@
       <x:c r="R96" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S96" s="9" t="n">
+      <x:c r="S96" s="9" t="str">
         <x:v>5155509</x:v>
       </x:c>
       <x:c r="T96" s="10" t="str">
@@ -6535,7 +6607,7 @@
       <x:c r="R97" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S97" s="9" t="n">
+      <x:c r="S97" s="9" t="str">
         <x:v>5155511</x:v>
       </x:c>
       <x:c r="T97" s="10" t="str">
@@ -6590,7 +6662,7 @@
       <x:c r="R98" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S98" s="9" t="n">
+      <x:c r="S98" s="9" t="str">
         <x:v>5155512</x:v>
       </x:c>
       <x:c r="T98" s="10" t="str">
@@ -6645,7 +6717,7 @@
       <x:c r="R99" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S99" s="9" t="n">
+      <x:c r="S99" s="9" t="str">
         <x:v>5155516</x:v>
       </x:c>
       <x:c r="T99" s="10" t="str">
@@ -6700,7 +6772,7 @@
       <x:c r="R100" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S100" s="9" t="n">
+      <x:c r="S100" s="9" t="str">
         <x:v>5155517</x:v>
       </x:c>
       <x:c r="T100" s="10" t="str">
@@ -6755,7 +6827,7 @@
       <x:c r="R101" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S101" s="9" t="n">
+      <x:c r="S101" s="9" t="str">
         <x:v>5155518</x:v>
       </x:c>
       <x:c r="T101" s="10" t="str">
@@ -6810,7 +6882,7 @@
       <x:c r="R102" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S102" s="9" t="n">
+      <x:c r="S102" s="9" t="str">
         <x:v>5155520</x:v>
       </x:c>
       <x:c r="T102" s="10" t="str">
@@ -6865,7 +6937,7 @@
       <x:c r="R103" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S103" s="9" t="n">
+      <x:c r="S103" s="9" t="str">
         <x:v>5155522</x:v>
       </x:c>
       <x:c r="T103" s="10" t="str">
@@ -6920,7 +6992,7 @@
       <x:c r="R104" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S104" s="9" t="n">
+      <x:c r="S104" s="9" t="str">
         <x:v>5155524</x:v>
       </x:c>
       <x:c r="T104" s="10" t="str">
@@ -6975,7 +7047,7 @@
       <x:c r="R105" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S105" s="9" t="n">
+      <x:c r="S105" s="9" t="str">
         <x:v>5155525</x:v>
       </x:c>
       <x:c r="T105" s="10" t="str">
@@ -7030,7 +7102,7 @@
       <x:c r="R106" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S106" s="9" t="n">
+      <x:c r="S106" s="9" t="str">
         <x:v>5395338</x:v>
       </x:c>
       <x:c r="T106" s="10" t="str">
@@ -7085,7 +7157,7 @@
       <x:c r="R107" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S107" s="9" t="n">
+      <x:c r="S107" s="9" t="str">
         <x:v>5376314</x:v>
       </x:c>
       <x:c r="T107" s="10" t="str">
@@ -7140,7 +7212,7 @@
       <x:c r="R108" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S108" s="9" t="n">
+      <x:c r="S108" s="9" t="str">
         <x:v>5151721</x:v>
       </x:c>
       <x:c r="T108" s="10" t="str">
@@ -7195,7 +7267,7 @@
       <x:c r="R109" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S109" s="9" t="n">
+      <x:c r="S109" s="9" t="str">
         <x:v>5155501</x:v>
       </x:c>
       <x:c r="T109" s="10" t="str">
@@ -7250,7 +7322,7 @@
       <x:c r="R110" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S110" s="9" t="n">
+      <x:c r="S110" s="9" t="str">
         <x:v>5155502</x:v>
       </x:c>
       <x:c r="T110" s="10" t="str">
@@ -7305,7 +7377,7 @@
       <x:c r="R111" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S111" s="9" t="n">
+      <x:c r="S111" s="9" t="str">
         <x:v>5155507</x:v>
       </x:c>
       <x:c r="T111" s="10" t="str">
@@ -7360,7 +7432,7 @@
       <x:c r="R112" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S112" s="9" t="n">
+      <x:c r="S112" s="9" t="str">
         <x:v>5155508</x:v>
       </x:c>
       <x:c r="T112" s="10" t="str">
@@ -7415,7 +7487,7 @@
       <x:c r="R113" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S113" s="9" t="n">
+      <x:c r="S113" s="9" t="str">
         <x:v>5155510</x:v>
       </x:c>
       <x:c r="T113" s="10" t="str">
@@ -7470,7 +7542,7 @@
       <x:c r="R114" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S114" s="9" t="n">
+      <x:c r="S114" s="9" t="str">
         <x:v>5155514</x:v>
       </x:c>
       <x:c r="T114" s="10" t="str">
@@ -7525,7 +7597,7 @@
       <x:c r="R115" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S115" s="9" t="n">
+      <x:c r="S115" s="9" t="str">
         <x:v>5155519</x:v>
       </x:c>
       <x:c r="T115" s="10" t="str">
@@ -7580,7 +7652,7 @@
       <x:c r="R116" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S116" s="9" t="n">
+      <x:c r="S116" s="9" t="str">
         <x:v>5155521</x:v>
       </x:c>
       <x:c r="T116" s="10" t="str">
@@ -7635,7 +7707,7 @@
       <x:c r="R117" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S117" s="9" t="n">
+      <x:c r="S117" s="9" t="str">
         <x:v>5155526</x:v>
       </x:c>
       <x:c r="T117" s="10" t="str">
@@ -7690,7 +7762,7 @@
       <x:c r="R118" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S118" s="9" t="n">
+      <x:c r="S118" s="9" t="str">
         <x:v>5155527</x:v>
       </x:c>
       <x:c r="T118" s="10" t="str">
@@ -7745,7 +7817,7 @@
       <x:c r="R119" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S119" s="9" t="n">
+      <x:c r="S119" s="9" t="str">
         <x:v>5376234</x:v>
       </x:c>
       <x:c r="T119" s="10" t="str">
@@ -7800,7 +7872,7 @@
       <x:c r="R120" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S120" s="9" t="n">
+      <x:c r="S120" s="9" t="str">
         <x:v>5394930</x:v>
       </x:c>
       <x:c r="T120" s="10" t="str">
@@ -7855,7 +7927,7 @@
       <x:c r="R121" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S121" s="9" t="n">
+      <x:c r="S121" s="9" t="str">
         <x:v>5395059</x:v>
       </x:c>
       <x:c r="T121" s="10" t="str">
@@ -7910,7 +7982,7 @@
       <x:c r="R122" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S122" s="9" t="n">
+      <x:c r="S122" s="9" t="str">
         <x:v>5395061</x:v>
       </x:c>
       <x:c r="T122" s="10" t="str">
@@ -7965,7 +8037,7 @@
       <x:c r="R123" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S123" s="9" t="n">
+      <x:c r="S123" s="9" t="str">
         <x:v>5395064</x:v>
       </x:c>
       <x:c r="T123" s="10" t="str">
@@ -8020,7 +8092,7 @@
       <x:c r="R124" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S124" s="9" t="n">
+      <x:c r="S124" s="9" t="str">
         <x:v>5395208</x:v>
       </x:c>
       <x:c r="T124" s="10" t="str">
@@ -8075,7 +8147,7 @@
       <x:c r="R125" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S125" s="9" t="n">
+      <x:c r="S125" s="9" t="str">
         <x:v>5418390</x:v>
       </x:c>
       <x:c r="T125" s="10" t="str">
@@ -8130,7 +8202,7 @@
       <x:c r="R126" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S126" s="9" t="n">
+      <x:c r="S126" s="9" t="str">
         <x:v>5418674</x:v>
       </x:c>
       <x:c r="T126" s="10" t="str">
@@ -8194,7 +8266,7 @@
       <x:c r="R127" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S127" s="9" t="n">
+      <x:c r="S127" s="9" t="str">
         <x:v>3702594</x:v>
       </x:c>
       <x:c r="T127" s="10" t="str">
@@ -8258,7 +8330,7 @@
       <x:c r="R128" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S128" s="9" t="n">
+      <x:c r="S128" s="9" t="str">
         <x:v>3703278</x:v>
       </x:c>
       <x:c r="T128" s="10" t="str">
@@ -8319,7 +8391,7 @@
       <x:c r="R129" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S129" s="9" t="n">
+      <x:c r="S129" s="9" t="str">
         <x:v>3703279</x:v>
       </x:c>
       <x:c r="T129" s="10" t="str">
@@ -8380,7 +8452,7 @@
       <x:c r="R130" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S130" s="9" t="n">
+      <x:c r="S130" s="9" t="str">
         <x:v>5151142</x:v>
       </x:c>
       <x:c r="T130" s="10" t="str">
@@ -8441,7 +8513,7 @@
       <x:c r="R131" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S131" s="9" t="n">
+      <x:c r="S131" s="9" t="str">
         <x:v>5151434</x:v>
       </x:c>
       <x:c r="T131" s="10" t="str">
@@ -8502,7 +8574,7 @@
       <x:c r="R132" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S132" s="9" t="n">
+      <x:c r="S132" s="9" t="str">
         <x:v>5151444</x:v>
       </x:c>
       <x:c r="T132" s="10" t="str">
@@ -8563,7 +8635,7 @@
       <x:c r="R133" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S133" s="9" t="n">
+      <x:c r="S133" s="9" t="str">
         <x:v>5151545</x:v>
       </x:c>
       <x:c r="T133" s="10" t="str">
@@ -8624,7 +8696,7 @@
       <x:c r="R134" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S134" s="9" t="n">
+      <x:c r="S134" s="9" t="str">
         <x:v>5151641</x:v>
       </x:c>
       <x:c r="T134" s="10" t="str">
@@ -8688,7 +8760,7 @@
       <x:c r="R135" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S135" s="9" t="n">
+      <x:c r="S135" s="9" t="str">
         <x:v>5151681</x:v>
       </x:c>
       <x:c r="T135" s="10" t="str">
@@ -8749,7 +8821,7 @@
       <x:c r="R136" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S136" s="9" t="n">
+      <x:c r="S136" s="9" t="str">
         <x:v>5151683</x:v>
       </x:c>
       <x:c r="T136" s="10" t="str">
@@ -8813,7 +8885,7 @@
       <x:c r="R137" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S137" s="9" t="n">
+      <x:c r="S137" s="9" t="str">
         <x:v>5151733</x:v>
       </x:c>
       <x:c r="T137" s="10" t="str">
@@ -8874,7 +8946,7 @@
       <x:c r="R138" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S138" s="9" t="n">
+      <x:c r="S138" s="9" t="str">
         <x:v>5151743</x:v>
       </x:c>
       <x:c r="T138" s="10" t="str">
@@ -8936,7 +9008,7 @@
       <x:c r="R139" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S139" s="9" t="n">
+      <x:c r="S139" s="9" t="str">
         <x:v>5151796</x:v>
       </x:c>
       <x:c r="T139" s="10" t="str">
@@ -8997,7 +9069,7 @@
       <x:c r="R140" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S140" s="9" t="n">
+      <x:c r="S140" s="9" t="str">
         <x:v>5151863</x:v>
       </x:c>
       <x:c r="T140" s="10" t="str">
@@ -9058,7 +9130,7 @@
       <x:c r="R141" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S141" s="9" t="n">
+      <x:c r="S141" s="9" t="str">
         <x:v>5151974</x:v>
       </x:c>
       <x:c r="T141" s="10" t="str">
@@ -9120,7 +9192,7 @@
       <x:c r="R142" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S142" s="9" t="n">
+      <x:c r="S142" s="9" t="str">
         <x:v>5152012</x:v>
       </x:c>
       <x:c r="T142" s="10" t="str">
@@ -9185,7 +9257,7 @@
       <x:c r="R143" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S143" s="9" t="n">
+      <x:c r="S143" s="9" t="str">
         <x:v>5152026</x:v>
       </x:c>
       <x:c r="T143" s="10" t="str">
@@ -9246,7 +9318,7 @@
       <x:c r="R144" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S144" s="9" t="n">
+      <x:c r="S144" s="9" t="str">
         <x:v>5155373</x:v>
       </x:c>
       <x:c r="T144" s="10" t="str">
@@ -9307,7 +9379,7 @@
       <x:c r="R145" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S145" s="9" t="n">
+      <x:c r="S145" s="9" t="str">
         <x:v>5155416</x:v>
       </x:c>
       <x:c r="T145" s="10" t="str">
@@ -9368,7 +9440,7 @@
       <x:c r="R146" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S146" s="9" t="n">
+      <x:c r="S146" s="9" t="str">
         <x:v>5155542</x:v>
       </x:c>
       <x:c r="T146" s="10" t="str">
@@ -9429,7 +9501,7 @@
       <x:c r="R147" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S147" s="9" t="n">
+      <x:c r="S147" s="9" t="str">
         <x:v>5155545</x:v>
       </x:c>
       <x:c r="T147" s="10" t="str">
@@ -9493,7 +9565,7 @@
       <x:c r="R148" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S148" s="9" t="n">
+      <x:c r="S148" s="9" t="str">
         <x:v>5155546</x:v>
       </x:c>
       <x:c r="T148" s="10" t="str">
@@ -9554,7 +9626,7 @@
       <x:c r="R149" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S149" s="9" t="n">
+      <x:c r="S149" s="9" t="str">
         <x:v>5155552</x:v>
       </x:c>
       <x:c r="T149" s="10" t="str">
@@ -9615,7 +9687,7 @@
       <x:c r="R150" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S150" s="9" t="n">
+      <x:c r="S150" s="9" t="str">
         <x:v>5155554</x:v>
       </x:c>
       <x:c r="T150" s="10" t="str">
@@ -9676,7 +9748,7 @@
       <x:c r="R151" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S151" s="9" t="n">
+      <x:c r="S151" s="9" t="str">
         <x:v>5155555</x:v>
       </x:c>
       <x:c r="T151" s="10" t="str">
@@ -9737,7 +9809,7 @@
       <x:c r="R152" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S152" s="9" t="n">
+      <x:c r="S152" s="9" t="str">
         <x:v>5155556</x:v>
       </x:c>
       <x:c r="T152" s="10" t="str">
@@ -9798,7 +9870,7 @@
       <x:c r="R153" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S153" s="9" t="n">
+      <x:c r="S153" s="9" t="str">
         <x:v>5155557</x:v>
       </x:c>
       <x:c r="T153" s="10" t="str">
@@ -9859,7 +9931,7 @@
       <x:c r="R154" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S154" s="9" t="n">
+      <x:c r="S154" s="9" t="str">
         <x:v>5155559</x:v>
       </x:c>
       <x:c r="T154" s="10" t="str">
@@ -9925,7 +9997,7 @@
       <x:c r="R155" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S155" s="9" t="n">
+      <x:c r="S155" s="9" t="str">
         <x:v>5155561</x:v>
       </x:c>
       <x:c r="T155" s="10" t="str">
@@ -9986,7 +10058,7 @@
       <x:c r="R156" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S156" s="9" t="n">
+      <x:c r="S156" s="9" t="str">
         <x:v>5155562</x:v>
       </x:c>
       <x:c r="T156" s="10" t="str">
@@ -10047,7 +10119,7 @@
       <x:c r="R157" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S157" s="9" t="n">
+      <x:c r="S157" s="9" t="str">
         <x:v>5155563</x:v>
       </x:c>
       <x:c r="T157" s="10" t="str">
@@ -10109,7 +10181,7 @@
       <x:c r="R158" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S158" s="9" t="n">
+      <x:c r="S158" s="9" t="str">
         <x:v>5155566</x:v>
       </x:c>
       <x:c r="T158" s="10" t="str">
@@ -10170,7 +10242,7 @@
       <x:c r="R159" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S159" s="9" t="n">
+      <x:c r="S159" s="9" t="str">
         <x:v>5155567</x:v>
       </x:c>
       <x:c r="T159" s="10" t="str">
@@ -10231,7 +10303,7 @@
       <x:c r="R160" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S160" s="9" t="n">
+      <x:c r="S160" s="9" t="str">
         <x:v>5155572</x:v>
       </x:c>
       <x:c r="T160" s="10" t="str">
@@ -10292,7 +10364,7 @@
       <x:c r="R161" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S161" s="9" t="n">
+      <x:c r="S161" s="9" t="str">
         <x:v>5155579</x:v>
       </x:c>
       <x:c r="T161" s="10" t="str">
@@ -10353,7 +10425,7 @@
       <x:c r="R162" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S162" s="9" t="n">
+      <x:c r="S162" s="9" t="str">
         <x:v>5155816</x:v>
       </x:c>
       <x:c r="T162" s="10" t="str">
@@ -10414,7 +10486,7 @@
       <x:c r="R163" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S163" s="9" t="n">
+      <x:c r="S163" s="9" t="str">
         <x:v>5155999</x:v>
       </x:c>
       <x:c r="T163" s="10" t="str">
@@ -10475,7 +10547,7 @@
       <x:c r="R164" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S164" s="9" t="n">
+      <x:c r="S164" s="9" t="str">
         <x:v>5376348</x:v>
       </x:c>
       <x:c r="T164" s="10" t="str">
@@ -10537,7 +10609,7 @@
       <x:c r="R165" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S165" s="9" t="n">
+      <x:c r="S165" s="9" t="str">
         <x:v>5376353</x:v>
       </x:c>
       <x:c r="T165" s="10" t="str">
@@ -10598,7 +10670,7 @@
       <x:c r="R166" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S166" s="9" t="n">
+      <x:c r="S166" s="9" t="str">
         <x:v>5376359</x:v>
       </x:c>
       <x:c r="T166" s="10" t="str">
@@ -10659,7 +10731,7 @@
       <x:c r="R167" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S167" s="9" t="n">
+      <x:c r="S167" s="9" t="str">
         <x:v>3702596</x:v>
       </x:c>
       <x:c r="T167" s="10" t="str">
@@ -10720,7 +10792,7 @@
       <x:c r="R168" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S168" s="9" t="n">
+      <x:c r="S168" s="9" t="str">
         <x:v>3702900</x:v>
       </x:c>
       <x:c r="T168" s="10" t="str">
@@ -10782,7 +10854,7 @@
       <x:c r="R169" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S169" s="9" t="n">
+      <x:c r="S169" s="9" t="str">
         <x:v>3703315</x:v>
       </x:c>
       <x:c r="T169" s="10" t="str">
@@ -10843,7 +10915,7 @@
       <x:c r="R170" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S170" s="9" t="n">
+      <x:c r="S170" s="9" t="str">
         <x:v>5151889</x:v>
       </x:c>
       <x:c r="T170" s="10" t="str">
@@ -10904,7 +10976,7 @@
       <x:c r="R171" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S171" s="9" t="n">
+      <x:c r="S171" s="9" t="str">
         <x:v>5155570</x:v>
       </x:c>
       <x:c r="T171" s="10" t="str">
@@ -10965,7 +11037,7 @@
       <x:c r="R172" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S172" s="9" t="n">
+      <x:c r="S172" s="9" t="str">
         <x:v>5155701</x:v>
       </x:c>
       <x:c r="T172" s="10" t="str">
@@ -11026,7 +11098,7 @@
       <x:c r="R173" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S173" s="9" t="n">
+      <x:c r="S173" s="9" t="str">
         <x:v>5377731</x:v>
       </x:c>
       <x:c r="T173" s="10" t="str">
@@ -11090,7 +11162,7 @@
       <x:c r="R174" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S174" s="9" t="n">
+      <x:c r="S174" s="9" t="str">
         <x:v>5378138</x:v>
       </x:c>
       <x:c r="T174" s="10" t="str">
@@ -11151,7 +11223,7 @@
       <x:c r="R175" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S175" s="9" t="n">
+      <x:c r="S175" s="9" t="str">
         <x:v>5151129</x:v>
       </x:c>
       <x:c r="T175" s="10" t="str">
@@ -11212,7 +11284,7 @@
       <x:c r="R176" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S176" s="9" t="n">
+      <x:c r="S176" s="9" t="str">
         <x:v>5151135</x:v>
       </x:c>
       <x:c r="T176" s="10" t="str">
@@ -11273,7 +11345,7 @@
       <x:c r="R177" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S177" s="9" t="n">
+      <x:c r="S177" s="9" t="str">
         <x:v>5151400</x:v>
       </x:c>
       <x:c r="T177" s="10" t="str">
@@ -11334,7 +11406,7 @@
       <x:c r="R178" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S178" s="9" t="n">
+      <x:c r="S178" s="9" t="str">
         <x:v>5151464</x:v>
       </x:c>
       <x:c r="T178" s="10" t="str">
@@ -11398,7 +11470,7 @@
       <x:c r="R179" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S179" s="9" t="n">
+      <x:c r="S179" s="9" t="str">
         <x:v>5151532</x:v>
       </x:c>
       <x:c r="T179" s="10" t="str">
@@ -11460,7 +11532,7 @@
       <x:c r="R180" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S180" s="9" t="n">
+      <x:c r="S180" s="9" t="str">
         <x:v>5151539</x:v>
       </x:c>
       <x:c r="T180" s="10" t="str">
@@ -11521,7 +11593,7 @@
       <x:c r="R181" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S181" s="9" t="n">
+      <x:c r="S181" s="9" t="str">
         <x:v>5151626</x:v>
       </x:c>
       <x:c r="T181" s="10" t="str">
@@ -11582,7 +11654,7 @@
       <x:c r="R182" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S182" s="9" t="n">
+      <x:c r="S182" s="9" t="str">
         <x:v>5151627</x:v>
       </x:c>
       <x:c r="T182" s="10" t="str">
@@ -11643,7 +11715,7 @@
       <x:c r="R183" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S183" s="9" t="n">
+      <x:c r="S183" s="9" t="str">
         <x:v>5151685</x:v>
       </x:c>
       <x:c r="T183" s="10" t="str">
@@ -11704,7 +11776,7 @@
       <x:c r="R184" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S184" s="9" t="n">
+      <x:c r="S184" s="9" t="str">
         <x:v>5151746</x:v>
       </x:c>
       <x:c r="T184" s="10" t="str">
@@ -11769,7 +11841,7 @@
       <x:c r="R185" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S185" s="9" t="n">
+      <x:c r="S185" s="9" t="str">
         <x:v>5151792</x:v>
       </x:c>
       <x:c r="T185" s="10" t="str">
@@ -11831,7 +11903,7 @@
       <x:c r="R186" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S186" s="9" t="n">
+      <x:c r="S186" s="9" t="str">
         <x:v>5151800</x:v>
       </x:c>
       <x:c r="T186" s="10" t="str">
@@ -11892,7 +11964,7 @@
       <x:c r="R187" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S187" s="9" t="n">
+      <x:c r="S187" s="9" t="str">
         <x:v>5152024</x:v>
       </x:c>
       <x:c r="T187" s="10" t="str">
@@ -11953,7 +12025,7 @@
       <x:c r="R188" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S188" s="9" t="n">
+      <x:c r="S188" s="9" t="str">
         <x:v>5155422</x:v>
       </x:c>
       <x:c r="T188" s="10" t="str">
@@ -12014,7 +12086,7 @@
       <x:c r="R189" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S189" s="9" t="n">
+      <x:c r="S189" s="9" t="str">
         <x:v>5155538</x:v>
       </x:c>
       <x:c r="T189" s="10" t="str">
@@ -12078,7 +12150,7 @@
       <x:c r="R190" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S190" s="9" t="n">
+      <x:c r="S190" s="9" t="str">
         <x:v>5155539</x:v>
       </x:c>
       <x:c r="T190" s="10" t="str">
@@ -12139,7 +12211,7 @@
       <x:c r="R191" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S191" s="9" t="n">
+      <x:c r="S191" s="9" t="str">
         <x:v>5155540</x:v>
       </x:c>
       <x:c r="T191" s="10" t="str">
@@ -12203,7 +12275,7 @@
       <x:c r="R192" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S192" s="9" t="n">
+      <x:c r="S192" s="9" t="str">
         <x:v>5155548</x:v>
       </x:c>
       <x:c r="T192" s="10" t="str">
@@ -12267,7 +12339,7 @@
       <x:c r="R193" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S193" s="9" t="n">
+      <x:c r="S193" s="9" t="str">
         <x:v>5155549</x:v>
       </x:c>
       <x:c r="T193" s="10" t="str">
@@ -12331,7 +12403,7 @@
       <x:c r="R194" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S194" s="9" t="n">
+      <x:c r="S194" s="9" t="str">
         <x:v>5155550</x:v>
       </x:c>
       <x:c r="T194" s="10" t="str">
@@ -12392,7 +12464,7 @@
       <x:c r="R195" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S195" s="9" t="n">
+      <x:c r="S195" s="9" t="str">
         <x:v>5155553</x:v>
       </x:c>
       <x:c r="T195" s="10" t="str">
@@ -12458,7 +12530,7 @@
       <x:c r="R196" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S196" s="9" t="n">
+      <x:c r="S196" s="9" t="str">
         <x:v>5155558</x:v>
       </x:c>
       <x:c r="T196" s="10" t="str">
@@ -12519,7 +12591,7 @@
       <x:c r="R197" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S197" s="9" t="n">
+      <x:c r="S197" s="9" t="str">
         <x:v>5155565</x:v>
       </x:c>
       <x:c r="T197" s="10" t="str">
@@ -12580,7 +12652,7 @@
       <x:c r="R198" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S198" s="9" t="n">
+      <x:c r="S198" s="9" t="str">
         <x:v>5155568</x:v>
       </x:c>
       <x:c r="T198" s="10" t="str">
@@ -12641,7 +12713,7 @@
       <x:c r="R199" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S199" s="9" t="n">
+      <x:c r="S199" s="9" t="str">
         <x:v>5155569</x:v>
       </x:c>
       <x:c r="T199" s="10" t="str">
@@ -12702,7 +12774,7 @@
       <x:c r="R200" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S200" s="9" t="n">
+      <x:c r="S200" s="9" t="str">
         <x:v>5155571</x:v>
       </x:c>
       <x:c r="T200" s="10" t="str">
@@ -12763,7 +12835,7 @@
       <x:c r="R201" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S201" s="9" t="n">
+      <x:c r="S201" s="9" t="str">
         <x:v>5155573</x:v>
       </x:c>
       <x:c r="T201" s="10" t="str">
@@ -12824,7 +12896,7 @@
       <x:c r="R202" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S202" s="9" t="n">
+      <x:c r="S202" s="9" t="str">
         <x:v>5155574</x:v>
       </x:c>
       <x:c r="T202" s="10" t="str">
@@ -12885,7 +12957,7 @@
       <x:c r="R203" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S203" s="9" t="n">
+      <x:c r="S203" s="9" t="str">
         <x:v>5155575</x:v>
       </x:c>
       <x:c r="T203" s="10" t="str">
@@ -12946,7 +13018,7 @@
       <x:c r="R204" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S204" s="9" t="n">
+      <x:c r="S204" s="9" t="str">
         <x:v>5155577</x:v>
       </x:c>
       <x:c r="T204" s="10" t="str">
@@ -13010,7 +13082,7 @@
       <x:c r="R205" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S205" s="9" t="n">
+      <x:c r="S205" s="9" t="str">
         <x:v>5155580</x:v>
       </x:c>
       <x:c r="T205" s="10" t="str">
@@ -13071,7 +13143,7 @@
       <x:c r="R206" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S206" s="9" t="n">
+      <x:c r="S206" s="9" t="str">
         <x:v>5155822</x:v>
       </x:c>
       <x:c r="T206" s="10" t="str">
@@ -13132,7 +13204,7 @@
       <x:c r="R207" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S207" s="9" t="n">
+      <x:c r="S207" s="9" t="str">
         <x:v>5155828</x:v>
       </x:c>
       <x:c r="T207" s="10" t="str">
@@ -13193,7 +13265,7 @@
       <x:c r="R208" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S208" s="9" t="n">
+      <x:c r="S208" s="9" t="str">
         <x:v>5155861</x:v>
       </x:c>
       <x:c r="T208" s="10" t="str">
@@ -13257,7 +13329,7 @@
       <x:c r="R209" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S209" s="9" t="n">
+      <x:c r="S209" s="9" t="str">
         <x:v>3702685</x:v>
       </x:c>
       <x:c r="T209" s="10" t="str">
@@ -13321,7 +13393,7 @@
       <x:c r="R210" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S210" s="9" t="n">
+      <x:c r="S210" s="9" t="str">
         <x:v>3702686</x:v>
       </x:c>
       <x:c r="T210" s="10" t="str">
@@ -13385,7 +13457,7 @@
       <x:c r="R211" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S211" s="9" t="n">
+      <x:c r="S211" s="9" t="str">
         <x:v>3703076</x:v>
       </x:c>
       <x:c r="T211" s="10" t="str">
@@ -13449,7 +13521,7 @@
       <x:c r="R212" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S212" s="9" t="n">
+      <x:c r="S212" s="9" t="str">
         <x:v>5151594</x:v>
       </x:c>
       <x:c r="T212" s="10" t="str">
@@ -13515,7 +13587,7 @@
       <x:c r="R213" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S213" s="9" t="n">
+      <x:c r="S213" s="9" t="str">
         <x:v>5151939</x:v>
       </x:c>
       <x:c r="T213" s="10" t="str">
@@ -13583,7 +13655,7 @@
       <x:c r="R214" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S214" s="9" t="n">
+      <x:c r="S214" s="9" t="str">
         <x:v>5152071</x:v>
       </x:c>
       <x:c r="T214" s="10" t="str">
@@ -13647,7 +13719,7 @@
       <x:c r="R215" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S215" s="9" t="n">
+      <x:c r="S215" s="9" t="str">
         <x:v>5155583</x:v>
       </x:c>
       <x:c r="T215" s="10" t="str">
@@ -13716,7 +13788,7 @@
       <x:c r="R216" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S216" s="9" t="n">
+      <x:c r="S216" s="9" t="str">
         <x:v>5155588</x:v>
       </x:c>
       <x:c r="T216" s="10" t="str">
@@ -13780,7 +13852,7 @@
       <x:c r="R217" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S217" s="9" t="n">
+      <x:c r="S217" s="9" t="str">
         <x:v>5155589</x:v>
       </x:c>
       <x:c r="T217" s="10" t="str">
@@ -13851,7 +13923,7 @@
       <x:c r="R218" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S218" s="9" t="n">
+      <x:c r="S218" s="9" t="str">
         <x:v>5155590</x:v>
       </x:c>
       <x:c r="T218" s="10" t="str">
@@ -13919,7 +13991,7 @@
       <x:c r="R219" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S219" s="9" t="n">
+      <x:c r="S219" s="9" t="str">
         <x:v>5155598</x:v>
       </x:c>
       <x:c r="T219" s="10" t="str">
@@ -13983,7 +14055,7 @@
       <x:c r="R220" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S220" s="9" t="n">
+      <x:c r="S220" s="9" t="str">
         <x:v>5155599</x:v>
       </x:c>
       <x:c r="T220" s="10" t="str">
@@ -14049,7 +14121,7 @@
       <x:c r="R221" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S221" s="9" t="n">
+      <x:c r="S221" s="9" t="str">
         <x:v>5155602</x:v>
       </x:c>
       <x:c r="T221" s="10" t="str">
@@ -14114,7 +14186,7 @@
       <x:c r="R222" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S222" s="9" t="n">
+      <x:c r="S222" s="9" t="str">
         <x:v>5155603</x:v>
       </x:c>
       <x:c r="T222" s="10" t="str">
@@ -14178,7 +14250,7 @@
       <x:c r="R223" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S223" s="9" t="n">
+      <x:c r="S223" s="9" t="str">
         <x:v>5155606</x:v>
       </x:c>
       <x:c r="T223" s="10" t="str">
@@ -14242,7 +14314,7 @@
       <x:c r="R224" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S224" s="9" t="n">
+      <x:c r="S224" s="9" t="str">
         <x:v>5155607</x:v>
       </x:c>
       <x:c r="T224" s="10" t="str">
@@ -14311,7 +14383,7 @@
       <x:c r="R225" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S225" s="9" t="n">
+      <x:c r="S225" s="9" t="str">
         <x:v>5155608</x:v>
       </x:c>
       <x:c r="T225" s="10" t="str">
@@ -14375,7 +14447,7 @@
       <x:c r="R226" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S226" s="9" t="n">
+      <x:c r="S226" s="9" t="str">
         <x:v>5155612</x:v>
       </x:c>
       <x:c r="T226" s="10" t="str">
@@ -14439,7 +14511,7 @@
       <x:c r="R227" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S227" s="9" t="n">
+      <x:c r="S227" s="9" t="str">
         <x:v>5155618</x:v>
       </x:c>
       <x:c r="T227" s="10" t="str">
@@ -14511,7 +14583,7 @@
       <x:c r="R228" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S228" s="9" t="n">
+      <x:c r="S228" s="9" t="str">
         <x:v>5155723</x:v>
       </x:c>
       <x:c r="T228" s="10" t="str">
@@ -14575,7 +14647,7 @@
       <x:c r="R229" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S229" s="9" t="n">
+      <x:c r="S229" s="9" t="str">
         <x:v>5155909</x:v>
       </x:c>
       <x:c r="T229" s="10" t="str">
@@ -14639,7 +14711,7 @@
       <x:c r="R230" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S230" s="9" t="n">
+      <x:c r="S230" s="9" t="str">
         <x:v>5376396</x:v>
       </x:c>
       <x:c r="T230" s="10" t="str">
@@ -14703,7 +14775,7 @@
       <x:c r="R231" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S231" s="9" t="n">
+      <x:c r="S231" s="9" t="str">
         <x:v>5377700</x:v>
       </x:c>
       <x:c r="T231" s="10" t="str">
@@ -14767,7 +14839,7 @@
       <x:c r="R232" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S232" s="9" t="n">
+      <x:c r="S232" s="9" t="str">
         <x:v>5378001</x:v>
       </x:c>
       <x:c r="T232" s="10" t="str">
@@ -14831,7 +14903,7 @@
       <x:c r="R233" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S233" s="9" t="n">
+      <x:c r="S233" s="9" t="str">
         <x:v>5378097</x:v>
       </x:c>
       <x:c r="T233" s="10" t="str">
@@ -14895,7 +14967,7 @@
       <x:c r="R234" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S234" s="9" t="n">
+      <x:c r="S234" s="9" t="str">
         <x:v>5378160</x:v>
       </x:c>
       <x:c r="T234" s="10" t="str">
@@ -14957,7 +15029,7 @@
       <x:c r="R235" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S235" s="9" t="n">
+      <x:c r="S235" s="9" t="str">
         <x:v>4204111</x:v>
       </x:c>
       <x:c r="T235" s="10" t="str">
@@ -15021,7 +15093,7 @@
       <x:c r="R236" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S236" s="9" t="n">
+      <x:c r="S236" s="9" t="str">
         <x:v>5151205</x:v>
       </x:c>
       <x:c r="T236" s="10" t="str">
@@ -15085,7 +15157,7 @@
       <x:c r="R237" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S237" s="9" t="n">
+      <x:c r="S237" s="9" t="str">
         <x:v>5152052</x:v>
       </x:c>
       <x:c r="T237" s="10" t="str">
@@ -15149,7 +15221,7 @@
       <x:c r="R238" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S238" s="9" t="n">
+      <x:c r="S238" s="9" t="str">
         <x:v>5151602</x:v>
       </x:c>
       <x:c r="T238" s="10" t="str">
@@ -15217,7 +15289,7 @@
       <x:c r="R239" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S239" s="9" t="n">
+      <x:c r="S239" s="9" t="str">
         <x:v>5151699</x:v>
       </x:c>
       <x:c r="T239" s="10" t="str">
@@ -15281,7 +15353,7 @@
       <x:c r="R240" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S240" s="9" t="n">
+      <x:c r="S240" s="9" t="str">
         <x:v>5151814</x:v>
       </x:c>
       <x:c r="T240" s="10" t="str">
@@ -15356,7 +15428,7 @@
       <x:c r="R241" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S241" s="9" t="n">
+      <x:c r="S241" s="9" t="str">
         <x:v>5151815</x:v>
       </x:c>
       <x:c r="T241" s="10" t="str">
@@ -15420,7 +15492,7 @@
       <x:c r="R242" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S242" s="9" t="n">
+      <x:c r="S242" s="9" t="str">
         <x:v>5152049</x:v>
       </x:c>
       <x:c r="T242" s="10" t="str">
@@ -15484,7 +15556,7 @@
       <x:c r="R243" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S243" s="9" t="n">
+      <x:c r="S243" s="9" t="str">
         <x:v>5155581</x:v>
       </x:c>
       <x:c r="T243" s="10" t="str">
@@ -15548,7 +15620,7 @@
       <x:c r="R244" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S244" s="9" t="n">
+      <x:c r="S244" s="9" t="str">
         <x:v>5155584</x:v>
       </x:c>
       <x:c r="T244" s="10" t="str">
@@ -15616,7 +15688,7 @@
       <x:c r="R245" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S245" s="9" t="n">
+      <x:c r="S245" s="9" t="str">
         <x:v>5155585</x:v>
       </x:c>
       <x:c r="T245" s="10" t="str">
@@ -15680,7 +15752,7 @@
       <x:c r="R246" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S246" s="9" t="n">
+      <x:c r="S246" s="9" t="str">
         <x:v>5155586</x:v>
       </x:c>
       <x:c r="T246" s="10" t="str">
@@ -15754,7 +15826,7 @@
       <x:c r="R247" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S247" s="9" t="n">
+      <x:c r="S247" s="9" t="str">
         <x:v>5155587</x:v>
       </x:c>
       <x:c r="T247" s="10" t="str">
@@ -15818,7 +15890,7 @@
       <x:c r="R248" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S248" s="9" t="n">
+      <x:c r="S248" s="9" t="str">
         <x:v>5155591</x:v>
       </x:c>
       <x:c r="T248" s="10" t="str">
@@ -15882,7 +15954,7 @@
       <x:c r="R249" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S249" s="9" t="n">
+      <x:c r="S249" s="9" t="str">
         <x:v>5155592</x:v>
       </x:c>
       <x:c r="T249" s="10" t="str">
@@ -15946,7 +16018,7 @@
       <x:c r="R250" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S250" s="9" t="n">
+      <x:c r="S250" s="9" t="str">
         <x:v>5155595</x:v>
       </x:c>
       <x:c r="T250" s="10" t="str">
@@ -16010,7 +16082,7 @@
       <x:c r="R251" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S251" s="9" t="n">
+      <x:c r="S251" s="9" t="str">
         <x:v>5155596</x:v>
       </x:c>
       <x:c r="T251" s="10" t="str">
@@ -16078,7 +16150,7 @@
       <x:c r="R252" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S252" s="9" t="n">
+      <x:c r="S252" s="9" t="str">
         <x:v>5155597</x:v>
       </x:c>
       <x:c r="T252" s="10" t="str">
@@ -16142,7 +16214,7 @@
       <x:c r="R253" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S253" s="9" t="n">
+      <x:c r="S253" s="9" t="str">
         <x:v>5155604</x:v>
       </x:c>
       <x:c r="T253" s="10" t="str">
@@ -16206,7 +16278,7 @@
       <x:c r="R254" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S254" s="9" t="n">
+      <x:c r="S254" s="9" t="str">
         <x:v>5155605</x:v>
       </x:c>
       <x:c r="T254" s="10" t="str">
@@ -16270,7 +16342,7 @@
       <x:c r="R255" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S255" s="9" t="n">
+      <x:c r="S255" s="9" t="str">
         <x:v>5155610</x:v>
       </x:c>
       <x:c r="T255" s="10" t="str">
@@ -16334,7 +16406,7 @@
       <x:c r="R256" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S256" s="9" t="n">
+      <x:c r="S256" s="9" t="str">
         <x:v>5155611</x:v>
       </x:c>
       <x:c r="T256" s="10" t="str">
@@ -16398,7 +16470,7 @@
       <x:c r="R257" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S257" s="9" t="n">
+      <x:c r="S257" s="9" t="str">
         <x:v>5155615</x:v>
       </x:c>
       <x:c r="T257" s="10" t="str">
@@ -16463,7 +16535,7 @@
       <x:c r="R258" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S258" s="9" t="n">
+      <x:c r="S258" s="9" t="str">
         <x:v>5155616</x:v>
       </x:c>
       <x:c r="T258" s="10" t="str">
@@ -16528,7 +16600,7 @@
       <x:c r="R259" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S259" s="9" t="n">
+      <x:c r="S259" s="9" t="str">
         <x:v>5376367</x:v>
       </x:c>
       <x:c r="T259" s="10" t="str">
@@ -16592,7 +16664,7 @@
       <x:c r="R260" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S260" s="9" t="n">
+      <x:c r="S260" s="9" t="str">
         <x:v>5376368</x:v>
       </x:c>
       <x:c r="T260" s="10" t="str">
@@ -16656,7 +16728,7 @@
       <x:c r="R261" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S261" s="9" t="n">
+      <x:c r="S261" s="9" t="str">
         <x:v>5377906</x:v>
       </x:c>
       <x:c r="T261" s="10" t="str">
@@ -16720,7 +16792,7 @@
       <x:c r="R262" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S262" s="9" t="n">
+      <x:c r="S262" s="9" t="str">
         <x:v>5377998</x:v>
       </x:c>
       <x:c r="T262" s="10" t="str">
@@ -16775,7 +16847,7 @@
       <x:c r="R263" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S263" s="9" t="n">
+      <x:c r="S263" s="9" t="str">
         <x:v>5126947</x:v>
       </x:c>
       <x:c r="T263" s="10" t="str">
@@ -16830,7 +16902,7 @@
       <x:c r="R264" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S264" s="9" t="n">
+      <x:c r="S264" s="9" t="str">
         <x:v>5126948</x:v>
       </x:c>
       <x:c r="T264" s="10" t="str">
@@ -16885,7 +16957,7 @@
       <x:c r="R265" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S265" s="9" t="n">
+      <x:c r="S265" s="9" t="str">
         <x:v>5126949</x:v>
       </x:c>
       <x:c r="T265" s="10" t="str">
@@ -16940,7 +17012,7 @@
       <x:c r="R266" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S266" s="9" t="n">
+      <x:c r="S266" s="9" t="str">
         <x:v>5126950</x:v>
       </x:c>
       <x:c r="T266" s="10" t="str">
@@ -16995,7 +17067,7 @@
       <x:c r="R267" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S267" s="9" t="n">
+      <x:c r="S267" s="9" t="str">
         <x:v>5155620</x:v>
       </x:c>
       <x:c r="T267" s="10" t="str">
@@ -17050,7 +17122,7 @@
       <x:c r="R268" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S268" s="9" t="n">
+      <x:c r="S268" s="9" t="str">
         <x:v>5155621</x:v>
       </x:c>
       <x:c r="T268" s="10" t="str">
@@ -17105,7 +17177,7 @@
       <x:c r="R269" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S269" s="9" t="n">
+      <x:c r="S269" s="9" t="str">
         <x:v>5155623</x:v>
       </x:c>
       <x:c r="T269" s="10" t="str">
@@ -17160,7 +17232,7 @@
       <x:c r="R270" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S270" s="9" t="n">
+      <x:c r="S270" s="9" t="str">
         <x:v>5155625</x:v>
       </x:c>
       <x:c r="T270" s="10" t="str">
@@ -17215,7 +17287,7 @@
       <x:c r="R271" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S271" s="9" t="n">
+      <x:c r="S271" s="9" t="str">
         <x:v>5155630</x:v>
       </x:c>
       <x:c r="T271" s="10" t="str">
@@ -17270,7 +17342,7 @@
       <x:c r="R272" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S272" s="9" t="n">
+      <x:c r="S272" s="9" t="str">
         <x:v>5155631</x:v>
       </x:c>
       <x:c r="T272" s="10" t="str">
@@ -17325,7 +17397,7 @@
       <x:c r="R273" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S273" s="9" t="n">
+      <x:c r="S273" s="9" t="str">
         <x:v>5155632</x:v>
       </x:c>
       <x:c r="T273" s="10" t="str">
@@ -17380,7 +17452,7 @@
       <x:c r="R274" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S274" s="9" t="n">
+      <x:c r="S274" s="9" t="str">
         <x:v>5155637</x:v>
       </x:c>
       <x:c r="T274" s="10" t="str">
@@ -17435,7 +17507,7 @@
       <x:c r="R275" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S275" s="9" t="n">
+      <x:c r="S275" s="9" t="str">
         <x:v>5155638</x:v>
       </x:c>
       <x:c r="T275" s="10" t="str">
@@ -17490,7 +17562,7 @@
       <x:c r="R276" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S276" s="9" t="n">
+      <x:c r="S276" s="9" t="str">
         <x:v>5376399</x:v>
       </x:c>
       <x:c r="T276" s="10" t="str">
@@ -17545,7 +17617,7 @@
       <x:c r="R277" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S277" s="9" t="n">
+      <x:c r="S277" s="9" t="str">
         <x:v>5376400</x:v>
       </x:c>
       <x:c r="T277" s="10" t="str">
@@ -17600,7 +17672,7 @@
       <x:c r="R278" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S278" s="9" t="n">
+      <x:c r="S278" s="9" t="str">
         <x:v>5376415</x:v>
       </x:c>
       <x:c r="T278" s="10" t="str">
@@ -17655,7 +17727,7 @@
       <x:c r="R279" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S279" s="9" t="n">
+      <x:c r="S279" s="9" t="str">
         <x:v>5377923</x:v>
       </x:c>
       <x:c r="T279" s="10" t="str">
@@ -17710,7 +17782,7 @@
       <x:c r="R280" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S280" s="9" t="n">
+      <x:c r="S280" s="9" t="str">
         <x:v>5378179</x:v>
       </x:c>
       <x:c r="T280" s="10" t="str">
@@ -17765,7 +17837,7 @@
       <x:c r="R281" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S281" s="9" t="n">
+      <x:c r="S281" s="9" t="str">
         <x:v>5395062</x:v>
       </x:c>
       <x:c r="T281" s="10" t="str">
@@ -17820,7 +17892,7 @@
       <x:c r="R282" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S282" s="9" t="n">
+      <x:c r="S282" s="9" t="str">
         <x:v>5395199</x:v>
       </x:c>
       <x:c r="T282" s="10" t="str">
@@ -17875,7 +17947,7 @@
       <x:c r="R283" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S283" s="9" t="n">
+      <x:c r="S283" s="9" t="str">
         <x:v>5395206</x:v>
       </x:c>
       <x:c r="T283" s="10" t="str">
@@ -17930,7 +18002,7 @@
       <x:c r="R284" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S284" s="9" t="n">
+      <x:c r="S284" s="9" t="str">
         <x:v>5151841</x:v>
       </x:c>
       <x:c r="T284" s="10" t="str">
@@ -17985,7 +18057,7 @@
       <x:c r="R285" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S285" s="9" t="n">
+      <x:c r="S285" s="9" t="str">
         <x:v>5155629</x:v>
       </x:c>
       <x:c r="T285" s="10" t="str">
@@ -18040,7 +18112,7 @@
       <x:c r="R286" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S286" s="9" t="n">
+      <x:c r="S286" s="9" t="str">
         <x:v>5155641</x:v>
       </x:c>
       <x:c r="T286" s="10" t="str">
@@ -18095,7 +18167,7 @@
       <x:c r="R287" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S287" s="9" t="n">
+      <x:c r="S287" s="9" t="str">
         <x:v>5395207</x:v>
       </x:c>
       <x:c r="T287" s="10" t="str">
@@ -18150,7 +18222,7 @@
       <x:c r="R288" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S288" s="9" t="n">
+      <x:c r="S288" s="9" t="str">
         <x:v>6919035</x:v>
       </x:c>
       <x:c r="T288" s="10" t="str">
@@ -18205,7 +18277,7 @@
       <x:c r="R289" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S289" s="9" t="n">
+      <x:c r="S289" s="9" t="str">
         <x:v>5151839</x:v>
       </x:c>
       <x:c r="T289" s="10" t="str">
@@ -18260,7 +18332,7 @@
       <x:c r="R290" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S290" s="9" t="n">
+      <x:c r="S290" s="9" t="str">
         <x:v>5155619</x:v>
       </x:c>
       <x:c r="T290" s="10" t="str">
@@ -18315,7 +18387,7 @@
       <x:c r="R291" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S291" s="9" t="n">
+      <x:c r="S291" s="9" t="str">
         <x:v>5155622</x:v>
       </x:c>
       <x:c r="T291" s="10" t="str">
@@ -18370,7 +18442,7 @@
       <x:c r="R292" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S292" s="9" t="n">
+      <x:c r="S292" s="9" t="str">
         <x:v>5155624</x:v>
       </x:c>
       <x:c r="T292" s="10" t="str">
@@ -18425,7 +18497,7 @@
       <x:c r="R293" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S293" s="9" t="n">
+      <x:c r="S293" s="9" t="str">
         <x:v>5155626</x:v>
       </x:c>
       <x:c r="T293" s="10" t="str">
@@ -18480,7 +18552,7 @@
       <x:c r="R294" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S294" s="9" t="n">
+      <x:c r="S294" s="9" t="str">
         <x:v>5155627</x:v>
       </x:c>
       <x:c r="T294" s="10" t="str">
@@ -18535,7 +18607,7 @@
       <x:c r="R295" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S295" s="9" t="n">
+      <x:c r="S295" s="9" t="str">
         <x:v>5155628</x:v>
       </x:c>
       <x:c r="T295" s="10" t="str">
@@ -18590,7 +18662,7 @@
       <x:c r="R296" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S296" s="9" t="n">
+      <x:c r="S296" s="9" t="str">
         <x:v>5155634</x:v>
       </x:c>
       <x:c r="T296" s="10" t="str">
@@ -18645,7 +18717,7 @@
       <x:c r="R297" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S297" s="9" t="n">
+      <x:c r="S297" s="9" t="str">
         <x:v>5155635</x:v>
       </x:c>
       <x:c r="T297" s="10" t="str">
@@ -18700,7 +18772,7 @@
       <x:c r="R298" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S298" s="9" t="n">
+      <x:c r="S298" s="9" t="str">
         <x:v>5155639</x:v>
       </x:c>
       <x:c r="T298" s="10" t="str">
@@ -18755,7 +18827,7 @@
       <x:c r="R299" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S299" s="9" t="n">
+      <x:c r="S299" s="9" t="str">
         <x:v>5155640</x:v>
       </x:c>
       <x:c r="T299" s="10" t="str">
@@ -18810,7 +18882,7 @@
       <x:c r="R300" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S300" s="9" t="n">
+      <x:c r="S300" s="9" t="str">
         <x:v>5155642</x:v>
       </x:c>
       <x:c r="T300" s="10" t="str">
@@ -18865,7 +18937,7 @@
       <x:c r="R301" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S301" s="9" t="n">
+      <x:c r="S301" s="9" t="str">
         <x:v>5155960</x:v>
       </x:c>
       <x:c r="T301" s="10" t="str">
@@ -18920,7 +18992,7 @@
       <x:c r="R302" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S302" s="9" t="n">
+      <x:c r="S302" s="9" t="str">
         <x:v>5376384</x:v>
       </x:c>
       <x:c r="T302" s="10" t="str">
@@ -18975,7 +19047,7 @@
       <x:c r="R303" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S303" s="9" t="n">
+      <x:c r="S303" s="9" t="str">
         <x:v>5376413</x:v>
       </x:c>
       <x:c r="T303" s="10" t="str">
@@ -19030,7 +19102,7 @@
       <x:c r="R304" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S304" s="9" t="n">
+      <x:c r="S304" s="9" t="str">
         <x:v>5377709</x:v>
       </x:c>
       <x:c r="T304" s="10" t="str">
@@ -19085,7 +19157,7 @@
       <x:c r="R305" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S305" s="9" t="n">
+      <x:c r="S305" s="9" t="str">
         <x:v>5377929</x:v>
       </x:c>
       <x:c r="T305" s="10" t="str">
@@ -19140,7 +19212,7 @@
       <x:c r="R306" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S306" s="9" t="n">
+      <x:c r="S306" s="9" t="str">
         <x:v>5378180</x:v>
       </x:c>
       <x:c r="T306" s="10" t="str">
@@ -19195,7 +19267,7 @@
       <x:c r="R307" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S307" s="9" t="n">
+      <x:c r="S307" s="9" t="str">
         <x:v>5395202</x:v>
       </x:c>
       <x:c r="T307" s="10" t="str">
@@ -19250,7 +19322,7 @@
       <x:c r="R308" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S308" s="9" t="n">
+      <x:c r="S308" s="9" t="str">
         <x:v>5395347</x:v>
       </x:c>
       <x:c r="T308" s="10" t="str">
@@ -19311,7 +19383,7 @@
       <x:c r="R309" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S309" s="9" t="n">
+      <x:c r="S309" s="9" t="str">
         <x:v>5151130</x:v>
       </x:c>
       <x:c r="T309" s="10" t="str">
@@ -19372,7 +19444,7 @@
       <x:c r="R310" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S310" s="9" t="n">
+      <x:c r="S310" s="9" t="str">
         <x:v>5151179</x:v>
       </x:c>
       <x:c r="T310" s="10" t="str">
@@ -19433,7 +19505,7 @@
       <x:c r="R311" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S311" s="9" t="n">
+      <x:c r="S311" s="9" t="str">
         <x:v>5151418</x:v>
       </x:c>
       <x:c r="T311" s="10" t="str">
@@ -19494,7 +19566,7 @@
       <x:c r="R312" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S312" s="9" t="n">
+      <x:c r="S312" s="9" t="str">
         <x:v>5151424</x:v>
       </x:c>
       <x:c r="T312" s="10" t="str">
@@ -19560,7 +19632,7 @@
       <x:c r="R313" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S313" s="9" t="n">
+      <x:c r="S313" s="9" t="str">
         <x:v>5151450</x:v>
       </x:c>
       <x:c r="T313" s="10" t="str">
@@ -19621,7 +19693,7 @@
       <x:c r="R314" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S314" s="9" t="n">
+      <x:c r="S314" s="9" t="str">
         <x:v>5151548</x:v>
       </x:c>
       <x:c r="T314" s="10" t="str">
@@ -19685,7 +19757,7 @@
       <x:c r="R315" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S315" s="9" t="n">
+      <x:c r="S315" s="9" t="str">
         <x:v>5151636</x:v>
       </x:c>
       <x:c r="T315" s="10" t="str">
@@ -19746,7 +19818,7 @@
       <x:c r="R316" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S316" s="9" t="n">
+      <x:c r="S316" s="9" t="str">
         <x:v>5151753</x:v>
       </x:c>
       <x:c r="T316" s="10" t="str">
@@ -19810,7 +19882,7 @@
       <x:c r="R317" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S317" s="9" t="n">
+      <x:c r="S317" s="9" t="str">
         <x:v>5151757</x:v>
       </x:c>
       <x:c r="T317" s="10" t="str">
@@ -19872,7 +19944,7 @@
       <x:c r="R318" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S318" s="9" t="n">
+      <x:c r="S318" s="9" t="str">
         <x:v>5151761</x:v>
       </x:c>
       <x:c r="T318" s="10" t="str">
@@ -19933,7 +20005,7 @@
       <x:c r="R319" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S319" s="9" t="n">
+      <x:c r="S319" s="9" t="str">
         <x:v>5151773</x:v>
       </x:c>
       <x:c r="T319" s="10" t="str">
@@ -19994,7 +20066,7 @@
       <x:c r="R320" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S320" s="9" t="n">
+      <x:c r="S320" s="9" t="str">
         <x:v>5151865</x:v>
       </x:c>
       <x:c r="T320" s="10" t="str">
@@ -20055,7 +20127,7 @@
       <x:c r="R321" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S321" s="9" t="n">
+      <x:c r="S321" s="9" t="str">
         <x:v>5151970</x:v>
       </x:c>
       <x:c r="T321" s="10" t="str">
@@ -20116,7 +20188,7 @@
       <x:c r="R322" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S322" s="9" t="n">
+      <x:c r="S322" s="9" t="str">
         <x:v>5152043</x:v>
       </x:c>
       <x:c r="T322" s="10" t="str">
@@ -20177,7 +20249,7 @@
       <x:c r="R323" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S323" s="9" t="n">
+      <x:c r="S323" s="9" t="str">
         <x:v>5155356</x:v>
       </x:c>
       <x:c r="T323" s="10" t="str">
@@ -20238,7 +20310,7 @@
       <x:c r="R324" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S324" s="9" t="n">
+      <x:c r="S324" s="9" t="str">
         <x:v>5155644</x:v>
       </x:c>
       <x:c r="T324" s="10" t="str">
@@ -20299,7 +20371,7 @@
       <x:c r="R325" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S325" s="9" t="n">
+      <x:c r="S325" s="9" t="str">
         <x:v>5155645</x:v>
       </x:c>
       <x:c r="T325" s="10" t="str">
@@ -20360,7 +20432,7 @@
       <x:c r="R326" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S326" s="9" t="n">
+      <x:c r="S326" s="9" t="str">
         <x:v>5155648</x:v>
       </x:c>
       <x:c r="T326" s="10" t="str">
@@ -20421,7 +20493,7 @@
       <x:c r="R327" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S327" s="9" t="n">
+      <x:c r="S327" s="9" t="str">
         <x:v>5155659</x:v>
       </x:c>
       <x:c r="T327" s="10" t="str">
@@ -20482,7 +20554,7 @@
       <x:c r="R328" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S328" s="9" t="n">
+      <x:c r="S328" s="9" t="str">
         <x:v>5155661</x:v>
       </x:c>
       <x:c r="T328" s="10" t="str">
@@ -20543,7 +20615,7 @@
       <x:c r="R329" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S329" s="9" t="n">
+      <x:c r="S329" s="9" t="str">
         <x:v>5155668</x:v>
       </x:c>
       <x:c r="T329" s="10" t="str">
@@ -20604,7 +20676,7 @@
       <x:c r="R330" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S330" s="9" t="n">
+      <x:c r="S330" s="9" t="str">
         <x:v>5155672</x:v>
       </x:c>
       <x:c r="T330" s="10" t="str">
@@ -20665,7 +20737,7 @@
       <x:c r="R331" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S331" s="9" t="n">
+      <x:c r="S331" s="9" t="str">
         <x:v>5155673</x:v>
       </x:c>
       <x:c r="T331" s="10" t="str">
@@ -20726,7 +20798,7 @@
       <x:c r="R332" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S332" s="9" t="n">
+      <x:c r="S332" s="9" t="str">
         <x:v>5155678</x:v>
       </x:c>
       <x:c r="T332" s="10" t="str">
@@ -20787,7 +20859,7 @@
       <x:c r="R333" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S333" s="9" t="n">
+      <x:c r="S333" s="9" t="str">
         <x:v>5155683</x:v>
       </x:c>
       <x:c r="T333" s="10" t="str">
@@ -20848,7 +20920,7 @@
       <x:c r="R334" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S334" s="9" t="n">
+      <x:c r="S334" s="9" t="str">
         <x:v>5155688</x:v>
       </x:c>
       <x:c r="T334" s="10" t="str">
@@ -20909,7 +20981,7 @@
       <x:c r="R335" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S335" s="9" t="n">
+      <x:c r="S335" s="9" t="str">
         <x:v>5155689</x:v>
       </x:c>
       <x:c r="T335" s="10" t="str">
@@ -20970,7 +21042,7 @@
       <x:c r="R336" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S336" s="9" t="n">
+      <x:c r="S336" s="9" t="str">
         <x:v>5155691</x:v>
       </x:c>
       <x:c r="T336" s="10" t="str">
@@ -21031,7 +21103,7 @@
       <x:c r="R337" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S337" s="9" t="n">
+      <x:c r="S337" s="9" t="str">
         <x:v>5155695</x:v>
       </x:c>
       <x:c r="T337" s="10" t="str">
@@ -21092,7 +21164,7 @@
       <x:c r="R338" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S338" s="9" t="n">
+      <x:c r="S338" s="9" t="str">
         <x:v>5155703</x:v>
       </x:c>
       <x:c r="T338" s="10" t="str">
@@ -21153,7 +21225,7 @@
       <x:c r="R339" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S339" s="9" t="n">
+      <x:c r="S339" s="9" t="str">
         <x:v>5377722</x:v>
       </x:c>
       <x:c r="T339" s="10" t="str">
@@ -21214,7 +21286,7 @@
       <x:c r="R340" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S340" s="9" t="n">
+      <x:c r="S340" s="9" t="str">
         <x:v>5377745</x:v>
       </x:c>
       <x:c r="T340" s="10" t="str">
@@ -21275,7 +21347,7 @@
       <x:c r="R341" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S341" s="9" t="n">
+      <x:c r="S341" s="9" t="str">
         <x:v>5377811</x:v>
       </x:c>
       <x:c r="T341" s="10" t="str">
@@ -21336,7 +21408,7 @@
       <x:c r="R342" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S342" s="9" t="n">
+      <x:c r="S342" s="9" t="str">
         <x:v>5151559</x:v>
       </x:c>
       <x:c r="T342" s="10" t="str">
@@ -21397,7 +21469,7 @@
       <x:c r="R343" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S343" s="9" t="n">
+      <x:c r="S343" s="9" t="str">
         <x:v>5155657</x:v>
       </x:c>
       <x:c r="T343" s="10" t="str">
@@ -21459,7 +21531,7 @@
       <x:c r="R344" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S344" s="9" t="n">
+      <x:c r="S344" s="9" t="str">
         <x:v>5155664</x:v>
       </x:c>
       <x:c r="T344" s="10" t="str">
@@ -21523,7 +21595,7 @@
       <x:c r="R345" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S345" s="9" t="n">
+      <x:c r="S345" s="9" t="str">
         <x:v>5155713</x:v>
       </x:c>
       <x:c r="T345" s="10" t="str">
@@ -21584,7 +21656,7 @@
       <x:c r="R346" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S346" s="9" t="n">
+      <x:c r="S346" s="9" t="str">
         <x:v>5151146</x:v>
       </x:c>
       <x:c r="T346" s="10" t="str">
@@ -21645,7 +21717,7 @@
       <x:c r="R347" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S347" s="9" t="n">
+      <x:c r="S347" s="9" t="str">
         <x:v>5151445</x:v>
       </x:c>
       <x:c r="T347" s="10" t="str">
@@ -21706,7 +21778,7 @@
       <x:c r="R348" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S348" s="9" t="n">
+      <x:c r="S348" s="9" t="str">
         <x:v>5151526</x:v>
       </x:c>
       <x:c r="T348" s="10" t="str">
@@ -21769,7 +21841,7 @@
       <x:c r="R349" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S349" s="9" t="n">
+      <x:c r="S349" s="9" t="str">
         <x:v>5151645</x:v>
       </x:c>
       <x:c r="T349" s="10" t="str">
@@ -21830,7 +21902,7 @@
       <x:c r="R350" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S350" s="9" t="n">
+      <x:c r="S350" s="9" t="str">
         <x:v>5151885</x:v>
       </x:c>
       <x:c r="T350" s="10" t="str">
@@ -21891,7 +21963,7 @@
       <x:c r="R351" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S351" s="9" t="n">
+      <x:c r="S351" s="9" t="str">
         <x:v>5151896</x:v>
       </x:c>
       <x:c r="T351" s="10" t="str">
@@ -21952,7 +22024,7 @@
       <x:c r="R352" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S352" s="9" t="n">
+      <x:c r="S352" s="9" t="str">
         <x:v>5151984</x:v>
       </x:c>
       <x:c r="T352" s="10" t="str">
@@ -22013,7 +22085,7 @@
       <x:c r="R353" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S353" s="9" t="n">
+      <x:c r="S353" s="9" t="str">
         <x:v>5152025</x:v>
       </x:c>
       <x:c r="T353" s="10" t="str">
@@ -22074,7 +22146,7 @@
       <x:c r="R354" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S354" s="9" t="n">
+      <x:c r="S354" s="9" t="str">
         <x:v>5155643</x:v>
       </x:c>
       <x:c r="T354" s="10" t="str">
@@ -22135,7 +22207,7 @@
       <x:c r="R355" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S355" s="9" t="n">
+      <x:c r="S355" s="9" t="str">
         <x:v>5155650</x:v>
       </x:c>
       <x:c r="T355" s="10" t="str">
@@ -22196,7 +22268,7 @@
       <x:c r="R356" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S356" s="9" t="n">
+      <x:c r="S356" s="9" t="str">
         <x:v>5155651</x:v>
       </x:c>
       <x:c r="T356" s="10" t="str">
@@ -22260,7 +22332,7 @@
       <x:c r="R357" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S357" s="9" t="n">
+      <x:c r="S357" s="9" t="str">
         <x:v>5155653</x:v>
       </x:c>
       <x:c r="T357" s="10" t="str">
@@ -22321,7 +22393,7 @@
       <x:c r="R358" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S358" s="9" t="n">
+      <x:c r="S358" s="9" t="str">
         <x:v>5155656</x:v>
       </x:c>
       <x:c r="T358" s="10" t="str">
@@ -22382,7 +22454,7 @@
       <x:c r="R359" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S359" s="9" t="n">
+      <x:c r="S359" s="9" t="str">
         <x:v>5155660</x:v>
       </x:c>
       <x:c r="T359" s="10" t="str">
@@ -22443,7 +22515,7 @@
       <x:c r="R360" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S360" s="9" t="n">
+      <x:c r="S360" s="9" t="str">
         <x:v>5155663</x:v>
       </x:c>
       <x:c r="T360" s="10" t="str">
@@ -22504,7 +22576,7 @@
       <x:c r="R361" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S361" s="9" t="n">
+      <x:c r="S361" s="9" t="str">
         <x:v>5155670</x:v>
       </x:c>
       <x:c r="T361" s="10" t="str">
@@ -22565,7 +22637,7 @@
       <x:c r="R362" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S362" s="9" t="n">
+      <x:c r="S362" s="9" t="str">
         <x:v>5155671</x:v>
       </x:c>
       <x:c r="T362" s="10" t="str">
@@ -22626,7 +22698,7 @@
       <x:c r="R363" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S363" s="9" t="n">
+      <x:c r="S363" s="9" t="str">
         <x:v>5155674</x:v>
       </x:c>
       <x:c r="T363" s="10" t="str">
@@ -22687,7 +22759,7 @@
       <x:c r="R364" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S364" s="9" t="n">
+      <x:c r="S364" s="9" t="str">
         <x:v>5155677</x:v>
       </x:c>
       <x:c r="T364" s="10" t="str">
@@ -22748,7 +22820,7 @@
       <x:c r="R365" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S365" s="9" t="n">
+      <x:c r="S365" s="9" t="str">
         <x:v>5155680</x:v>
       </x:c>
       <x:c r="T365" s="10" t="str">
@@ -22812,7 +22884,7 @@
       <x:c r="R366" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S366" s="9" t="n">
+      <x:c r="S366" s="9" t="str">
         <x:v>5155681</x:v>
       </x:c>
       <x:c r="T366" s="10" t="str">
@@ -22873,7 +22945,7 @@
       <x:c r="R367" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S367" s="9" t="n">
+      <x:c r="S367" s="9" t="str">
         <x:v>5155682</x:v>
       </x:c>
       <x:c r="T367" s="10" t="str">
@@ -22934,7 +23006,7 @@
       <x:c r="R368" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S368" s="9" t="n">
+      <x:c r="S368" s="9" t="str">
         <x:v>5155690</x:v>
       </x:c>
       <x:c r="T368" s="10" t="str">
@@ -22995,7 +23067,7 @@
       <x:c r="R369" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S369" s="9" t="n">
+      <x:c r="S369" s="9" t="str">
         <x:v>5155692</x:v>
       </x:c>
       <x:c r="T369" s="10" t="str">
@@ -23056,7 +23128,7 @@
       <x:c r="R370" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S370" s="9" t="n">
+      <x:c r="S370" s="9" t="str">
         <x:v>5155693</x:v>
       </x:c>
       <x:c r="T370" s="10" t="str">
@@ -23117,7 +23189,7 @@
       <x:c r="R371" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S371" s="9" t="n">
+      <x:c r="S371" s="9" t="str">
         <x:v>5155694</x:v>
       </x:c>
       <x:c r="T371" s="10" t="str">
@@ -23178,7 +23250,7 @@
       <x:c r="R372" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S372" s="9" t="n">
+      <x:c r="S372" s="9" t="str">
         <x:v>5155698</x:v>
       </x:c>
       <x:c r="T372" s="10" t="str">
@@ -23239,7 +23311,7 @@
       <x:c r="R373" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S373" s="9" t="n">
+      <x:c r="S373" s="9" t="str">
         <x:v>5155699</x:v>
       </x:c>
       <x:c r="T373" s="10" t="str">
@@ -23300,7 +23372,7 @@
       <x:c r="R374" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S374" s="9" t="n">
+      <x:c r="S374" s="9" t="str">
         <x:v>5155708</x:v>
       </x:c>
       <x:c r="T374" s="10" t="str">
@@ -23361,7 +23433,7 @@
       <x:c r="R375" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S375" s="9" t="n">
+      <x:c r="S375" s="9" t="str">
         <x:v>5155709</x:v>
       </x:c>
       <x:c r="T375" s="10" t="str">
@@ -23422,7 +23494,7 @@
       <x:c r="R376" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S376" s="9" t="n">
+      <x:c r="S376" s="9" t="str">
         <x:v>5155711</x:v>
       </x:c>
       <x:c r="T376" s="10" t="str">
@@ -23486,7 +23558,7 @@
       <x:c r="R377" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S377" s="9" t="n">
+      <x:c r="S377" s="9" t="str">
         <x:v>5155712</x:v>
       </x:c>
       <x:c r="T377" s="10" t="str">
@@ -23547,7 +23619,7 @@
       <x:c r="R378" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S378" s="9" t="n">
+      <x:c r="S378" s="9" t="str">
         <x:v>5155714</x:v>
       </x:c>
       <x:c r="T378" s="10" t="str">
@@ -23609,7 +23681,7 @@
       <x:c r="R379" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S379" s="9" t="n">
+      <x:c r="S379" s="9" t="str">
         <x:v>5155715</x:v>
       </x:c>
       <x:c r="T379" s="10" t="str">
@@ -23685,7 +23757,7 @@
       <x:c r="R380" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S380" s="9" t="n">
+      <x:c r="S380" s="9" t="str">
         <x:v>5151211</x:v>
       </x:c>
       <x:c r="T380" s="10" t="str">
@@ -23749,7 +23821,7 @@
       <x:c r="R381" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S381" s="9" t="n">
+      <x:c r="S381" s="9" t="str">
         <x:v>5151704</x:v>
       </x:c>
       <x:c r="T381" s="10" t="str">
@@ -23813,7 +23885,7 @@
       <x:c r="R382" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S382" s="9" t="n">
+      <x:c r="S382" s="9" t="str">
         <x:v>5151951</x:v>
       </x:c>
       <x:c r="T382" s="10" t="str">
@@ -23877,7 +23949,7 @@
       <x:c r="R383" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S383" s="9" t="n">
+      <x:c r="S383" s="9" t="str">
         <x:v>5152068</x:v>
       </x:c>
       <x:c r="T383" s="10" t="str">
@@ -23945,7 +24017,7 @@
       <x:c r="R384" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S384" s="9" t="n">
+      <x:c r="S384" s="9" t="str">
         <x:v>5155718</x:v>
       </x:c>
       <x:c r="T384" s="10" t="str">
@@ -24011,7 +24083,7 @@
       <x:c r="R385" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S385" s="9" t="n">
+      <x:c r="S385" s="9" t="str">
         <x:v>5155722</x:v>
       </x:c>
       <x:c r="T385" s="10" t="str">
@@ -24075,7 +24147,7 @@
       <x:c r="R386" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S386" s="9" t="n">
+      <x:c r="S386" s="9" t="str">
         <x:v>5155726</x:v>
       </x:c>
       <x:c r="T386" s="10" t="str">
@@ -24139,7 +24211,7 @@
       <x:c r="R387" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S387" s="9" t="n">
+      <x:c r="S387" s="9" t="str">
         <x:v>5155730</x:v>
       </x:c>
       <x:c r="T387" s="10" t="str">
@@ -24203,7 +24275,7 @@
       <x:c r="R388" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S388" s="9" t="n">
+      <x:c r="S388" s="9" t="str">
         <x:v>5155731</x:v>
       </x:c>
       <x:c r="T388" s="10" t="str">
@@ -24267,7 +24339,7 @@
       <x:c r="R389" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S389" s="9" t="n">
+      <x:c r="S389" s="9" t="str">
         <x:v>5155733</x:v>
       </x:c>
       <x:c r="T389" s="10" t="str">
@@ -24332,7 +24404,7 @@
       <x:c r="R390" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S390" s="9" t="n">
+      <x:c r="S390" s="9" t="str">
         <x:v>5155745</x:v>
       </x:c>
       <x:c r="T390" s="10" t="str">
@@ -24396,7 +24468,7 @@
       <x:c r="R391" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S391" s="9" t="n">
+      <x:c r="S391" s="9" t="str">
         <x:v>5155748</x:v>
       </x:c>
       <x:c r="T391" s="10" t="str">
@@ -24460,7 +24532,7 @@
       <x:c r="R392" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S392" s="9" t="n">
+      <x:c r="S392" s="9" t="str">
         <x:v>5155750</x:v>
       </x:c>
       <x:c r="T392" s="10" t="str">
@@ -24524,7 +24596,7 @@
       <x:c r="R393" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S393" s="9" t="n">
+      <x:c r="S393" s="9" t="str">
         <x:v>5155754</x:v>
       </x:c>
       <x:c r="T393" s="10" t="str">
@@ -24588,7 +24660,7 @@
       <x:c r="R394" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S394" s="9" t="n">
+      <x:c r="S394" s="9" t="str">
         <x:v>5155755</x:v>
       </x:c>
       <x:c r="T394" s="10" t="str">
@@ -24652,7 +24724,7 @@
       <x:c r="R395" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S395" s="9" t="n">
+      <x:c r="S395" s="9" t="str">
         <x:v>5155757</x:v>
       </x:c>
       <x:c r="T395" s="10" t="str">
@@ -24716,7 +24788,7 @@
       <x:c r="R396" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S396" s="9" t="n">
+      <x:c r="S396" s="9" t="str">
         <x:v>5155759</x:v>
       </x:c>
       <x:c r="T396" s="10" t="str">
@@ -24784,7 +24856,7 @@
       <x:c r="R397" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S397" s="9" t="n">
+      <x:c r="S397" s="9" t="str">
         <x:v>5377638</x:v>
       </x:c>
       <x:c r="T397" s="10" t="str">
@@ -24848,7 +24920,7 @@
       <x:c r="R398" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S398" s="9" t="n">
+      <x:c r="S398" s="9" t="str">
         <x:v>5377695</x:v>
       </x:c>
       <x:c r="T398" s="10" t="str">
@@ -24912,7 +24984,7 @@
       <x:c r="R399" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S399" s="9" t="n">
+      <x:c r="S399" s="9" t="str">
         <x:v>5377701</x:v>
       </x:c>
       <x:c r="T399" s="10" t="str">
@@ -24976,7 +25048,7 @@
       <x:c r="R400" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S400" s="9" t="n">
+      <x:c r="S400" s="9" t="str">
         <x:v>5377765</x:v>
       </x:c>
       <x:c r="T400" s="10" t="str">
@@ -25040,7 +25112,7 @@
       <x:c r="R401" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S401" s="9" t="n">
+      <x:c r="S401" s="9" t="str">
         <x:v>5377773</x:v>
       </x:c>
       <x:c r="T401" s="10" t="str">
@@ -25104,7 +25176,7 @@
       <x:c r="R402" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S402" s="9" t="n">
+      <x:c r="S402" s="9" t="str">
         <x:v>5377822</x:v>
       </x:c>
       <x:c r="T402" s="10" t="str">
@@ -25168,7 +25240,7 @@
       <x:c r="R403" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S403" s="9" t="n">
+      <x:c r="S403" s="9" t="str">
         <x:v>5377826</x:v>
       </x:c>
       <x:c r="T403" s="10" t="str">
@@ -25233,7 +25305,7 @@
       <x:c r="R404" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S404" s="9" t="n">
+      <x:c r="S404" s="9" t="str">
         <x:v>5377828</x:v>
       </x:c>
       <x:c r="T404" s="10" t="str">
@@ -25297,7 +25369,7 @@
       <x:c r="R405" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S405" s="9" t="n">
+      <x:c r="S405" s="9" t="str">
         <x:v>5155721</x:v>
       </x:c>
       <x:c r="T405" s="10" t="str">
@@ -25361,7 +25433,7 @@
       <x:c r="R406" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S406" s="9" t="n">
+      <x:c r="S406" s="9" t="str">
         <x:v>5155728</x:v>
       </x:c>
       <x:c r="T406" s="10" t="str">
@@ -25425,7 +25497,7 @@
       <x:c r="R407" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S407" s="9" t="n">
+      <x:c r="S407" s="9" t="str">
         <x:v>5155744</x:v>
       </x:c>
       <x:c r="T407" s="10" t="str">
@@ -25492,7 +25564,7 @@
       <x:c r="R408" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S408" s="9" t="n">
+      <x:c r="S408" s="9" t="str">
         <x:v>5155751</x:v>
       </x:c>
       <x:c r="T408" s="10" t="str">
@@ -25556,7 +25628,7 @@
       <x:c r="R409" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S409" s="9" t="n">
+      <x:c r="S409" s="9" t="str">
         <x:v>5377636</x:v>
       </x:c>
       <x:c r="T409" s="10" t="str">
@@ -25620,7 +25692,7 @@
       <x:c r="R410" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S410" s="9" t="n">
+      <x:c r="S410" s="9" t="str">
         <x:v>5377825</x:v>
       </x:c>
       <x:c r="T410" s="10" t="str">
@@ -25684,7 +25756,7 @@
       <x:c r="R411" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S411" s="9" t="n">
+      <x:c r="S411" s="9" t="str">
         <x:v>5151470</x:v>
       </x:c>
       <x:c r="T411" s="10" t="str">
@@ -25749,7 +25821,7 @@
       <x:c r="R412" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S412" s="9" t="n">
+      <x:c r="S412" s="9" t="str">
         <x:v>5151471</x:v>
       </x:c>
       <x:c r="T412" s="10" t="str">
@@ -25813,7 +25885,7 @@
       <x:c r="R413" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S413" s="9" t="n">
+      <x:c r="S413" s="9" t="str">
         <x:v>5151586</x:v>
       </x:c>
       <x:c r="T413" s="10" t="str">
@@ -25880,7 +25952,7 @@
       <x:c r="R414" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S414" s="9" t="n">
+      <x:c r="S414" s="9" t="str">
         <x:v>5151590</x:v>
       </x:c>
       <x:c r="T414" s="10" t="str">
@@ -25945,7 +26017,7 @@
       <x:c r="R415" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S415" s="9" t="n">
+      <x:c r="S415" s="9" t="str">
         <x:v>5155716</x:v>
       </x:c>
       <x:c r="T415" s="10" t="str">
@@ -26009,7 +26081,7 @@
       <x:c r="R416" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S416" s="9" t="n">
+      <x:c r="S416" s="9" t="str">
         <x:v>5155717</x:v>
       </x:c>
       <x:c r="T416" s="10" t="str">
@@ -26074,7 +26146,7 @@
       <x:c r="R417" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S417" s="9" t="n">
+      <x:c r="S417" s="9" t="str">
         <x:v>5155719</x:v>
       </x:c>
       <x:c r="T417" s="10" t="str">
@@ -26138,7 +26210,7 @@
       <x:c r="R418" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S418" s="9" t="n">
+      <x:c r="S418" s="9" t="str">
         <x:v>5155720</x:v>
       </x:c>
       <x:c r="T418" s="10" t="str">
@@ -26202,7 +26274,7 @@
       <x:c r="R419" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S419" s="9" t="n">
+      <x:c r="S419" s="9" t="str">
         <x:v>5155725</x:v>
       </x:c>
       <x:c r="T419" s="10" t="str">
@@ -26266,7 +26338,7 @@
       <x:c r="R420" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S420" s="9" t="n">
+      <x:c r="S420" s="9" t="str">
         <x:v>5155727</x:v>
       </x:c>
       <x:c r="T420" s="10" t="str">
@@ -26336,7 +26408,7 @@
       <x:c r="R421" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S421" s="9" t="n">
+      <x:c r="S421" s="9" t="str">
         <x:v>5155729</x:v>
       </x:c>
       <x:c r="T421" s="10" t="str">
@@ -26401,7 +26473,7 @@
       <x:c r="R422" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S422" s="9" t="n">
+      <x:c r="S422" s="9" t="str">
         <x:v>5155732</x:v>
       </x:c>
       <x:c r="T422" s="10" t="str">
@@ -26465,7 +26537,7 @@
       <x:c r="R423" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S423" s="9" t="n">
+      <x:c r="S423" s="9" t="str">
         <x:v>5155734</x:v>
       </x:c>
       <x:c r="T423" s="10" t="str">
@@ -26529,7 +26601,7 @@
       <x:c r="R424" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S424" s="9" t="n">
+      <x:c r="S424" s="9" t="str">
         <x:v>5155736</x:v>
       </x:c>
       <x:c r="T424" s="10" t="str">
@@ -26594,7 +26666,7 @@
       <x:c r="R425" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S425" s="9" t="n">
+      <x:c r="S425" s="9" t="str">
         <x:v>5155737</x:v>
       </x:c>
       <x:c r="T425" s="10" t="str">
@@ -26664,7 +26736,7 @@
       <x:c r="R426" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S426" s="9" t="n">
+      <x:c r="S426" s="9" t="str">
         <x:v>5155739</x:v>
       </x:c>
       <x:c r="T426" s="10" t="str">
@@ -26728,7 +26800,7 @@
       <x:c r="R427" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S427" s="9" t="n">
+      <x:c r="S427" s="9" t="str">
         <x:v>5155740</x:v>
       </x:c>
       <x:c r="T427" s="10" t="str">
@@ -26794,7 +26866,7 @@
       <x:c r="R428" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S428" s="9" t="n">
+      <x:c r="S428" s="9" t="str">
         <x:v>5155741</x:v>
       </x:c>
       <x:c r="T428" s="10" t="str">
@@ -26858,7 +26930,7 @@
       <x:c r="R429" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S429" s="9" t="n">
+      <x:c r="S429" s="9" t="str">
         <x:v>5155747</x:v>
       </x:c>
       <x:c r="T429" s="10" t="str">
@@ -26922,7 +26994,7 @@
       <x:c r="R430" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S430" s="9" t="n">
+      <x:c r="S430" s="9" t="str">
         <x:v>5155749</x:v>
       </x:c>
       <x:c r="T430" s="10" t="str">
@@ -26986,7 +27058,7 @@
       <x:c r="R431" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S431" s="9" t="n">
+      <x:c r="S431" s="9" t="str">
         <x:v>5155752</x:v>
       </x:c>
       <x:c r="T431" s="10" t="str">
@@ -27055,7 +27127,7 @@
       <x:c r="R432" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S432" s="9" t="n">
+      <x:c r="S432" s="9" t="str">
         <x:v>5155753</x:v>
       </x:c>
       <x:c r="T432" s="10" t="str">
@@ -27119,7 +27191,7 @@
       <x:c r="R433" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S433" s="9" t="n">
+      <x:c r="S433" s="9" t="str">
         <x:v>5155756</x:v>
       </x:c>
       <x:c r="T433" s="10" t="str">
@@ -27188,7 +27260,7 @@
       <x:c r="R434" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S434" s="9" t="n">
+      <x:c r="S434" s="9" t="str">
         <x:v>5156161</x:v>
       </x:c>
       <x:c r="T434" s="10" t="str">
@@ -27252,7 +27324,7 @@
       <x:c r="R435" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S435" s="9" t="n">
+      <x:c r="S435" s="9" t="str">
         <x:v>5376379</x:v>
       </x:c>
       <x:c r="T435" s="10" t="str">
@@ -27316,7 +27388,7 @@
       <x:c r="R436" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S436" s="9" t="n">
+      <x:c r="S436" s="9" t="str">
         <x:v>5377831</x:v>
       </x:c>
       <x:c r="T436" s="10" t="str">
@@ -27371,7 +27443,7 @@
       <x:c r="R437" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S437" s="9" t="n">
+      <x:c r="S437" s="9" t="str">
         <x:v>5151495</x:v>
       </x:c>
       <x:c r="T437" s="10" t="str">
@@ -27426,7 +27498,7 @@
       <x:c r="R438" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S438" s="9" t="n">
+      <x:c r="S438" s="9" t="str">
         <x:v>5151611</x:v>
       </x:c>
       <x:c r="T438" s="10" t="str">
@@ -27481,7 +27553,7 @@
       <x:c r="R439" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S439" s="9" t="n">
+      <x:c r="S439" s="9" t="str">
         <x:v>5155762</x:v>
       </x:c>
       <x:c r="T439" s="10" t="str">
@@ -27536,7 +27608,7 @@
       <x:c r="R440" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S440" s="9" t="n">
+      <x:c r="S440" s="9" t="str">
         <x:v>5155765</x:v>
       </x:c>
       <x:c r="T440" s="10" t="str">
@@ -27591,7 +27663,7 @@
       <x:c r="R441" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S441" s="9" t="n">
+      <x:c r="S441" s="9" t="str">
         <x:v>5155766</x:v>
       </x:c>
       <x:c r="T441" s="10" t="str">
@@ -27646,7 +27718,7 @@
       <x:c r="R442" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S442" s="9" t="n">
+      <x:c r="S442" s="9" t="str">
         <x:v>5155768</x:v>
       </x:c>
       <x:c r="T442" s="10" t="str">
@@ -27701,7 +27773,7 @@
       <x:c r="R443" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S443" s="9" t="n">
+      <x:c r="S443" s="9" t="str">
         <x:v>5155769</x:v>
       </x:c>
       <x:c r="T443" s="10" t="str">
@@ -27756,7 +27828,7 @@
       <x:c r="R444" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S444" s="9" t="n">
+      <x:c r="S444" s="9" t="str">
         <x:v>5155770</x:v>
       </x:c>
       <x:c r="T444" s="10" t="str">
@@ -27811,7 +27883,7 @@
       <x:c r="R445" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S445" s="9" t="n">
+      <x:c r="S445" s="9" t="str">
         <x:v>5155773</x:v>
       </x:c>
       <x:c r="T445" s="10" t="str">
@@ -27866,7 +27938,7 @@
       <x:c r="R446" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S446" s="9" t="n">
+      <x:c r="S446" s="9" t="str">
         <x:v>5155774</x:v>
       </x:c>
       <x:c r="T446" s="10" t="str">
@@ -27921,7 +27993,7 @@
       <x:c r="R447" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S447" s="9" t="n">
+      <x:c r="S447" s="9" t="str">
         <x:v>5155776</x:v>
       </x:c>
       <x:c r="T447" s="10" t="str">
@@ -27976,7 +28048,7 @@
       <x:c r="R448" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S448" s="9" t="n">
+      <x:c r="S448" s="9" t="str">
         <x:v>5155777</x:v>
       </x:c>
       <x:c r="T448" s="10" t="str">
@@ -28031,7 +28103,7 @@
       <x:c r="R449" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S449" s="9" t="n">
+      <x:c r="S449" s="9" t="str">
         <x:v>5155783</x:v>
       </x:c>
       <x:c r="T449" s="10" t="str">
@@ -28086,7 +28158,7 @@
       <x:c r="R450" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S450" s="9" t="n">
+      <x:c r="S450" s="9" t="str">
         <x:v>5155790</x:v>
       </x:c>
       <x:c r="T450" s="10" t="str">
@@ -28141,7 +28213,7 @@
       <x:c r="R451" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S451" s="9" t="n">
+      <x:c r="S451" s="9" t="str">
         <x:v>5155794</x:v>
       </x:c>
       <x:c r="T451" s="10" t="str">
@@ -28196,7 +28268,7 @@
       <x:c r="R452" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S452" s="9" t="n">
+      <x:c r="S452" s="9" t="str">
         <x:v>5155795</x:v>
       </x:c>
       <x:c r="T452" s="10" t="str">
@@ -28251,7 +28323,7 @@
       <x:c r="R453" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S453" s="9" t="n">
+      <x:c r="S453" s="9" t="str">
         <x:v>5155796</x:v>
       </x:c>
       <x:c r="T453" s="10" t="str">
@@ -28306,7 +28378,7 @@
       <x:c r="R454" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S454" s="9" t="n">
+      <x:c r="S454" s="9" t="str">
         <x:v>5155797</x:v>
       </x:c>
       <x:c r="T454" s="10" t="str">
@@ -28361,7 +28433,7 @@
       <x:c r="R455" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S455" s="9" t="n">
+      <x:c r="S455" s="9" t="str">
         <x:v>5377705</x:v>
       </x:c>
       <x:c r="T455" s="10" t="str">
@@ -28416,7 +28488,7 @@
       <x:c r="R456" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S456" s="9" t="n">
+      <x:c r="S456" s="9" t="str">
         <x:v>5395211</x:v>
       </x:c>
       <x:c r="T456" s="10" t="str">
@@ -28471,7 +28543,7 @@
       <x:c r="R457" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S457" s="9" t="n">
+      <x:c r="S457" s="9" t="str">
         <x:v>5151843</x:v>
       </x:c>
       <x:c r="T457" s="10" t="str">
@@ -28526,7 +28598,7 @@
       <x:c r="R458" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S458" s="9" t="n">
+      <x:c r="S458" s="9" t="str">
         <x:v>5151965</x:v>
       </x:c>
       <x:c r="T458" s="10" t="str">
@@ -28581,7 +28653,7 @@
       <x:c r="R459" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S459" s="9" t="n">
+      <x:c r="S459" s="9" t="str">
         <x:v>5155761</x:v>
       </x:c>
       <x:c r="T459" s="10" t="str">
@@ -28636,7 +28708,7 @@
       <x:c r="R460" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S460" s="9" t="n">
+      <x:c r="S460" s="9" t="str">
         <x:v>5155763</x:v>
       </x:c>
       <x:c r="T460" s="10" t="str">
@@ -28691,7 +28763,7 @@
       <x:c r="R461" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S461" s="9" t="n">
+      <x:c r="S461" s="9" t="str">
         <x:v>5155767</x:v>
       </x:c>
       <x:c r="T461" s="10" t="str">
@@ -28746,7 +28818,7 @@
       <x:c r="R462" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S462" s="9" t="n">
+      <x:c r="S462" s="9" t="str">
         <x:v>5155775</x:v>
       </x:c>
       <x:c r="T462" s="10" t="str">
@@ -28801,7 +28873,7 @@
       <x:c r="R463" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S463" s="9" t="n">
+      <x:c r="S463" s="9" t="str">
         <x:v>5155778</x:v>
       </x:c>
       <x:c r="T463" s="10" t="str">
@@ -28856,7 +28928,7 @@
       <x:c r="R464" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S464" s="9" t="n">
+      <x:c r="S464" s="9" t="str">
         <x:v>5155779</x:v>
       </x:c>
       <x:c r="T464" s="10" t="str">
@@ -28911,7 +28983,7 @@
       <x:c r="R465" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S465" s="9" t="n">
+      <x:c r="S465" s="9" t="str">
         <x:v>5155780</x:v>
       </x:c>
       <x:c r="T465" s="10" t="str">
@@ -28966,7 +29038,7 @@
       <x:c r="R466" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S466" s="9" t="n">
+      <x:c r="S466" s="9" t="str">
         <x:v>5155781</x:v>
       </x:c>
       <x:c r="T466" s="10" t="str">
@@ -29021,7 +29093,7 @@
       <x:c r="R467" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S467" s="9" t="n">
+      <x:c r="S467" s="9" t="str">
         <x:v>5155782</x:v>
       </x:c>
       <x:c r="T467" s="10" t="str">
@@ -29076,7 +29148,7 @@
       <x:c r="R468" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S468" s="9" t="n">
+      <x:c r="S468" s="9" t="str">
         <x:v>5155784</x:v>
       </x:c>
       <x:c r="T468" s="10" t="str">
@@ -29131,7 +29203,7 @@
       <x:c r="R469" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S469" s="9" t="n">
+      <x:c r="S469" s="9" t="str">
         <x:v>5155786</x:v>
       </x:c>
       <x:c r="T469" s="10" t="str">
@@ -29186,7 +29258,7 @@
       <x:c r="R470" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S470" s="9" t="n">
+      <x:c r="S470" s="9" t="str">
         <x:v>5155787</x:v>
       </x:c>
       <x:c r="T470" s="10" t="str">
@@ -29241,7 +29313,7 @@
       <x:c r="R471" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S471" s="9" t="n">
+      <x:c r="S471" s="9" t="str">
         <x:v>5155788</x:v>
       </x:c>
       <x:c r="T471" s="10" t="str">
@@ -29296,7 +29368,7 @@
       <x:c r="R472" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S472" s="9" t="n">
+      <x:c r="S472" s="9" t="str">
         <x:v>5155789</x:v>
       </x:c>
       <x:c r="T472" s="10" t="str">
@@ -29351,7 +29423,7 @@
       <x:c r="R473" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S473" s="9" t="n">
+      <x:c r="S473" s="9" t="str">
         <x:v>5155791</x:v>
       </x:c>
       <x:c r="T473" s="10" t="str">
@@ -29406,7 +29478,7 @@
       <x:c r="R474" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S474" s="9" t="n">
+      <x:c r="S474" s="9" t="str">
         <x:v>5155792</x:v>
       </x:c>
       <x:c r="T474" s="10" t="str">
@@ -29461,7 +29533,7 @@
       <x:c r="R475" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S475" s="9" t="n">
+      <x:c r="S475" s="9" t="str">
         <x:v>5155793</x:v>
       </x:c>
       <x:c r="T475" s="10" t="str">
@@ -29516,7 +29588,7 @@
       <x:c r="R476" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S476" s="9" t="n">
+      <x:c r="S476" s="9" t="str">
         <x:v>5155798</x:v>
       </x:c>
       <x:c r="T476" s="10" t="str">
@@ -29571,7 +29643,7 @@
       <x:c r="R477" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S477" s="9" t="n">
+      <x:c r="S477" s="9" t="str">
         <x:v>5155799</x:v>
       </x:c>
       <x:c r="T477" s="10" t="str">
@@ -29626,7 +29698,7 @@
       <x:c r="R478" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S478" s="9" t="n">
+      <x:c r="S478" s="9" t="str">
         <x:v>5377790</x:v>
       </x:c>
       <x:c r="T478" s="10" t="str">
@@ -29681,7 +29753,7 @@
       <x:c r="R479" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S479" s="9" t="n">
+      <x:c r="S479" s="9" t="str">
         <x:v>5394929</x:v>
       </x:c>
       <x:c r="T479" s="10" t="str">
@@ -29736,7 +29808,7 @@
       <x:c r="R480" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S480" s="9" t="n">
+      <x:c r="S480" s="9" t="str">
         <x:v>5395339</x:v>
       </x:c>
       <x:c r="T480" s="10" t="str">
@@ -29791,7 +29863,7 @@
       <x:c r="R481" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S481" s="9" t="n">
+      <x:c r="S481" s="9" t="str">
         <x:v>5395342</x:v>
       </x:c>
       <x:c r="T481" s="10" t="str">
@@ -29852,7 +29924,7 @@
       <x:c r="R482" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S482" s="9" t="n">
+      <x:c r="S482" s="9" t="str">
         <x:v>5151412</x:v>
       </x:c>
       <x:c r="T482" s="10" t="str">
@@ -29913,7 +29985,7 @@
       <x:c r="R483" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S483" s="9" t="n">
+      <x:c r="S483" s="9" t="str">
         <x:v>5151438</x:v>
       </x:c>
       <x:c r="T483" s="10" t="str">
@@ -29974,7 +30046,7 @@
       <x:c r="R484" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S484" s="9" t="n">
+      <x:c r="S484" s="9" t="str">
         <x:v>5151693</x:v>
       </x:c>
       <x:c r="T484" s="10" t="str">
@@ -30039,7 +30111,7 @@
       <x:c r="R485" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S485" s="9" t="n">
+      <x:c r="S485" s="9" t="str">
         <x:v>5151764</x:v>
       </x:c>
       <x:c r="T485" s="10" t="str">
@@ -30100,7 +30172,7 @@
       <x:c r="R486" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S486" s="9" t="n">
+      <x:c r="S486" s="9" t="str">
         <x:v>5151810</x:v>
       </x:c>
       <x:c r="T486" s="10" t="str">
@@ -30161,7 +30233,7 @@
       <x:c r="R487" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S487" s="9" t="n">
+      <x:c r="S487" s="9" t="str">
         <x:v>5151877</x:v>
       </x:c>
       <x:c r="T487" s="10" t="str">
@@ -30222,7 +30294,7 @@
       <x:c r="R488" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S488" s="9" t="n">
+      <x:c r="S488" s="9" t="str">
         <x:v>5151988</x:v>
       </x:c>
       <x:c r="T488" s="10" t="str">
@@ -30283,7 +30355,7 @@
       <x:c r="R489" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S489" s="9" t="n">
+      <x:c r="S489" s="9" t="str">
         <x:v>5155804</x:v>
       </x:c>
       <x:c r="T489" s="10" t="str">
@@ -30344,7 +30416,7 @@
       <x:c r="R490" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S490" s="9" t="n">
+      <x:c r="S490" s="9" t="str">
         <x:v>5155807</x:v>
       </x:c>
       <x:c r="T490" s="10" t="str">
@@ -30408,7 +30480,7 @@
       <x:c r="R491" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S491" s="9" t="n">
+      <x:c r="S491" s="9" t="str">
         <x:v>5155808</x:v>
       </x:c>
       <x:c r="T491" s="10" t="str">
@@ -30469,7 +30541,7 @@
       <x:c r="R492" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S492" s="9" t="n">
+      <x:c r="S492" s="9" t="str">
         <x:v>5155817</x:v>
       </x:c>
       <x:c r="T492" s="10" t="str">
@@ -30530,7 +30602,7 @@
       <x:c r="R493" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S493" s="9" t="n">
+      <x:c r="S493" s="9" t="str">
         <x:v>5155819</x:v>
       </x:c>
       <x:c r="T493" s="10" t="str">
@@ -30594,7 +30666,7 @@
       <x:c r="R494" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S494" s="9" t="n">
+      <x:c r="S494" s="9" t="str">
         <x:v>5155820</x:v>
       </x:c>
       <x:c r="T494" s="10" t="str">
@@ -30655,7 +30727,7 @@
       <x:c r="R495" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S495" s="9" t="n">
+      <x:c r="S495" s="9" t="str">
         <x:v>5155824</x:v>
       </x:c>
       <x:c r="T495" s="10" t="str">
@@ -30716,7 +30788,7 @@
       <x:c r="R496" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S496" s="9" t="n">
+      <x:c r="S496" s="9" t="str">
         <x:v>5155825</x:v>
       </x:c>
       <x:c r="T496" s="10" t="str">
@@ -30777,7 +30849,7 @@
       <x:c r="R497" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S497" s="9" t="n">
+      <x:c r="S497" s="9" t="str">
         <x:v>5155836</x:v>
       </x:c>
       <x:c r="T497" s="10" t="str">
@@ -30838,7 +30910,7 @@
       <x:c r="R498" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S498" s="9" t="n">
+      <x:c r="S498" s="9" t="str">
         <x:v>5155840</x:v>
       </x:c>
       <x:c r="T498" s="10" t="str">
@@ -30899,7 +30971,7 @@
       <x:c r="R499" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S499" s="9" t="n">
+      <x:c r="S499" s="9" t="str">
         <x:v>5155842</x:v>
       </x:c>
       <x:c r="T499" s="10" t="str">
@@ -30960,7 +31032,7 @@
       <x:c r="R500" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S500" s="9" t="n">
+      <x:c r="S500" s="9" t="str">
         <x:v>5155844</x:v>
       </x:c>
       <x:c r="T500" s="10" t="str">
@@ -31021,7 +31093,7 @@
       <x:c r="R501" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S501" s="9" t="n">
+      <x:c r="S501" s="9" t="str">
         <x:v>5155845</x:v>
       </x:c>
       <x:c r="T501" s="10" t="str">
@@ -31082,7 +31154,7 @@
       <x:c r="R502" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S502" s="9" t="n">
+      <x:c r="S502" s="9" t="str">
         <x:v>5155856</x:v>
       </x:c>
       <x:c r="T502" s="10" t="str">
@@ -31147,7 +31219,7 @@
       <x:c r="R503" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S503" s="9" t="n">
+      <x:c r="S503" s="9" t="str">
         <x:v>5155858</x:v>
       </x:c>
       <x:c r="T503" s="10" t="str">
@@ -31208,7 +31280,7 @@
       <x:c r="R504" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S504" s="9" t="n">
+      <x:c r="S504" s="9" t="str">
         <x:v>5155862</x:v>
       </x:c>
       <x:c r="T504" s="10" t="str">
@@ -31269,7 +31341,7 @@
       <x:c r="R505" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S505" s="9" t="n">
+      <x:c r="S505" s="9" t="str">
         <x:v>5155866</x:v>
       </x:c>
       <x:c r="T505" s="10" t="str">
@@ -31330,7 +31402,7 @@
       <x:c r="R506" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S506" s="9" t="n">
+      <x:c r="S506" s="9" t="str">
         <x:v>5155871</x:v>
       </x:c>
       <x:c r="T506" s="10" t="str">
@@ -31391,7 +31463,7 @@
       <x:c r="R507" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S507" s="9" t="n">
+      <x:c r="S507" s="9" t="str">
         <x:v>5155873</x:v>
       </x:c>
       <x:c r="T507" s="10" t="str">
@@ -31452,7 +31524,7 @@
       <x:c r="R508" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S508" s="9" t="n">
+      <x:c r="S508" s="9" t="str">
         <x:v>5155875</x:v>
       </x:c>
       <x:c r="T508" s="10" t="str">
@@ -31513,7 +31585,7 @@
       <x:c r="R509" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S509" s="9" t="n">
+      <x:c r="S509" s="9" t="str">
         <x:v>5155880</x:v>
       </x:c>
       <x:c r="T509" s="10" t="str">
@@ -31577,7 +31649,7 @@
       <x:c r="R510" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S510" s="9" t="n">
+      <x:c r="S510" s="9" t="str">
         <x:v>5377880</x:v>
       </x:c>
       <x:c r="T510" s="10" t="str">
@@ -31639,7 +31711,7 @@
       <x:c r="R511" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S511" s="9" t="n">
+      <x:c r="S511" s="9" t="str">
         <x:v>5377887</x:v>
       </x:c>
       <x:c r="T511" s="10" t="str">
@@ -31700,7 +31772,7 @@
       <x:c r="R512" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S512" s="9" t="n">
+      <x:c r="S512" s="9" t="str">
         <x:v>5377953</x:v>
       </x:c>
       <x:c r="T512" s="10" t="str">
@@ -31761,7 +31833,7 @@
       <x:c r="R513" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S513" s="9" t="n">
+      <x:c r="S513" s="9" t="str">
         <x:v>5377962</x:v>
       </x:c>
       <x:c r="T513" s="10" t="str">
@@ -31822,7 +31894,7 @@
       <x:c r="R514" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S514" s="9" t="n">
+      <x:c r="S514" s="9" t="str">
         <x:v>5377973</x:v>
       </x:c>
       <x:c r="T514" s="10" t="str">
@@ -31883,7 +31955,7 @@
       <x:c r="R515" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S515" s="9" t="n">
+      <x:c r="S515" s="9" t="str">
         <x:v>5155867</x:v>
       </x:c>
       <x:c r="T515" s="10" t="str">
@@ -31944,7 +32016,7 @@
       <x:c r="R516" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S516" s="9" t="n">
+      <x:c r="S516" s="9" t="str">
         <x:v>5151405</x:v>
       </x:c>
       <x:c r="T516" s="10" t="str">
@@ -32005,7 +32077,7 @@
       <x:c r="R517" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S517" s="9" t="n">
+      <x:c r="S517" s="9" t="str">
         <x:v>5151521</x:v>
       </x:c>
       <x:c r="T517" s="10" t="str">
@@ -32067,7 +32139,7 @@
       <x:c r="R518" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S518" s="9" t="n">
+      <x:c r="S518" s="9" t="str">
         <x:v>5151562</x:v>
       </x:c>
       <x:c r="T518" s="10" t="str">
@@ -32136,7 +32208,7 @@
       <x:c r="R519" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S519" s="9" t="n">
+      <x:c r="S519" s="9" t="str">
         <x:v>5151736</x:v>
       </x:c>
       <x:c r="T519" s="10" t="str">
@@ -32197,7 +32269,7 @@
       <x:c r="R520" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S520" s="9" t="n">
+      <x:c r="S520" s="9" t="str">
         <x:v>5151765</x:v>
       </x:c>
       <x:c r="T520" s="10" t="str">
@@ -32258,7 +32330,7 @@
       <x:c r="R521" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S521" s="9" t="n">
+      <x:c r="S521" s="9" t="str">
         <x:v>5151767</x:v>
       </x:c>
       <x:c r="T521" s="10" t="str">
@@ -32319,7 +32391,7 @@
       <x:c r="R522" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S522" s="9" t="n">
+      <x:c r="S522" s="9" t="str">
         <x:v>5151873</x:v>
       </x:c>
       <x:c r="T522" s="10" t="str">
@@ -32380,7 +32452,7 @@
       <x:c r="R523" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S523" s="9" t="n">
+      <x:c r="S523" s="9" t="str">
         <x:v>5151910</x:v>
       </x:c>
       <x:c r="T523" s="10" t="str">
@@ -32441,7 +32513,7 @@
       <x:c r="R524" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S524" s="9" t="n">
+      <x:c r="S524" s="9" t="str">
         <x:v>5151991</x:v>
       </x:c>
       <x:c r="T524" s="10" t="str">
@@ -32502,7 +32574,7 @@
       <x:c r="R525" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S525" s="9" t="n">
+      <x:c r="S525" s="9" t="str">
         <x:v>5155801</x:v>
       </x:c>
       <x:c r="T525" s="10" t="str">
@@ -32563,7 +32635,7 @@
       <x:c r="R526" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S526" s="9" t="n">
+      <x:c r="S526" s="9" t="str">
         <x:v>5155813</x:v>
       </x:c>
       <x:c r="T526" s="10" t="str">
@@ -32624,7 +32696,7 @@
       <x:c r="R527" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S527" s="9" t="n">
+      <x:c r="S527" s="9" t="str">
         <x:v>5155829</x:v>
       </x:c>
       <x:c r="T527" s="10" t="str">
@@ -32685,7 +32757,7 @@
       <x:c r="R528" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S528" s="9" t="n">
+      <x:c r="S528" s="9" t="str">
         <x:v>5155832</x:v>
       </x:c>
       <x:c r="T528" s="10" t="str">
@@ -32748,7 +32820,7 @@
       <x:c r="R529" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S529" s="9" t="n">
+      <x:c r="S529" s="9" t="str">
         <x:v>5155835</x:v>
       </x:c>
       <x:c r="T529" s="10" t="str">
@@ -32809,7 +32881,7 @@
       <x:c r="R530" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S530" s="9" t="n">
+      <x:c r="S530" s="9" t="str">
         <x:v>5155837</x:v>
       </x:c>
       <x:c r="T530" s="10" t="str">
@@ -32870,7 +32942,7 @@
       <x:c r="R531" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S531" s="9" t="n">
+      <x:c r="S531" s="9" t="str">
         <x:v>5155838</x:v>
       </x:c>
       <x:c r="T531" s="10" t="str">
@@ -32931,7 +33003,7 @@
       <x:c r="R532" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S532" s="9" t="n">
+      <x:c r="S532" s="9" t="str">
         <x:v>5155847</x:v>
       </x:c>
       <x:c r="T532" s="10" t="str">
@@ -32992,7 +33064,7 @@
       <x:c r="R533" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S533" s="9" t="n">
+      <x:c r="S533" s="9" t="str">
         <x:v>5155848</x:v>
       </x:c>
       <x:c r="T533" s="10" t="str">
@@ -33053,7 +33125,7 @@
       <x:c r="R534" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S534" s="9" t="n">
+      <x:c r="S534" s="9" t="str">
         <x:v>5155849</x:v>
       </x:c>
       <x:c r="T534" s="10" t="str">
@@ -33114,7 +33186,7 @@
       <x:c r="R535" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S535" s="9" t="n">
+      <x:c r="S535" s="9" t="str">
         <x:v>5155850</x:v>
       </x:c>
       <x:c r="T535" s="10" t="str">
@@ -33175,7 +33247,7 @@
       <x:c r="R536" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S536" s="9" t="n">
+      <x:c r="S536" s="9" t="str">
         <x:v>5155854</x:v>
       </x:c>
       <x:c r="T536" s="10" t="str">
@@ -33236,7 +33308,7 @@
       <x:c r="R537" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S537" s="9" t="n">
+      <x:c r="S537" s="9" t="str">
         <x:v>5155860</x:v>
       </x:c>
       <x:c r="T537" s="10" t="str">
@@ -33297,7 +33369,7 @@
       <x:c r="R538" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S538" s="9" t="n">
+      <x:c r="S538" s="9" t="str">
         <x:v>5155863</x:v>
       </x:c>
       <x:c r="T538" s="10" t="str">
@@ -33358,7 +33430,7 @@
       <x:c r="R539" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S539" s="9" t="n">
+      <x:c r="S539" s="9" t="str">
         <x:v>5155876</x:v>
       </x:c>
       <x:c r="T539" s="10" t="str">
@@ -33419,7 +33491,7 @@
       <x:c r="R540" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S540" s="9" t="n">
+      <x:c r="S540" s="9" t="str">
         <x:v>5155877</x:v>
       </x:c>
       <x:c r="T540" s="10" t="str">
@@ -33480,7 +33552,7 @@
       <x:c r="R541" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S541" s="9" t="n">
+      <x:c r="S541" s="9" t="str">
         <x:v>5155879</x:v>
       </x:c>
       <x:c r="T541" s="10" t="str">
@@ -33541,7 +33613,7 @@
       <x:c r="R542" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S542" s="9" t="n">
+      <x:c r="S542" s="9" t="str">
         <x:v>5155881</x:v>
       </x:c>
       <x:c r="T542" s="10" t="str">
@@ -33605,7 +33677,7 @@
       <x:c r="R543" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S543" s="9" t="n">
+      <x:c r="S543" s="9" t="str">
         <x:v>5151707</x:v>
       </x:c>
       <x:c r="T543" s="10" t="str">
@@ -33671,7 +33743,7 @@
       <x:c r="R544" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S544" s="9" t="n">
+      <x:c r="S544" s="9" t="str">
         <x:v>5155888</x:v>
       </x:c>
       <x:c r="T544" s="10" t="str">
@@ -33735,7 +33807,7 @@
       <x:c r="R545" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S545" s="9" t="n">
+      <x:c r="S545" s="9" t="str">
         <x:v>5155896</x:v>
       </x:c>
       <x:c r="T545" s="10" t="str">
@@ -33799,7 +33871,7 @@
       <x:c r="R546" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S546" s="9" t="n">
+      <x:c r="S546" s="9" t="str">
         <x:v>5155897</x:v>
       </x:c>
       <x:c r="T546" s="10" t="str">
@@ -33864,7 +33936,7 @@
       <x:c r="R547" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S547" s="9" t="n">
+      <x:c r="S547" s="9" t="str">
         <x:v>5155900</x:v>
       </x:c>
       <x:c r="T547" s="10" t="str">
@@ -33928,7 +34000,7 @@
       <x:c r="R548" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S548" s="9" t="n">
+      <x:c r="S548" s="9" t="str">
         <x:v>5155903</x:v>
       </x:c>
       <x:c r="T548" s="10" t="str">
@@ -33992,7 +34064,7 @@
       <x:c r="R549" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S549" s="9" t="n">
+      <x:c r="S549" s="9" t="str">
         <x:v>5155904</x:v>
       </x:c>
       <x:c r="T549" s="10" t="str">
@@ -34056,7 +34128,7 @@
       <x:c r="R550" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S550" s="9" t="n">
+      <x:c r="S550" s="9" t="str">
         <x:v>5155905</x:v>
       </x:c>
       <x:c r="T550" s="10" t="str">
@@ -34124,7 +34196,7 @@
       <x:c r="R551" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S551" s="9" t="n">
+      <x:c r="S551" s="9" t="str">
         <x:v>5155912</x:v>
       </x:c>
       <x:c r="T551" s="10" t="str">
@@ -34188,7 +34260,7 @@
       <x:c r="R552" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S552" s="9" t="n">
+      <x:c r="S552" s="9" t="str">
         <x:v>5155916</x:v>
       </x:c>
       <x:c r="T552" s="10" t="str">
@@ -34252,7 +34324,7 @@
       <x:c r="R553" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S553" s="9" t="n">
+      <x:c r="S553" s="9" t="str">
         <x:v>5155919</x:v>
       </x:c>
       <x:c r="T553" s="10" t="str">
@@ -34320,7 +34392,7 @@
       <x:c r="R554" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S554" s="9" t="n">
+      <x:c r="S554" s="9" t="str">
         <x:v>5155921</x:v>
       </x:c>
       <x:c r="T554" s="10" t="str">
@@ -34384,7 +34456,7 @@
       <x:c r="R555" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S555" s="9" t="n">
+      <x:c r="S555" s="9" t="str">
         <x:v>5155922</x:v>
       </x:c>
       <x:c r="T555" s="10" t="str">
@@ -34448,7 +34520,7 @@
       <x:c r="R556" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S556" s="9" t="n">
+      <x:c r="S556" s="9" t="str">
         <x:v>5155923</x:v>
       </x:c>
       <x:c r="T556" s="10" t="str">
@@ -34512,7 +34584,7 @@
       <x:c r="R557" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S557" s="9" t="n">
+      <x:c r="S557" s="9" t="str">
         <x:v>5155927</x:v>
       </x:c>
       <x:c r="T557" s="10" t="str">
@@ -34576,7 +34648,7 @@
       <x:c r="R558" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S558" s="9" t="n">
+      <x:c r="S558" s="9" t="str">
         <x:v>5377901</x:v>
       </x:c>
       <x:c r="T558" s="10" t="str">
@@ -34640,7 +34712,7 @@
       <x:c r="R559" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S559" s="9" t="n">
+      <x:c r="S559" s="9" t="str">
         <x:v>5155920</x:v>
       </x:c>
       <x:c r="T559" s="10" t="str">
@@ -34704,7 +34776,7 @@
       <x:c r="R560" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S560" s="9" t="n">
+      <x:c r="S560" s="9" t="str">
         <x:v>5155928</x:v>
       </x:c>
       <x:c r="T560" s="10" t="str">
@@ -34768,7 +34840,7 @@
       <x:c r="R561" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S561" s="9" t="n">
+      <x:c r="S561" s="9" t="str">
         <x:v>5151821</x:v>
       </x:c>
       <x:c r="T561" s="10" t="str">
@@ -34832,7 +34904,7 @@
       <x:c r="R562" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S562" s="9" t="n">
+      <x:c r="S562" s="9" t="str">
         <x:v>5151954</x:v>
       </x:c>
       <x:c r="T562" s="10" t="str">
@@ -34896,7 +34968,7 @@
       <x:c r="R563" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S563" s="9" t="n">
+      <x:c r="S563" s="9" t="str">
         <x:v>5155884</x:v>
       </x:c>
       <x:c r="T563" s="10" t="str">
@@ -34960,7 +35032,7 @@
       <x:c r="R564" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S564" s="9" t="n">
+      <x:c r="S564" s="9" t="str">
         <x:v>5155885</x:v>
       </x:c>
       <x:c r="T564" s="10" t="str">
@@ -35024,7 +35096,7 @@
       <x:c r="R565" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S565" s="9" t="n">
+      <x:c r="S565" s="9" t="str">
         <x:v>5155886</x:v>
       </x:c>
       <x:c r="T565" s="10" t="str">
@@ -35092,7 +35164,7 @@
       <x:c r="R566" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S566" s="9" t="n">
+      <x:c r="S566" s="9" t="str">
         <x:v>5155887</x:v>
       </x:c>
       <x:c r="T566" s="10" t="str">
@@ -35156,7 +35228,7 @@
       <x:c r="R567" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S567" s="9" t="n">
+      <x:c r="S567" s="9" t="str">
         <x:v>5155893</x:v>
       </x:c>
       <x:c r="T567" s="10" t="str">
@@ -35220,7 +35292,7 @@
       <x:c r="R568" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S568" s="9" t="n">
+      <x:c r="S568" s="9" t="str">
         <x:v>5155895</x:v>
       </x:c>
       <x:c r="T568" s="10" t="str">
@@ -35284,7 +35356,7 @@
       <x:c r="R569" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S569" s="9" t="n">
+      <x:c r="S569" s="9" t="str">
         <x:v>5155898</x:v>
       </x:c>
       <x:c r="T569" s="10" t="str">
@@ -35348,7 +35420,7 @@
       <x:c r="R570" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S570" s="9" t="n">
+      <x:c r="S570" s="9" t="str">
         <x:v>5155899</x:v>
       </x:c>
       <x:c r="T570" s="10" t="str">
@@ -35412,7 +35484,7 @@
       <x:c r="R571" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S571" s="9" t="n">
+      <x:c r="S571" s="9" t="str">
         <x:v>5155902</x:v>
       </x:c>
       <x:c r="T571" s="10" t="str">
@@ -35476,7 +35548,7 @@
       <x:c r="R572" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S572" s="9" t="n">
+      <x:c r="S572" s="9" t="str">
         <x:v>5155906</x:v>
       </x:c>
       <x:c r="T572" s="10" t="str">
@@ -35540,7 +35612,7 @@
       <x:c r="R573" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S573" s="9" t="n">
+      <x:c r="S573" s="9" t="str">
         <x:v>5155907</x:v>
       </x:c>
       <x:c r="T573" s="10" t="str">
@@ -35604,7 +35676,7 @@
       <x:c r="R574" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S574" s="9" t="n">
+      <x:c r="S574" s="9" t="str">
         <x:v>5155908</x:v>
       </x:c>
       <x:c r="T574" s="10" t="str">
@@ -35668,7 +35740,7 @@
       <x:c r="R575" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S575" s="9" t="n">
+      <x:c r="S575" s="9" t="str">
         <x:v>5155910</x:v>
       </x:c>
       <x:c r="T575" s="10" t="str">
@@ -35732,7 +35804,7 @@
       <x:c r="R576" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S576" s="9" t="n">
+      <x:c r="S576" s="9" t="str">
         <x:v>5155914</x:v>
       </x:c>
       <x:c r="T576" s="10" t="str">
@@ -35796,7 +35868,7 @@
       <x:c r="R577" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S577" s="9" t="n">
+      <x:c r="S577" s="9" t="str">
         <x:v>5155915</x:v>
       </x:c>
       <x:c r="T577" s="10" t="str">
@@ -35860,7 +35932,7 @@
       <x:c r="R578" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S578" s="9" t="n">
+      <x:c r="S578" s="9" t="str">
         <x:v>5155917</x:v>
       </x:c>
       <x:c r="T578" s="10" t="str">
@@ -35924,7 +35996,7 @@
       <x:c r="R579" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S579" s="9" t="n">
+      <x:c r="S579" s="9" t="str">
         <x:v>5155924</x:v>
       </x:c>
       <x:c r="T579" s="10" t="str">
@@ -35991,7 +36063,7 @@
       <x:c r="R580" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S580" s="9" t="n">
+      <x:c r="S580" s="9" t="str">
         <x:v>5155925</x:v>
       </x:c>
       <x:c r="T580" s="10" t="str">
@@ -36055,7 +36127,7 @@
       <x:c r="R581" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S581" s="9" t="n">
+      <x:c r="S581" s="9" t="str">
         <x:v>5155926</x:v>
       </x:c>
       <x:c r="T581" s="10" t="str">
@@ -36119,7 +36191,7 @@
       <x:c r="R582" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S582" s="9" t="n">
+      <x:c r="S582" s="9" t="str">
         <x:v>5377905</x:v>
       </x:c>
       <x:c r="T582" s="10" t="str">
@@ -36183,7 +36255,7 @@
       <x:c r="R583" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S583" s="9" t="n">
+      <x:c r="S583" s="9" t="str">
         <x:v>5378090</x:v>
       </x:c>
       <x:c r="T583" s="10" t="str">
@@ -36238,7 +36310,7 @@
       <x:c r="R584" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S584" s="9" t="n">
+      <x:c r="S584" s="9" t="str">
         <x:v>5151727</x:v>
       </x:c>
       <x:c r="T584" s="10" t="str">
@@ -36293,7 +36365,7 @@
       <x:c r="R585" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S585" s="9" t="n">
+      <x:c r="S585" s="9" t="str">
         <x:v>5155930</x:v>
       </x:c>
       <x:c r="T585" s="10" t="str">
@@ -36348,7 +36420,7 @@
       <x:c r="R586" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S586" s="9" t="n">
+      <x:c r="S586" s="9" t="str">
         <x:v>5155933</x:v>
       </x:c>
       <x:c r="T586" s="10" t="str">
@@ -36403,7 +36475,7 @@
       <x:c r="R587" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S587" s="9" t="n">
+      <x:c r="S587" s="9" t="str">
         <x:v>5155934</x:v>
       </x:c>
       <x:c r="T587" s="10" t="str">
@@ -36458,7 +36530,7 @@
       <x:c r="R588" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S588" s="9" t="n">
+      <x:c r="S588" s="9" t="str">
         <x:v>5155940</x:v>
       </x:c>
       <x:c r="T588" s="10" t="str">
@@ -36513,7 +36585,7 @@
       <x:c r="R589" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S589" s="9" t="n">
+      <x:c r="S589" s="9" t="str">
         <x:v>5155943</x:v>
       </x:c>
       <x:c r="T589" s="10" t="str">
@@ -36568,7 +36640,7 @@
       <x:c r="R590" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S590" s="9" t="n">
+      <x:c r="S590" s="9" t="str">
         <x:v>5155946</x:v>
       </x:c>
       <x:c r="T590" s="10" t="str">
@@ -36627,7 +36699,7 @@
       <x:c r="R591" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S591" s="9" t="n">
+      <x:c r="S591" s="9" t="str">
         <x:v>5155947</x:v>
       </x:c>
       <x:c r="T591" s="10" t="str">
@@ -36682,7 +36754,7 @@
       <x:c r="R592" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S592" s="9" t="n">
+      <x:c r="S592" s="9" t="str">
         <x:v>5155948</x:v>
       </x:c>
       <x:c r="T592" s="10" t="str">
@@ -36737,7 +36809,7 @@
       <x:c r="R593" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S593" s="9" t="n">
+      <x:c r="S593" s="9" t="str">
         <x:v>5155955</x:v>
       </x:c>
       <x:c r="T593" s="10" t="str">
@@ -36792,7 +36864,7 @@
       <x:c r="R594" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S594" s="9" t="n">
+      <x:c r="S594" s="9" t="str">
         <x:v>5155959</x:v>
       </x:c>
       <x:c r="T594" s="10" t="str">
@@ -36847,7 +36919,7 @@
       <x:c r="R595" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S595" s="9" t="n">
+      <x:c r="S595" s="9" t="str">
         <x:v>5155962</x:v>
       </x:c>
       <x:c r="T595" s="10" t="str">
@@ -36902,7 +36974,7 @@
       <x:c r="R596" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S596" s="9" t="n">
+      <x:c r="S596" s="9" t="str">
         <x:v>5155966</x:v>
       </x:c>
       <x:c r="T596" s="10" t="str">
@@ -36957,7 +37029,7 @@
       <x:c r="R597" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S597" s="9" t="n">
+      <x:c r="S597" s="9" t="str">
         <x:v>5155968</x:v>
       </x:c>
       <x:c r="T597" s="10" t="str">
@@ -37012,7 +37084,7 @@
       <x:c r="R598" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S598" s="9" t="n">
+      <x:c r="S598" s="9" t="str">
         <x:v>5155969</x:v>
       </x:c>
       <x:c r="T598" s="10" t="str">
@@ -37067,7 +37139,7 @@
       <x:c r="R599" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S599" s="9" t="n">
+      <x:c r="S599" s="9" t="str">
         <x:v>5155975</x:v>
       </x:c>
       <x:c r="T599" s="10" t="str">
@@ -37122,7 +37194,7 @@
       <x:c r="R600" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S600" s="9" t="n">
+      <x:c r="S600" s="9" t="str">
         <x:v>5377927</x:v>
       </x:c>
       <x:c r="T600" s="10" t="str">
@@ -37177,7 +37249,7 @@
       <x:c r="R601" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S601" s="9" t="n">
+      <x:c r="S601" s="9" t="str">
         <x:v>5377932</x:v>
       </x:c>
       <x:c r="T601" s="10" t="str">
@@ -37232,7 +37304,7 @@
       <x:c r="R602" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S602" s="9" t="n">
+      <x:c r="S602" s="9" t="str">
         <x:v>5377933</x:v>
       </x:c>
       <x:c r="T602" s="10" t="str">
@@ -37287,7 +37359,7 @@
       <x:c r="R603" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S603" s="9" t="n">
+      <x:c r="S603" s="9" t="str">
         <x:v>5377934</x:v>
       </x:c>
       <x:c r="T603" s="10" t="str">
@@ -37342,7 +37414,7 @@
       <x:c r="R604" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S604" s="9" t="n">
+      <x:c r="S604" s="9" t="str">
         <x:v>5377937</x:v>
       </x:c>
       <x:c r="T604" s="10" t="str">
@@ -37397,7 +37469,7 @@
       <x:c r="R605" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S605" s="9" t="n">
+      <x:c r="S605" s="9" t="str">
         <x:v>5395058</x:v>
       </x:c>
       <x:c r="T605" s="10" t="str">
@@ -37452,7 +37524,7 @@
       <x:c r="R606" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S606" s="9" t="n">
+      <x:c r="S606" s="9" t="str">
         <x:v>5395063</x:v>
       </x:c>
       <x:c r="T606" s="10" t="str">
@@ -37507,7 +37579,7 @@
       <x:c r="R607" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S607" s="9" t="n">
+      <x:c r="S607" s="9" t="str">
         <x:v>5155938</x:v>
       </x:c>
       <x:c r="T607" s="10" t="str">
@@ -37562,7 +37634,7 @@
       <x:c r="R608" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S608" s="9" t="n">
+      <x:c r="S608" s="9" t="str">
         <x:v>5155951</x:v>
       </x:c>
       <x:c r="T608" s="10" t="str">
@@ -37617,7 +37689,7 @@
       <x:c r="R609" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S609" s="9" t="n">
+      <x:c r="S609" s="9" t="str">
         <x:v>5155956</x:v>
       </x:c>
       <x:c r="T609" s="10" t="str">
@@ -37672,7 +37744,7 @@
       <x:c r="R610" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S610" s="9" t="n">
+      <x:c r="S610" s="9" t="str">
         <x:v>5155967</x:v>
       </x:c>
       <x:c r="T610" s="10" t="str">
@@ -37727,7 +37799,7 @@
       <x:c r="R611" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S611" s="9" t="n">
+      <x:c r="S611" s="9" t="str">
         <x:v>5151613</x:v>
       </x:c>
       <x:c r="T611" s="10" t="str">
@@ -37782,7 +37854,7 @@
       <x:c r="R612" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S612" s="9" t="n">
+      <x:c r="S612" s="9" t="str">
         <x:v>5155931</x:v>
       </x:c>
       <x:c r="T612" s="10" t="str">
@@ -37837,7 +37909,7 @@
       <x:c r="R613" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S613" s="9" t="n">
+      <x:c r="S613" s="9" t="str">
         <x:v>5155932</x:v>
       </x:c>
       <x:c r="T613" s="10" t="str">
@@ -37892,7 +37964,7 @@
       <x:c r="R614" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S614" s="9" t="n">
+      <x:c r="S614" s="9" t="str">
         <x:v>5155936</x:v>
       </x:c>
       <x:c r="T614" s="10" t="str">
@@ -37947,7 +38019,7 @@
       <x:c r="R615" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S615" s="9" t="n">
+      <x:c r="S615" s="9" t="str">
         <x:v>5155939</x:v>
       </x:c>
       <x:c r="T615" s="10" t="str">
@@ -38002,7 +38074,7 @@
       <x:c r="R616" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S616" s="9" t="n">
+      <x:c r="S616" s="9" t="str">
         <x:v>5155942</x:v>
       </x:c>
       <x:c r="T616" s="10" t="str">
@@ -38057,7 +38129,7 @@
       <x:c r="R617" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S617" s="9" t="n">
+      <x:c r="S617" s="9" t="str">
         <x:v>5155945</x:v>
       </x:c>
       <x:c r="T617" s="10" t="str">
@@ -38112,7 +38184,7 @@
       <x:c r="R618" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S618" s="9" t="n">
+      <x:c r="S618" s="9" t="str">
         <x:v>5155949</x:v>
       </x:c>
       <x:c r="T618" s="10" t="str">
@@ -38167,7 +38239,7 @@
       <x:c r="R619" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S619" s="9" t="n">
+      <x:c r="S619" s="9" t="str">
         <x:v>5155950</x:v>
       </x:c>
       <x:c r="T619" s="10" t="str">
@@ -38222,7 +38294,7 @@
       <x:c r="R620" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S620" s="9" t="n">
+      <x:c r="S620" s="9" t="str">
         <x:v>5155953</x:v>
       </x:c>
       <x:c r="T620" s="10" t="str">
@@ -38277,7 +38349,7 @@
       <x:c r="R621" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S621" s="9" t="n">
+      <x:c r="S621" s="9" t="str">
         <x:v>5155957</x:v>
       </x:c>
       <x:c r="T621" s="10" t="str">
@@ -38332,7 +38404,7 @@
       <x:c r="R622" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S622" s="9" t="n">
+      <x:c r="S622" s="9" t="str">
         <x:v>5155958</x:v>
       </x:c>
       <x:c r="T622" s="10" t="str">
@@ -38387,7 +38459,7 @@
       <x:c r="R623" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S623" s="9" t="n">
+      <x:c r="S623" s="9" t="str">
         <x:v>5155961</x:v>
       </x:c>
       <x:c r="T623" s="10" t="str">
@@ -38442,7 +38514,7 @@
       <x:c r="R624" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S624" s="9" t="n">
+      <x:c r="S624" s="9" t="str">
         <x:v>5155963</x:v>
       </x:c>
       <x:c r="T624" s="10" t="str">
@@ -38497,7 +38569,7 @@
       <x:c r="R625" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S625" s="9" t="n">
+      <x:c r="S625" s="9" t="str">
         <x:v>5155964</x:v>
       </x:c>
       <x:c r="T625" s="10" t="str">
@@ -38552,7 +38624,7 @@
       <x:c r="R626" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S626" s="9" t="n">
+      <x:c r="S626" s="9" t="str">
         <x:v>5155965</x:v>
       </x:c>
       <x:c r="T626" s="10" t="str">
@@ -38607,7 +38679,7 @@
       <x:c r="R627" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S627" s="9" t="n">
+      <x:c r="S627" s="9" t="str">
         <x:v>5155970</x:v>
       </x:c>
       <x:c r="T627" s="10" t="str">
@@ -38662,7 +38734,7 @@
       <x:c r="R628" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S628" s="9" t="n">
+      <x:c r="S628" s="9" t="str">
         <x:v>5155971</x:v>
       </x:c>
       <x:c r="T628" s="10" t="str">
@@ -38717,7 +38789,7 @@
       <x:c r="R629" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S629" s="9" t="n">
+      <x:c r="S629" s="9" t="str">
         <x:v>5155972</x:v>
       </x:c>
       <x:c r="T629" s="10" t="str">
@@ -38772,7 +38844,7 @@
       <x:c r="R630" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S630" s="9" t="n">
+      <x:c r="S630" s="9" t="str">
         <x:v>5155973</x:v>
       </x:c>
       <x:c r="T630" s="10" t="str">
@@ -38827,7 +38899,7 @@
       <x:c r="R631" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S631" s="9" t="n">
+      <x:c r="S631" s="9" t="str">
         <x:v>5155974</x:v>
       </x:c>
       <x:c r="T631" s="10" t="str">
@@ -38882,7 +38954,7 @@
       <x:c r="R632" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S632" s="9" t="n">
+      <x:c r="S632" s="9" t="str">
         <x:v>5377918</x:v>
       </x:c>
       <x:c r="T632" s="10" t="str">
@@ -38937,7 +39009,7 @@
       <x:c r="R633" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S633" s="9" t="n">
+      <x:c r="S633" s="9" t="str">
         <x:v>5377926</x:v>
       </x:c>
       <x:c r="T633" s="10" t="str">
@@ -38992,7 +39064,7 @@
       <x:c r="R634" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S634" s="9" t="n">
+      <x:c r="S634" s="9" t="str">
         <x:v>5378020</x:v>
       </x:c>
       <x:c r="T634" s="10" t="str">
@@ -39047,7 +39119,7 @@
       <x:c r="R635" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S635" s="9" t="n">
+      <x:c r="S635" s="9" t="str">
         <x:v>5378036</x:v>
       </x:c>
       <x:c r="T635" s="10" t="str">
@@ -39102,7 +39174,7 @@
       <x:c r="R636" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S636" s="9" t="n">
+      <x:c r="S636" s="9" t="str">
         <x:v>5394931</x:v>
       </x:c>
       <x:c r="T636" s="10" t="str">
@@ -39157,7 +39229,7 @@
       <x:c r="R637" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S637" s="9" t="n">
+      <x:c r="S637" s="9" t="str">
         <x:v>5395198</x:v>
       </x:c>
       <x:c r="T637" s="10" t="str">
@@ -39212,7 +39284,7 @@
       <x:c r="R638" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S638" s="9" t="n">
+      <x:c r="S638" s="9" t="str">
         <x:v>5418539</x:v>
       </x:c>
       <x:c r="T638" s="10" t="str">
@@ -39267,7 +39339,7 @@
       <x:c r="R639" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S639" s="9" t="n">
+      <x:c r="S639" s="9" t="str">
         <x:v>5418685</x:v>
       </x:c>
       <x:c r="T639" s="10" t="str">
@@ -39328,7 +39400,7 @@
       <x:c r="R640" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S640" s="9" t="n">
+      <x:c r="S640" s="9" t="str">
         <x:v>5151128</x:v>
       </x:c>
       <x:c r="T640" s="10" t="str">
@@ -39389,7 +39461,7 @@
       <x:c r="R641" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S641" s="9" t="n">
+      <x:c r="S641" s="9" t="str">
         <x:v>5151186</x:v>
       </x:c>
       <x:c r="T641" s="10" t="str">
@@ -39450,7 +39522,7 @@
       <x:c r="R642" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S642" s="9" t="n">
+      <x:c r="S642" s="9" t="str">
         <x:v>5151661</x:v>
       </x:c>
       <x:c r="T642" s="10" t="str">
@@ -39512,7 +39584,7 @@
       <x:c r="R643" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S643" s="9" t="n">
+      <x:c r="S643" s="9" t="str">
         <x:v>5151893</x:v>
       </x:c>
       <x:c r="T643" s="10" t="str">
@@ -39573,7 +39645,7 @@
       <x:c r="R644" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S644" s="9" t="n">
+      <x:c r="S644" s="9" t="str">
         <x:v>5152034</x:v>
       </x:c>
       <x:c r="T644" s="10" t="str">
@@ -39634,7 +39706,7 @@
       <x:c r="R645" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S645" s="9" t="n">
+      <x:c r="S645" s="9" t="str">
         <x:v>5155983</x:v>
       </x:c>
       <x:c r="T645" s="10" t="str">
@@ -39699,7 +39771,7 @@
       <x:c r="R646" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S646" s="9" t="n">
+      <x:c r="S646" s="9" t="str">
         <x:v>5155986</x:v>
       </x:c>
       <x:c r="T646" s="10" t="str">
@@ -39760,7 +39832,7 @@
       <x:c r="R647" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S647" s="9" t="n">
+      <x:c r="S647" s="9" t="str">
         <x:v>5155990</x:v>
       </x:c>
       <x:c r="T647" s="10" t="str">
@@ -39821,7 +39893,7 @@
       <x:c r="R648" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S648" s="9" t="n">
+      <x:c r="S648" s="9" t="str">
         <x:v>5155996</x:v>
       </x:c>
       <x:c r="T648" s="10" t="str">
@@ -39882,7 +39954,7 @@
       <x:c r="R649" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S649" s="9" t="n">
+      <x:c r="S649" s="9" t="str">
         <x:v>5155997</x:v>
       </x:c>
       <x:c r="T649" s="10" t="str">
@@ -39943,7 +40015,7 @@
       <x:c r="R650" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S650" s="9" t="n">
+      <x:c r="S650" s="9" t="str">
         <x:v>5156005</x:v>
       </x:c>
       <x:c r="T650" s="10" t="str">
@@ -40004,7 +40076,7 @@
       <x:c r="R651" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S651" s="9" t="n">
+      <x:c r="S651" s="9" t="str">
         <x:v>5156008</x:v>
       </x:c>
       <x:c r="T651" s="10" t="str">
@@ -40065,7 +40137,7 @@
       <x:c r="R652" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S652" s="9" t="n">
+      <x:c r="S652" s="9" t="str">
         <x:v>5156014</x:v>
       </x:c>
       <x:c r="T652" s="10" t="str">
@@ -40126,7 +40198,7 @@
       <x:c r="R653" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S653" s="9" t="n">
+      <x:c r="S653" s="9" t="str">
         <x:v>5156015</x:v>
       </x:c>
       <x:c r="T653" s="10" t="str">
@@ -40187,7 +40259,7 @@
       <x:c r="R654" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S654" s="9" t="n">
+      <x:c r="S654" s="9" t="str">
         <x:v>5156019</x:v>
       </x:c>
       <x:c r="T654" s="10" t="str">
@@ -40251,7 +40323,7 @@
       <x:c r="R655" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S655" s="9" t="n">
+      <x:c r="S655" s="9" t="str">
         <x:v>5156020</x:v>
       </x:c>
       <x:c r="T655" s="10" t="str">
@@ -40312,7 +40384,7 @@
       <x:c r="R656" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S656" s="9" t="n">
+      <x:c r="S656" s="9" t="str">
         <x:v>5156022</x:v>
       </x:c>
       <x:c r="T656" s="10" t="str">
@@ -40373,7 +40445,7 @@
       <x:c r="R657" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S657" s="9" t="n">
+      <x:c r="S657" s="9" t="str">
         <x:v>5156023</x:v>
       </x:c>
       <x:c r="T657" s="10" t="str">
@@ -40434,7 +40506,7 @@
       <x:c r="R658" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S658" s="9" t="n">
+      <x:c r="S658" s="9" t="str">
         <x:v>5378073</x:v>
       </x:c>
       <x:c r="T658" s="10" t="str">
@@ -40496,7 +40568,7 @@
       <x:c r="R659" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S659" s="9" t="n">
+      <x:c r="S659" s="9" t="str">
         <x:v>5378141</x:v>
       </x:c>
       <x:c r="T659" s="10" t="str">
@@ -40557,7 +40629,7 @@
       <x:c r="R660" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S660" s="9" t="n">
+      <x:c r="S660" s="9" t="str">
         <x:v>5378154</x:v>
       </x:c>
       <x:c r="T660" s="10" t="str">
@@ -40618,7 +40690,7 @@
       <x:c r="R661" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S661" s="9" t="n">
+      <x:c r="S661" s="9" t="str">
         <x:v>5155370</x:v>
       </x:c>
       <x:c r="T661" s="10" t="str">
@@ -40679,7 +40751,7 @@
       <x:c r="R662" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S662" s="9" t="n">
+      <x:c r="S662" s="9" t="str">
         <x:v>5156001</x:v>
       </x:c>
       <x:c r="T662" s="10" t="str">
@@ -40740,7 +40812,7 @@
       <x:c r="R663" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S663" s="9" t="n">
+      <x:c r="S663" s="9" t="str">
         <x:v>5156007</x:v>
       </x:c>
       <x:c r="T663" s="10" t="str">
@@ -40801,7 +40873,7 @@
       <x:c r="R664" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S664" s="9" t="n">
+      <x:c r="S664" s="9" t="str">
         <x:v>5156033</x:v>
       </x:c>
       <x:c r="T664" s="10" t="str">
@@ -40862,7 +40934,7 @@
       <x:c r="R665" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S665" s="9" t="n">
+      <x:c r="S665" s="9" t="str">
         <x:v>5151579</x:v>
       </x:c>
       <x:c r="T665" s="10" t="str">
@@ -40930,7 +41002,7 @@
       <x:c r="R666" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S666" s="9" t="n">
+      <x:c r="S666" s="9" t="str">
         <x:v>5151658</x:v>
       </x:c>
       <x:c r="T666" s="10" t="str">
@@ -40991,7 +41063,7 @@
       <x:c r="R667" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S667" s="9" t="n">
+      <x:c r="S667" s="9" t="str">
         <x:v>5151999</x:v>
       </x:c>
       <x:c r="T667" s="10" t="str">
@@ -41052,7 +41124,7 @@
       <x:c r="R668" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S668" s="9" t="n">
+      <x:c r="S668" s="9" t="str">
         <x:v>5152036</x:v>
       </x:c>
       <x:c r="T668" s="10" t="str">
@@ -41113,7 +41185,7 @@
       <x:c r="R669" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S669" s="9" t="n">
+      <x:c r="S669" s="9" t="str">
         <x:v>5155980</x:v>
       </x:c>
       <x:c r="T669" s="10" t="str">
@@ -41174,7 +41246,7 @@
       <x:c r="R670" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S670" s="9" t="n">
+      <x:c r="S670" s="9" t="str">
         <x:v>5155981</x:v>
       </x:c>
       <x:c r="T670" s="10" t="str">
@@ -41235,7 +41307,7 @@
       <x:c r="R671" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S671" s="9" t="n">
+      <x:c r="S671" s="9" t="str">
         <x:v>5155985</x:v>
       </x:c>
       <x:c r="T671" s="10" t="str">
@@ -41296,7 +41368,7 @@
       <x:c r="R672" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S672" s="9" t="n">
+      <x:c r="S672" s="9" t="str">
         <x:v>5155987</x:v>
       </x:c>
       <x:c r="T672" s="10" t="str">
@@ -41357,7 +41429,7 @@
       <x:c r="R673" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S673" s="9" t="n">
+      <x:c r="S673" s="9" t="str">
         <x:v>5155988</x:v>
       </x:c>
       <x:c r="T673" s="10" t="str">
@@ -41418,7 +41490,7 @@
       <x:c r="R674" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S674" s="9" t="n">
+      <x:c r="S674" s="9" t="str">
         <x:v>5155993</x:v>
       </x:c>
       <x:c r="T674" s="10" t="str">
@@ -41479,7 +41551,7 @@
       <x:c r="R675" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S675" s="9" t="n">
+      <x:c r="S675" s="9" t="str">
         <x:v>5155994</x:v>
       </x:c>
       <x:c r="T675" s="10" t="str">
@@ -41540,7 +41612,7 @@
       <x:c r="R676" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S676" s="9" t="n">
+      <x:c r="S676" s="9" t="str">
         <x:v>5155995</x:v>
       </x:c>
       <x:c r="T676" s="10" t="str">
@@ -41601,7 +41673,7 @@
       <x:c r="R677" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S677" s="9" t="n">
+      <x:c r="S677" s="9" t="str">
         <x:v>5156002</x:v>
       </x:c>
       <x:c r="T677" s="10" t="str">
@@ -41665,7 +41737,7 @@
       <x:c r="R678" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S678" s="9" t="n">
+      <x:c r="S678" s="9" t="str">
         <x:v>5156006</x:v>
       </x:c>
       <x:c r="T678" s="10" t="str">
@@ -41726,7 +41798,7 @@
       <x:c r="R679" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S679" s="9" t="n">
+      <x:c r="S679" s="9" t="str">
         <x:v>5156013</x:v>
       </x:c>
       <x:c r="T679" s="10" t="str">
@@ -41787,7 +41859,7 @@
       <x:c r="R680" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S680" s="9" t="n">
+      <x:c r="S680" s="9" t="str">
         <x:v>5156018</x:v>
       </x:c>
       <x:c r="T680" s="10" t="str">
@@ -41848,7 +41920,7 @@
       <x:c r="R681" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S681" s="9" t="n">
+      <x:c r="S681" s="9" t="str">
         <x:v>5156024</x:v>
       </x:c>
       <x:c r="T681" s="10" t="str">
@@ -41910,7 +41982,7 @@
       <x:c r="R682" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S682" s="9" t="n">
+      <x:c r="S682" s="9" t="str">
         <x:v>5156025</x:v>
       </x:c>
       <x:c r="T682" s="10" t="str">
@@ -41971,7 +42043,7 @@
       <x:c r="R683" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S683" s="9" t="n">
+      <x:c r="S683" s="9" t="str">
         <x:v>5156026</x:v>
       </x:c>
       <x:c r="T683" s="10" t="str">
@@ -42032,7 +42104,7 @@
       <x:c r="R684" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S684" s="9" t="n">
+      <x:c r="S684" s="9" t="str">
         <x:v>5156027</x:v>
       </x:c>
       <x:c r="T684" s="10" t="str">
@@ -42093,7 +42165,7 @@
       <x:c r="R685" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S685" s="9" t="n">
+      <x:c r="S685" s="9" t="str">
         <x:v>5156029</x:v>
       </x:c>
       <x:c r="T685" s="10" t="str">
@@ -42154,7 +42226,7 @@
       <x:c r="R686" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S686" s="9" t="n">
+      <x:c r="S686" s="9" t="str">
         <x:v>5156030</x:v>
       </x:c>
       <x:c r="T686" s="10" t="str">
@@ -42218,7 +42290,7 @@
       <x:c r="R687" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S687" s="9" t="n">
+      <x:c r="S687" s="9" t="str">
         <x:v>5156031</x:v>
       </x:c>
       <x:c r="T687" s="10" t="str">
@@ -42282,7 +42354,7 @@
       <x:c r="R688" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S688" s="9" t="n">
+      <x:c r="S688" s="9" t="str">
         <x:v>5156036</x:v>
       </x:c>
       <x:c r="T688" s="10" t="str">
@@ -42346,7 +42418,7 @@
       <x:c r="R689" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S689" s="9" t="n">
+      <x:c r="S689" s="9" t="str">
         <x:v>5156039</x:v>
       </x:c>
       <x:c r="T689" s="10" t="str">
@@ -42410,7 +42482,7 @@
       <x:c r="R690" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S690" s="9" t="n">
+      <x:c r="S690" s="9" t="str">
         <x:v>5156044</x:v>
       </x:c>
       <x:c r="T690" s="10" t="str">
@@ -42474,7 +42546,7 @@
       <x:c r="R691" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S691" s="9" t="n">
+      <x:c r="S691" s="9" t="str">
         <x:v>5156053</x:v>
       </x:c>
       <x:c r="T691" s="10" t="str">
@@ -42538,7 +42610,7 @@
       <x:c r="R692" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S692" s="9" t="n">
+      <x:c r="S692" s="9" t="str">
         <x:v>5156057</x:v>
       </x:c>
       <x:c r="T692" s="10" t="str">
@@ -42602,7 +42674,7 @@
       <x:c r="R693" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S693" s="9" t="n">
+      <x:c r="S693" s="9" t="str">
         <x:v>5156058</x:v>
       </x:c>
       <x:c r="T693" s="10" t="str">
@@ -42666,7 +42738,7 @@
       <x:c r="R694" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S694" s="9" t="n">
+      <x:c r="S694" s="9" t="str">
         <x:v>5156060</x:v>
       </x:c>
       <x:c r="T694" s="10" t="str">
@@ -42730,7 +42802,7 @@
       <x:c r="R695" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S695" s="9" t="n">
+      <x:c r="S695" s="9" t="str">
         <x:v>5156063</x:v>
       </x:c>
       <x:c r="T695" s="10" t="str">
@@ -42794,7 +42866,7 @@
       <x:c r="R696" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S696" s="9" t="n">
+      <x:c r="S696" s="9" t="str">
         <x:v>5156065</x:v>
       </x:c>
       <x:c r="T696" s="10" t="str">
@@ -42858,7 +42930,7 @@
       <x:c r="R697" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S697" s="9" t="n">
+      <x:c r="S697" s="9" t="str">
         <x:v>5156066</x:v>
       </x:c>
       <x:c r="T697" s="10" t="str">
@@ -42922,7 +42994,7 @@
       <x:c r="R698" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S698" s="9" t="n">
+      <x:c r="S698" s="9" t="str">
         <x:v>5378087</x:v>
       </x:c>
       <x:c r="T698" s="10" t="str">
@@ -42987,7 +43059,7 @@
       <x:c r="R699" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S699" s="9" t="n">
+      <x:c r="S699" s="9" t="str">
         <x:v>5151824</x:v>
       </x:c>
       <x:c r="T699" s="10" t="str">
@@ -43051,7 +43123,7 @@
       <x:c r="R700" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S700" s="9" t="n">
+      <x:c r="S700" s="9" t="str">
         <x:v>5156042</x:v>
       </x:c>
       <x:c r="T700" s="10" t="str">
@@ -43115,7 +43187,7 @@
       <x:c r="R701" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S701" s="9" t="n">
+      <x:c r="S701" s="9" t="str">
         <x:v>5156047</x:v>
       </x:c>
       <x:c r="T701" s="10" t="str">
@@ -43179,7 +43251,7 @@
       <x:c r="R702" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S702" s="9" t="n">
+      <x:c r="S702" s="9" t="str">
         <x:v>5156061</x:v>
       </x:c>
       <x:c r="T702" s="10" t="str">
@@ -43243,7 +43315,7 @@
       <x:c r="R703" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S703" s="9" t="n">
+      <x:c r="S703" s="9" t="str">
         <x:v>5151491</x:v>
       </x:c>
       <x:c r="T703" s="10" t="str">
@@ -43305,7 +43377,7 @@
       <x:c r="R704" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S704" s="9" t="n">
+      <x:c r="S704" s="9" t="str">
         <x:v>5151938</x:v>
       </x:c>
       <x:c r="T704" s="10" t="str">
@@ -43370,7 +43442,7 @@
       <x:c r="R705" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S705" s="9" t="n">
+      <x:c r="S705" s="9" t="str">
         <x:v>5155746</x:v>
       </x:c>
       <x:c r="T705" s="10" t="str">
@@ -43438,7 +43510,7 @@
       <x:c r="R706" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S706" s="9" t="n">
+      <x:c r="S706" s="9" t="str">
         <x:v>5156035</x:v>
       </x:c>
       <x:c r="T706" s="10" t="str">
@@ -43500,7 +43572,7 @@
       <x:c r="R707" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S707" s="9" t="n">
+      <x:c r="S707" s="9" t="str">
         <x:v>5156037</x:v>
       </x:c>
       <x:c r="T707" s="10" t="str">
@@ -43564,7 +43636,7 @@
       <x:c r="R708" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S708" s="9" t="n">
+      <x:c r="S708" s="9" t="str">
         <x:v>5156041</x:v>
       </x:c>
       <x:c r="T708" s="10" t="str">
@@ -43628,7 +43700,7 @@
       <x:c r="R709" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S709" s="9" t="n">
+      <x:c r="S709" s="9" t="str">
         <x:v>5156048</x:v>
       </x:c>
       <x:c r="T709" s="10" t="str">
@@ -43693,7 +43765,7 @@
       <x:c r="R710" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S710" s="9" t="n">
+      <x:c r="S710" s="9" t="str">
         <x:v>5156049</x:v>
       </x:c>
       <x:c r="T710" s="10" t="str">
@@ -43757,7 +43829,7 @@
       <x:c r="R711" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S711" s="9" t="n">
+      <x:c r="S711" s="9" t="str">
         <x:v>5156050</x:v>
       </x:c>
       <x:c r="T711" s="10" t="str">
@@ -43821,7 +43893,7 @@
       <x:c r="R712" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S712" s="9" t="n">
+      <x:c r="S712" s="9" t="str">
         <x:v>5156051</x:v>
       </x:c>
       <x:c r="T712" s="10" t="str">
@@ -43885,7 +43957,7 @@
       <x:c r="R713" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S713" s="9" t="n">
+      <x:c r="S713" s="9" t="str">
         <x:v>5156054</x:v>
       </x:c>
       <x:c r="T713" s="10" t="str">
@@ -43949,7 +44021,7 @@
       <x:c r="R714" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S714" s="9" t="n">
+      <x:c r="S714" s="9" t="str">
         <x:v>5156055</x:v>
       </x:c>
       <x:c r="T714" s="10" t="str">
@@ -44013,7 +44085,7 @@
       <x:c r="R715" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S715" s="9" t="n">
+      <x:c r="S715" s="9" t="str">
         <x:v>5156056</x:v>
       </x:c>
       <x:c r="T715" s="10" t="str">
@@ -44077,7 +44149,7 @@
       <x:c r="R716" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S716" s="9" t="n">
+      <x:c r="S716" s="9" t="str">
         <x:v>5156059</x:v>
       </x:c>
       <x:c r="T716" s="10" t="str">
@@ -44141,7 +44213,7 @@
       <x:c r="R717" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S717" s="9" t="n">
+      <x:c r="S717" s="9" t="str">
         <x:v>5156062</x:v>
       </x:c>
       <x:c r="T717" s="10" t="str">
@@ -44205,7 +44277,7 @@
       <x:c r="R718" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S718" s="9" t="n">
+      <x:c r="S718" s="9" t="str">
         <x:v>5156064</x:v>
       </x:c>
       <x:c r="T718" s="10" t="str">
@@ -44269,7 +44341,7 @@
       <x:c r="R719" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S719" s="9" t="n">
+      <x:c r="S719" s="9" t="str">
         <x:v>5156067</x:v>
       </x:c>
       <x:c r="T719" s="10" t="str">
@@ -44333,7 +44405,7 @@
       <x:c r="R720" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S720" s="9" t="n">
+      <x:c r="S720" s="9" t="str">
         <x:v>5156068</x:v>
       </x:c>
       <x:c r="T720" s="10" t="str">
@@ -44402,7 +44474,7 @@
       <x:c r="R721" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S721" s="9" t="n">
+      <x:c r="S721" s="9" t="str">
         <x:v>5156069</x:v>
       </x:c>
       <x:c r="T721" s="10" t="str">
@@ -44457,7 +44529,7 @@
       <x:c r="R722" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S722" s="9" t="n">
+      <x:c r="S722" s="9" t="str">
         <x:v>5151498</x:v>
       </x:c>
       <x:c r="T722" s="10" t="str">
@@ -44512,7 +44584,7 @@
       <x:c r="R723" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S723" s="9" t="n">
+      <x:c r="S723" s="9" t="str">
         <x:v>5156070</x:v>
       </x:c>
       <x:c r="T723" s="10" t="str">
@@ -44567,7 +44639,7 @@
       <x:c r="R724" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S724" s="9" t="n">
+      <x:c r="S724" s="9" t="str">
         <x:v>5156071</x:v>
       </x:c>
       <x:c r="T724" s="10" t="str">
@@ -44622,7 +44694,7 @@
       <x:c r="R725" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S725" s="9" t="n">
+      <x:c r="S725" s="9" t="str">
         <x:v>5156072</x:v>
       </x:c>
       <x:c r="T725" s="10" t="str">
@@ -44677,7 +44749,7 @@
       <x:c r="R726" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S726" s="9" t="n">
+      <x:c r="S726" s="9" t="str">
         <x:v>5156079</x:v>
       </x:c>
       <x:c r="T726" s="10" t="str">
@@ -44732,7 +44804,7 @@
       <x:c r="R727" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S727" s="9" t="n">
+      <x:c r="S727" s="9" t="str">
         <x:v>5378021</x:v>
       </x:c>
       <x:c r="T727" s="10" t="str">
@@ -44787,7 +44859,7 @@
       <x:c r="R728" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S728" s="9" t="n">
+      <x:c r="S728" s="9" t="str">
         <x:v>5378195</x:v>
       </x:c>
       <x:c r="T728" s="10" t="str">
@@ -44842,7 +44914,7 @@
       <x:c r="R729" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S729" s="9" t="n">
+      <x:c r="S729" s="9" t="str">
         <x:v>5156074</x:v>
       </x:c>
       <x:c r="T729" s="10" t="str">
@@ -44897,7 +44969,7 @@
       <x:c r="R730" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S730" s="9" t="n">
+      <x:c r="S730" s="9" t="str">
         <x:v>5156080</x:v>
       </x:c>
       <x:c r="T730" s="10" t="str">
@@ -44952,7 +45024,7 @@
       <x:c r="R731" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S731" s="9" t="n">
+      <x:c r="S731" s="9" t="str">
         <x:v>5378122</x:v>
       </x:c>
       <x:c r="T731" s="10" t="str">
@@ -45007,7 +45079,7 @@
       <x:c r="R732" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S732" s="9" t="n">
+      <x:c r="S732" s="9" t="str">
         <x:v>5156073</x:v>
       </x:c>
       <x:c r="T732" s="10" t="str">
@@ -45062,7 +45134,7 @@
       <x:c r="R733" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S733" s="9" t="n">
+      <x:c r="S733" s="9" t="str">
         <x:v>5156075</x:v>
       </x:c>
       <x:c r="T733" s="10" t="str">
@@ -45117,7 +45189,7 @@
       <x:c r="R734" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S734" s="9" t="n">
+      <x:c r="S734" s="9" t="str">
         <x:v>5156076</x:v>
       </x:c>
       <x:c r="T734" s="10" t="str">
@@ -45172,7 +45244,7 @@
       <x:c r="R735" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S735" s="9" t="n">
+      <x:c r="S735" s="9" t="str">
         <x:v>5156077</x:v>
       </x:c>
       <x:c r="T735" s="10" t="str">
@@ -45227,7 +45299,7 @@
       <x:c r="R736" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S736" s="9" t="n">
+      <x:c r="S736" s="9" t="str">
         <x:v>5156078</x:v>
       </x:c>
       <x:c r="T736" s="10" t="str">
@@ -45282,7 +45354,7 @@
       <x:c r="R737" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S737" s="9" t="n">
+      <x:c r="S737" s="9" t="str">
         <x:v>5156081</x:v>
       </x:c>
       <x:c r="T737" s="10" t="str">
@@ -45335,7 +45407,7 @@
       <x:c r="R738" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S738" s="9" t="n">
+      <x:c r="S738" s="9" t="str">
         <x:v>5156082</x:v>
       </x:c>
       <x:c r="T738" s="10" t="str">
@@ -45390,7 +45462,7 @@
       <x:c r="R739" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S739" s="9" t="n">
+      <x:c r="S739" s="9" t="str">
         <x:v>5378115</x:v>
       </x:c>
       <x:c r="T739" s="10" t="str">
@@ -45445,7 +45517,7 @@
       <x:c r="R740" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S740" s="9" t="n">
+      <x:c r="S740" s="9" t="str">
         <x:v>5395065</x:v>
       </x:c>
       <x:c r="T740" s="10" t="str">
@@ -45498,7 +45570,7 @@
       <x:c r="R741" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S741" s="9" t="n">
+      <x:c r="S741" s="9" t="str">
         <x:v>5395346</x:v>
       </x:c>
       <x:c r="T741" s="10" t="str">
@@ -45553,7 +45625,7 @@
       <x:c r="R742" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S742" s="9" t="n">
+      <x:c r="S742" s="9" t="str">
         <x:v>5418385</x:v>
       </x:c>
       <x:c r="T742" s="10" t="str">
@@ -45608,7 +45680,7 @@
       <x:c r="R743" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S743" s="9" t="n">
+      <x:c r="S743" s="9" t="str">
         <x:v>5418397</x:v>
       </x:c>
       <x:c r="T743" s="10" t="str">
@@ -45669,7 +45741,7 @@
       <x:c r="R744" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S744" s="9" t="n">
+      <x:c r="S744" s="9" t="str">
         <x:v>5156084</x:v>
       </x:c>
       <x:c r="T744" s="10" t="str">
@@ -45730,7 +45802,7 @@
       <x:c r="R745" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S745" s="9" t="n">
+      <x:c r="S745" s="9" t="str">
         <x:v>5156089</x:v>
       </x:c>
       <x:c r="T745" s="10" t="str">
@@ -45791,7 +45863,7 @@
       <x:c r="R746" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S746" s="9" t="n">
+      <x:c r="S746" s="9" t="str">
         <x:v>6919027</x:v>
       </x:c>
       <x:c r="T746" s="10" t="str">
@@ -45855,7 +45927,7 @@
       <x:c r="R747" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S747" s="9" t="n">
+      <x:c r="S747" s="9" t="str">
         <x:v>5086114</x:v>
       </x:c>
       <x:c r="T747" s="10" t="str">
@@ -45916,7 +45988,7 @@
       <x:c r="R748" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S748" s="9" t="n">
+      <x:c r="S748" s="9" t="str">
         <x:v>5156086</x:v>
       </x:c>
       <x:c r="T748" s="10" t="str">
@@ -45980,7 +46052,7 @@
       <x:c r="R749" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S749" s="9" t="n">
+      <x:c r="S749" s="9" t="str">
         <x:v>5156094</x:v>
       </x:c>
       <x:c r="T749" s="10" t="str">
@@ -46041,7 +46113,7 @@
       <x:c r="R750" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S750" s="9" t="n">
+      <x:c r="S750" s="9" t="str">
         <x:v>6919030</x:v>
       </x:c>
       <x:c r="T750" s="10" t="str">
@@ -46105,7 +46177,7 @@
       <x:c r="R751" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S751" s="9" t="n">
+      <x:c r="S751" s="9" t="str">
         <x:v>5004233</x:v>
       </x:c>
       <x:c r="T751" s="10" t="str">
@@ -46166,7 +46238,7 @@
       <x:c r="R752" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S752" s="9" t="n">
+      <x:c r="S752" s="9" t="str">
         <x:v>5004235</x:v>
       </x:c>
       <x:c r="T752" s="10" t="str">
@@ -46227,7 +46299,7 @@
       <x:c r="R753" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S753" s="9" t="n">
+      <x:c r="S753" s="9" t="str">
         <x:v>5004236</x:v>
       </x:c>
       <x:c r="T753" s="10" t="str">
@@ -46288,7 +46360,7 @@
       <x:c r="R754" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S754" s="9" t="n">
+      <x:c r="S754" s="9" t="str">
         <x:v>5004237</x:v>
       </x:c>
       <x:c r="T754" s="10" t="str">
@@ -46349,7 +46421,7 @@
       <x:c r="R755" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S755" s="9" t="n">
+      <x:c r="S755" s="9" t="str">
         <x:v>5004238</x:v>
       </x:c>
       <x:c r="T755" s="10" t="str">
@@ -46412,7 +46484,7 @@
       <x:c r="R756" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S756" s="9" t="n">
+      <x:c r="S756" s="9" t="str">
         <x:v>5004240</x:v>
       </x:c>
       <x:c r="T756" s="10" t="str">
@@ -46474,7 +46546,7 @@
       <x:c r="R757" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S757" s="9" t="n">
+      <x:c r="S757" s="9" t="str">
         <x:v>5004242</x:v>
       </x:c>
       <x:c r="T757" s="10" t="str">
@@ -46535,7 +46607,7 @@
       <x:c r="R758" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S758" s="9" t="n">
+      <x:c r="S758" s="9" t="str">
         <x:v>5151663</x:v>
       </x:c>
       <x:c r="T758" s="10" t="str">
@@ -46596,7 +46668,7 @@
       <x:c r="R759" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S759" s="9" t="n">
+      <x:c r="S759" s="9" t="str">
         <x:v>5156083</x:v>
       </x:c>
       <x:c r="T759" s="10" t="str">
@@ -46657,7 +46729,7 @@
       <x:c r="R760" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S760" s="9" t="n">
+      <x:c r="S760" s="9" t="str">
         <x:v>5156085</x:v>
       </x:c>
       <x:c r="T760" s="10" t="str">
@@ -46721,7 +46793,7 @@
       <x:c r="R761" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S761" s="9" t="n">
+      <x:c r="S761" s="9" t="str">
         <x:v>5156087</x:v>
       </x:c>
       <x:c r="T761" s="10" t="str">
@@ -46782,7 +46854,7 @@
       <x:c r="R762" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S762" s="9" t="n">
+      <x:c r="S762" s="9" t="str">
         <x:v>5156091</x:v>
       </x:c>
       <x:c r="T762" s="10" t="str">
@@ -46843,7 +46915,7 @@
       <x:c r="R763" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S763" s="9" t="n">
+      <x:c r="S763" s="9" t="str">
         <x:v>5156093</x:v>
       </x:c>
       <x:c r="T763" s="10" t="str">
@@ -46904,7 +46976,7 @@
       <x:c r="R764" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S764" s="9" t="n">
+      <x:c r="S764" s="9" t="str">
         <x:v>5156102</x:v>
       </x:c>
       <x:c r="T764" s="10" t="str">
@@ -46971,7 +47043,7 @@
       <x:c r="R765" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S765" s="9" t="n">
+      <x:c r="S765" s="9" t="str">
         <x:v>5151204</x:v>
       </x:c>
       <x:c r="T765" s="10" t="str">
@@ -47035,7 +47107,7 @@
       <x:c r="R766" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S766" s="9" t="n">
+      <x:c r="S766" s="9" t="str">
         <x:v>5156100</x:v>
       </x:c>
       <x:c r="T766" s="10" t="str">
@@ -47099,7 +47171,7 @@
       <x:c r="R767" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S767" s="9" t="n">
+      <x:c r="S767" s="9" t="str">
         <x:v>5156103</x:v>
       </x:c>
       <x:c r="T767" s="10" t="str">
@@ -47161,7 +47233,7 @@
       <x:c r="R768" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S768" s="9" t="n">
+      <x:c r="S768" s="9" t="str">
         <x:v>5156104</x:v>
       </x:c>
       <x:c r="T768" s="10" t="str">
@@ -47225,7 +47297,7 @@
       <x:c r="R769" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S769" s="9" t="n">
+      <x:c r="S769" s="9" t="str">
         <x:v>5156106</x:v>
       </x:c>
       <x:c r="T769" s="10" t="str">
@@ -47289,7 +47361,7 @@
       <x:c r="R770" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S770" s="9" t="n">
+      <x:c r="S770" s="9" t="str">
         <x:v>5156101</x:v>
       </x:c>
       <x:c r="T770" s="10" t="str">
@@ -47353,7 +47425,7 @@
       <x:c r="R771" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S771" s="9" t="n">
+      <x:c r="S771" s="9" t="str">
         <x:v>5156105</x:v>
       </x:c>
       <x:c r="T771" s="10" t="str">
@@ -47417,7 +47489,7 @@
       <x:c r="R772" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S772" s="9" t="n">
+      <x:c r="S772" s="9" t="str">
         <x:v>6919031</x:v>
       </x:c>
       <x:c r="T772" s="10" t="str">
@@ -47481,7 +47553,7 @@
       <x:c r="R773" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S773" s="9" t="n">
+      <x:c r="S773" s="9" t="str">
         <x:v>6919032</x:v>
       </x:c>
       <x:c r="T773" s="10" t="str">
@@ -47545,7 +47617,7 @@
       <x:c r="R774" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S774" s="9" t="n">
+      <x:c r="S774" s="9" t="str">
         <x:v>5004251</x:v>
       </x:c>
       <x:c r="T774" s="10" t="str">
@@ -47609,7 +47681,7 @@
       <x:c r="R775" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S775" s="9" t="n">
+      <x:c r="S775" s="9" t="str">
         <x:v>5004252</x:v>
       </x:c>
       <x:c r="T775" s="10" t="str">
@@ -47673,7 +47745,7 @@
       <x:c r="R776" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S776" s="9" t="n">
+      <x:c r="S776" s="9" t="str">
         <x:v>5004253</x:v>
       </x:c>
       <x:c r="T776" s="10" t="str">
@@ -47742,7 +47814,7 @@
       <x:c r="R777" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S777" s="9" t="n">
+      <x:c r="S777" s="9" t="str">
         <x:v>5004254</x:v>
       </x:c>
       <x:c r="T777" s="10" t="str">
@@ -47806,7 +47878,7 @@
       <x:c r="R778" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S778" s="9" t="n">
+      <x:c r="S778" s="9" t="str">
         <x:v>5004255</x:v>
       </x:c>
       <x:c r="T778" s="10" t="str">
@@ -47871,7 +47943,7 @@
       <x:c r="R779" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S779" s="9" t="n">
+      <x:c r="S779" s="9" t="str">
         <x:v>5004256</x:v>
       </x:c>
       <x:c r="T779" s="10" t="str">
@@ -47935,7 +48007,7 @@
       <x:c r="R780" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S780" s="9" t="n">
+      <x:c r="S780" s="9" t="str">
         <x:v>5151828</x:v>
       </x:c>
       <x:c r="T780" s="10" t="str">
@@ -48004,7 +48076,7 @@
       <x:c r="R781" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S781" s="9" t="n">
+      <x:c r="S781" s="9" t="str">
         <x:v>5156095</x:v>
       </x:c>
       <x:c r="T781" s="10" t="str">
@@ -48068,7 +48140,7 @@
       <x:c r="R782" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S782" s="9" t="n">
+      <x:c r="S782" s="9" t="str">
         <x:v>5156096</x:v>
       </x:c>
       <x:c r="T782" s="10" t="str">
@@ -48132,7 +48204,7 @@
       <x:c r="R783" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S783" s="9" t="n">
+      <x:c r="S783" s="9" t="str">
         <x:v>5156097</x:v>
       </x:c>
       <x:c r="T783" s="10" t="str">
@@ -48196,7 +48268,7 @@
       <x:c r="R784" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S784" s="9" t="n">
+      <x:c r="S784" s="9" t="str">
         <x:v>5156099</x:v>
       </x:c>
       <x:c r="T784" s="10" t="str">
@@ -48258,7 +48330,7 @@
       <x:c r="R785" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S785" s="9" t="n">
+      <x:c r="S785" s="9" t="str">
         <x:v>5156108</x:v>
       </x:c>
       <x:c r="T785" s="10" t="str">
@@ -48313,7 +48385,7 @@
       <x:c r="R786" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S786" s="9" t="n">
+      <x:c r="S786" s="9" t="str">
         <x:v>5086139</x:v>
       </x:c>
       <x:c r="T786" s="10" t="str">
@@ -48368,7 +48440,7 @@
       <x:c r="R787" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S787" s="9" t="n">
+      <x:c r="S787" s="9" t="str">
         <x:v>5094431</x:v>
       </x:c>
       <x:c r="T787" s="10" t="str">
@@ -48423,7 +48495,7 @@
       <x:c r="R788" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S788" s="9" t="n">
+      <x:c r="S788" s="9" t="str">
         <x:v>5156117</x:v>
       </x:c>
       <x:c r="T788" s="10" t="str">
@@ -48478,7 +48550,7 @@
       <x:c r="R789" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S789" s="9" t="n">
+      <x:c r="S789" s="9" t="str">
         <x:v>5156122</x:v>
       </x:c>
       <x:c r="T789" s="10" t="str">
@@ -48533,7 +48605,7 @@
       <x:c r="R790" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S790" s="9" t="n">
+      <x:c r="S790" s="9" t="str">
         <x:v>5156124</x:v>
       </x:c>
       <x:c r="T790" s="10" t="str">
@@ -48586,7 +48658,7 @@
       <x:c r="R791" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S791" s="9" t="n">
+      <x:c r="S791" s="9" t="str">
         <x:v>5156129</x:v>
       </x:c>
       <x:c r="T791" s="10" t="str">
@@ -48641,7 +48713,7 @@
       <x:c r="R792" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S792" s="9" t="n">
+      <x:c r="S792" s="9" t="str">
         <x:v>5156130</x:v>
       </x:c>
       <x:c r="T792" s="10" t="str">
@@ -48696,7 +48768,7 @@
       <x:c r="R793" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S793" s="9" t="n">
+      <x:c r="S793" s="9" t="str">
         <x:v>6919034</x:v>
       </x:c>
       <x:c r="T793" s="10" t="str">
@@ -48751,7 +48823,7 @@
       <x:c r="R794" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S794" s="9" t="n">
+      <x:c r="S794" s="9" t="str">
         <x:v>5156110</x:v>
       </x:c>
       <x:c r="T794" s="10" t="str">
@@ -48806,7 +48878,7 @@
       <x:c r="R795" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S795" s="9" t="n">
+      <x:c r="S795" s="9" t="str">
         <x:v>5156113</x:v>
       </x:c>
       <x:c r="T795" s="10" t="str">
@@ -48861,7 +48933,7 @@
       <x:c r="R796" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S796" s="9" t="n">
+      <x:c r="S796" s="9" t="str">
         <x:v>5156120</x:v>
       </x:c>
       <x:c r="T796" s="10" t="str">
@@ -48916,7 +48988,7 @@
       <x:c r="R797" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S797" s="9" t="n">
+      <x:c r="S797" s="9" t="str">
         <x:v>5156123</x:v>
       </x:c>
       <x:c r="T797" s="10" t="str">
@@ -48971,7 +49043,7 @@
       <x:c r="R798" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S798" s="9" t="n">
+      <x:c r="S798" s="9" t="str">
         <x:v>5156125</x:v>
       </x:c>
       <x:c r="T798" s="10" t="str">
@@ -49026,7 +49098,7 @@
       <x:c r="R799" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S799" s="9" t="n">
+      <x:c r="S799" s="9" t="str">
         <x:v>5156127</x:v>
       </x:c>
       <x:c r="T799" s="10" t="str">
@@ -49081,7 +49153,7 @@
       <x:c r="R800" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S800" s="9" t="n">
+      <x:c r="S800" s="9" t="str">
         <x:v>5156109</x:v>
       </x:c>
       <x:c r="T800" s="10" t="str">
@@ -49136,7 +49208,7 @@
       <x:c r="R801" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S801" s="9" t="n">
+      <x:c r="S801" s="9" t="str">
         <x:v>5156112</x:v>
       </x:c>
       <x:c r="T801" s="10" t="str">
@@ -49191,7 +49263,7 @@
       <x:c r="R802" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S802" s="9" t="n">
+      <x:c r="S802" s="9" t="str">
         <x:v>5156114</x:v>
       </x:c>
       <x:c r="T802" s="10" t="str">
@@ -49246,7 +49318,7 @@
       <x:c r="R803" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S803" s="9" t="n">
+      <x:c r="S803" s="9" t="str">
         <x:v>5156115</x:v>
       </x:c>
       <x:c r="T803" s="10" t="str">
@@ -49301,7 +49373,7 @@
       <x:c r="R804" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S804" s="9" t="n">
+      <x:c r="S804" s="9" t="str">
         <x:v>5156116</x:v>
       </x:c>
       <x:c r="T804" s="10" t="str">
@@ -49356,7 +49428,7 @@
       <x:c r="R805" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S805" s="9" t="n">
+      <x:c r="S805" s="9" t="str">
         <x:v>5156119</x:v>
       </x:c>
       <x:c r="T805" s="10" t="str">
@@ -49411,7 +49483,7 @@
       <x:c r="R806" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S806" s="9" t="n">
+      <x:c r="S806" s="9" t="str">
         <x:v>5156121</x:v>
       </x:c>
       <x:c r="T806" s="10" t="str">
@@ -49466,7 +49538,7 @@
       <x:c r="R807" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S807" s="9" t="n">
+      <x:c r="S807" s="9" t="str">
         <x:v>5156126</x:v>
       </x:c>
       <x:c r="T807" s="10" t="str">
@@ -49521,7 +49593,7 @@
       <x:c r="R808" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S808" s="9" t="n">
+      <x:c r="S808" s="9" t="str">
         <x:v>5156128</x:v>
       </x:c>
       <x:c r="T808" s="10" t="str">
@@ -49574,7 +49646,7 @@
       <x:c r="R809" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S809" s="9" t="n">
+      <x:c r="S809" s="9" t="str">
         <x:v>5156131</x:v>
       </x:c>
       <x:c r="T809" s="10" t="str">
@@ -49627,7 +49699,7 @@
       <x:c r="R810" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S810" s="9" t="n">
+      <x:c r="S810" s="9" t="str">
         <x:v>5156132</x:v>
       </x:c>
       <x:c r="T810" s="10" t="str">
@@ -49688,7 +49760,7 @@
       <x:c r="R811" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S811" s="9" t="n">
+      <x:c r="S811" s="9" t="str">
         <x:v>5156146</x:v>
       </x:c>
       <x:c r="T811" s="10" t="str">
@@ -49749,7 +49821,7 @@
       <x:c r="R812" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S812" s="9" t="n">
+      <x:c r="S812" s="9" t="str">
         <x:v>5156147</x:v>
       </x:c>
       <x:c r="T812" s="10" t="str">
@@ -49810,7 +49882,7 @@
       <x:c r="R813" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S813" s="9" t="n">
+      <x:c r="S813" s="9" t="str">
         <x:v>5156149</x:v>
       </x:c>
       <x:c r="T813" s="10" t="str">
@@ -49871,7 +49943,7 @@
       <x:c r="R814" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S814" s="9" t="n">
+      <x:c r="S814" s="9" t="str">
         <x:v>5156134</x:v>
       </x:c>
       <x:c r="T814" s="10" t="str">
@@ -49932,7 +50004,7 @@
       <x:c r="R815" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S815" s="9" t="n">
+      <x:c r="S815" s="9" t="str">
         <x:v>5156135</x:v>
       </x:c>
       <x:c r="T815" s="10" t="str">
@@ -49993,7 +50065,7 @@
       <x:c r="R816" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S816" s="9" t="n">
+      <x:c r="S816" s="9" t="str">
         <x:v>5378211</x:v>
       </x:c>
       <x:c r="T816" s="10" t="str">
@@ -50054,7 +50126,7 @@
       <x:c r="R817" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S817" s="9" t="n">
+      <x:c r="S817" s="9" t="str">
         <x:v>5378225</x:v>
       </x:c>
       <x:c r="T817" s="10" t="str">
@@ -50115,7 +50187,7 @@
       <x:c r="R818" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S818" s="9" t="n">
+      <x:c r="S818" s="9" t="str">
         <x:v>5151453</x:v>
       </x:c>
       <x:c r="T818" s="10" t="str">
@@ -50176,7 +50248,7 @@
       <x:c r="R819" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S819" s="9" t="n">
+      <x:c r="S819" s="9" t="str">
         <x:v>5152044</x:v>
       </x:c>
       <x:c r="T819" s="10" t="str">
@@ -50237,7 +50309,7 @@
       <x:c r="R820" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S820" s="9" t="n">
+      <x:c r="S820" s="9" t="str">
         <x:v>5156137</x:v>
       </x:c>
       <x:c r="T820" s="10" t="str">
@@ -50298,7 +50370,7 @@
       <x:c r="R821" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S821" s="9" t="n">
+      <x:c r="S821" s="9" t="str">
         <x:v>5156140</x:v>
       </x:c>
       <x:c r="T821" s="10" t="str">
@@ -50362,7 +50434,7 @@
       <x:c r="R822" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S822" s="9" t="n">
+      <x:c r="S822" s="9" t="str">
         <x:v>5156141</x:v>
       </x:c>
       <x:c r="T822" s="10" t="str">
@@ -50423,7 +50495,7 @@
       <x:c r="R823" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S823" s="9" t="n">
+      <x:c r="S823" s="9" t="str">
         <x:v>5156143</x:v>
       </x:c>
       <x:c r="T823" s="10" t="str">
@@ -50484,7 +50556,7 @@
       <x:c r="R824" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S824" s="9" t="n">
+      <x:c r="S824" s="9" t="str">
         <x:v>5156145</x:v>
       </x:c>
       <x:c r="T824" s="10" t="str">
@@ -50548,7 +50620,7 @@
       <x:c r="R825" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S825" s="9" t="n">
+      <x:c r="S825" s="9" t="str">
         <x:v>5151720</x:v>
       </x:c>
       <x:c r="T825" s="10" t="str">
@@ -50613,7 +50685,7 @@
       <x:c r="R826" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S826" s="9" t="n">
+      <x:c r="S826" s="9" t="str">
         <x:v>5151836</x:v>
       </x:c>
       <x:c r="T826" s="10" t="str">
@@ -50677,7 +50749,7 @@
       <x:c r="R827" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S827" s="9" t="n">
+      <x:c r="S827" s="9" t="str">
         <x:v>5156153</x:v>
       </x:c>
       <x:c r="T827" s="10" t="str">
@@ -50741,7 +50813,7 @@
       <x:c r="R828" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S828" s="9" t="n">
+      <x:c r="S828" s="9" t="str">
         <x:v>5156156</x:v>
       </x:c>
       <x:c r="T828" s="10" t="str">
@@ -50805,7 +50877,7 @@
       <x:c r="R829" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S829" s="9" t="n">
+      <x:c r="S829" s="9" t="str">
         <x:v>5156158</x:v>
       </x:c>
       <x:c r="T829" s="10" t="str">
@@ -50869,7 +50941,7 @@
       <x:c r="R830" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S830" s="9" t="n">
+      <x:c r="S830" s="9" t="str">
         <x:v>5378215</x:v>
       </x:c>
       <x:c r="T830" s="10" t="str">
@@ -50933,7 +51005,7 @@
       <x:c r="R831" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S831" s="9" t="n">
+      <x:c r="S831" s="9" t="str">
         <x:v>5378232</x:v>
       </x:c>
       <x:c r="T831" s="10" t="str">
@@ -50997,7 +51069,7 @@
       <x:c r="R832" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S832" s="9" t="n">
+      <x:c r="S832" s="9" t="str">
         <x:v>5086143</x:v>
       </x:c>
       <x:c r="T832" s="10" t="str">
@@ -51061,7 +51133,7 @@
       <x:c r="R833" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S833" s="9" t="n">
+      <x:c r="S833" s="9" t="str">
         <x:v>5151476</x:v>
       </x:c>
       <x:c r="T833" s="10" t="str">
@@ -51125,7 +51197,7 @@
       <x:c r="R834" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S834" s="9" t="n">
+      <x:c r="S834" s="9" t="str">
         <x:v>5152055</x:v>
       </x:c>
       <x:c r="T834" s="10" t="str">
@@ -51189,7 +51261,7 @@
       <x:c r="R835" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S835" s="9" t="n">
+      <x:c r="S835" s="9" t="str">
         <x:v>5156152</x:v>
       </x:c>
       <x:c r="T835" s="10" t="str">
@@ -51253,7 +51325,7 @@
       <x:c r="R836" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S836" s="9" t="n">
+      <x:c r="S836" s="9" t="str">
         <x:v>5156154</x:v>
       </x:c>
       <x:c r="T836" s="10" t="str">
@@ -51317,7 +51389,7 @@
       <x:c r="R837" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S837" s="9" t="n">
+      <x:c r="S837" s="9" t="str">
         <x:v>5086180</x:v>
       </x:c>
       <x:c r="T837" s="10" t="str">
@@ -51381,7 +51453,7 @@
       <x:c r="R838" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S838" s="9" t="n">
+      <x:c r="S838" s="9" t="str">
         <x:v>5156150</x:v>
       </x:c>
       <x:c r="T838" s="10" t="str">
@@ -51445,7 +51517,7 @@
       <x:c r="R839" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S839" s="9" t="n">
+      <x:c r="S839" s="9" t="str">
         <x:v>5156151</x:v>
       </x:c>
       <x:c r="T839" s="10" t="str">
@@ -51509,7 +51581,7 @@
       <x:c r="R840" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S840" s="9" t="n">
+      <x:c r="S840" s="9" t="str">
         <x:v>5156157</x:v>
       </x:c>
       <x:c r="T840" s="10" t="str">
@@ -51573,7 +51645,7 @@
       <x:c r="R841" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S841" s="9" t="n">
+      <x:c r="S841" s="9" t="str">
         <x:v>5156159</x:v>
       </x:c>
       <x:c r="T841" s="10" t="str">
@@ -51637,7 +51709,7 @@
       <x:c r="R842" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S842" s="9" t="n">
+      <x:c r="S842" s="9" t="str">
         <x:v>5156160</x:v>
       </x:c>
       <x:c r="T842" s="10" t="str">
@@ -51692,7 +51764,7 @@
       <x:c r="R843" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S843" s="9" t="n">
+      <x:c r="S843" s="9" t="str">
         <x:v>5156164</x:v>
       </x:c>
       <x:c r="T843" s="10" t="str">
@@ -51747,7 +51819,7 @@
       <x:c r="R844" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S844" s="9" t="n">
+      <x:c r="S844" s="9" t="str">
         <x:v>5156162</x:v>
       </x:c>
       <x:c r="T844" s="10" t="str">
@@ -51802,7 +51874,7 @@
       <x:c r="R845" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S845" s="9" t="n">
+      <x:c r="S845" s="9" t="str">
         <x:v>5156163</x:v>
       </x:c>
       <x:c r="T845" s="10" t="str">
@@ -51857,7 +51929,7 @@
       <x:c r="R846" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S846" s="9" t="n">
+      <x:c r="S846" s="9" t="str">
         <x:v>5394923</x:v>
       </x:c>
       <x:c r="T846" s="10" t="str">
@@ -51912,7 +51984,7 @@
       <x:c r="R847" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S847" s="9" t="n">
+      <x:c r="S847" s="9" t="str">
         <x:v>5395349</x:v>
       </x:c>
       <x:c r="T847" s="10" t="str">
@@ -51973,7 +52045,7 @@
       <x:c r="R848" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S848" s="9" t="n">
+      <x:c r="S848" s="9" t="str">
         <x:v>5151803</x:v>
       </x:c>
       <x:c r="T848" s="10" t="str">
@@ -52034,7 +52106,7 @@
       <x:c r="R849" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S849" s="9" t="n">
+      <x:c r="S849" s="9" t="str">
         <x:v>5155344</x:v>
       </x:c>
       <x:c r="T849" s="10" t="str">
@@ -52097,7 +52169,7 @@
       <x:c r="R850" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S850" s="9" t="n">
+      <x:c r="S850" s="9" t="str">
         <x:v>5155345</x:v>
       </x:c>
       <x:c r="T850" s="10" t="str">
@@ -52158,7 +52230,7 @@
       <x:c r="R851" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S851" s="9" t="n">
+      <x:c r="S851" s="9" t="str">
         <x:v>5155348</x:v>
       </x:c>
       <x:c r="T851" s="10" t="str">
@@ -52219,7 +52291,7 @@
       <x:c r="R852" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S852" s="9" t="n">
+      <x:c r="S852" s="9" t="str">
         <x:v>5155349</x:v>
       </x:c>
       <x:c r="T852" s="10" t="str">
@@ -52280,7 +52352,7 @@
       <x:c r="R853" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S853" s="9" t="n">
+      <x:c r="S853" s="9" t="str">
         <x:v>5155351</x:v>
       </x:c>
       <x:c r="T853" s="10" t="str">
@@ -52341,7 +52413,7 @@
       <x:c r="R854" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S854" s="9" t="n">
+      <x:c r="S854" s="9" t="str">
         <x:v>5155354</x:v>
       </x:c>
       <x:c r="T854" s="10" t="str">
@@ -52402,7 +52474,7 @@
       <x:c r="R855" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S855" s="9" t="n">
+      <x:c r="S855" s="9" t="str">
         <x:v>5155358</x:v>
       </x:c>
       <x:c r="T855" s="10" t="str">
@@ -52463,7 +52535,7 @@
       <x:c r="R856" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S856" s="9" t="n">
+      <x:c r="S856" s="9" t="str">
         <x:v>5155365</x:v>
       </x:c>
       <x:c r="T856" s="10" t="str">
@@ -52524,7 +52596,7 @@
       <x:c r="R857" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S857" s="9" t="n">
+      <x:c r="S857" s="9" t="str">
         <x:v>5155371</x:v>
       </x:c>
       <x:c r="T857" s="10" t="str">
@@ -52585,7 +52657,7 @@
       <x:c r="R858" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S858" s="9" t="n">
+      <x:c r="S858" s="9" t="str">
         <x:v>5155372</x:v>
       </x:c>
       <x:c r="T858" s="10" t="str">
@@ -52646,7 +52718,7 @@
       <x:c r="R859" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S859" s="9" t="n">
+      <x:c r="S859" s="9" t="str">
         <x:v>5377949</x:v>
       </x:c>
       <x:c r="T859" s="10" t="str">
@@ -52707,7 +52779,7 @@
       <x:c r="R860" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S860" s="9" t="n">
+      <x:c r="S860" s="9" t="str">
         <x:v>5155359</x:v>
       </x:c>
       <x:c r="T860" s="10" t="str">
@@ -52768,7 +52840,7 @@
       <x:c r="R861" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S861" s="9" t="n">
+      <x:c r="S861" s="9" t="str">
         <x:v>5155374</x:v>
       </x:c>
       <x:c r="T861" s="10" t="str">
@@ -52829,7 +52901,7 @@
       <x:c r="R862" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S862" s="9" t="n">
+      <x:c r="S862" s="9" t="str">
         <x:v>5156032</x:v>
       </x:c>
       <x:c r="T862" s="10" t="str">
@@ -52890,7 +52962,7 @@
       <x:c r="R863" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S863" s="9" t="n">
+      <x:c r="S863" s="9" t="str">
         <x:v>5376281</x:v>
       </x:c>
       <x:c r="T863" s="10" t="str">
@@ -52951,7 +53023,7 @@
       <x:c r="R864" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S864" s="9" t="n">
+      <x:c r="S864" s="9" t="str">
         <x:v>5377977</x:v>
       </x:c>
       <x:c r="T864" s="10" t="str">
@@ -53014,7 +53086,7 @@
       <x:c r="R865" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S865" s="9" t="n">
+      <x:c r="S865" s="9" t="str">
         <x:v>5151569</x:v>
       </x:c>
       <x:c r="T865" s="10" t="str">
@@ -53075,7 +53147,7 @@
       <x:c r="R866" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S866" s="9" t="n">
+      <x:c r="S866" s="9" t="str">
         <x:v>5151735</x:v>
       </x:c>
       <x:c r="T866" s="10" t="str">
@@ -53136,7 +53208,7 @@
       <x:c r="R867" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S867" s="9" t="n">
+      <x:c r="S867" s="9" t="str">
         <x:v>5151987</x:v>
       </x:c>
       <x:c r="T867" s="10" t="str">
@@ -53197,7 +53269,7 @@
       <x:c r="R868" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S868" s="9" t="n">
+      <x:c r="S868" s="9" t="str">
         <x:v>5152004</x:v>
       </x:c>
       <x:c r="T868" s="10" t="str">
@@ -53258,7 +53330,7 @@
       <x:c r="R869" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S869" s="9" t="n">
+      <x:c r="S869" s="9" t="str">
         <x:v>5155346</x:v>
       </x:c>
       <x:c r="T869" s="10" t="str">
@@ -53319,7 +53391,7 @@
       <x:c r="R870" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S870" s="9" t="n">
+      <x:c r="S870" s="9" t="str">
         <x:v>5155350</x:v>
       </x:c>
       <x:c r="T870" s="10" t="str">
@@ -53380,7 +53452,7 @@
       <x:c r="R871" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S871" s="9" t="n">
+      <x:c r="S871" s="9" t="str">
         <x:v>5155352</x:v>
       </x:c>
       <x:c r="T871" s="10" t="str">
@@ -53441,7 +53513,7 @@
       <x:c r="R872" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S872" s="9" t="n">
+      <x:c r="S872" s="9" t="str">
         <x:v>5155361</x:v>
       </x:c>
       <x:c r="T872" s="10" t="str">
@@ -53502,7 +53574,7 @@
       <x:c r="R873" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S873" s="9" t="n">
+      <x:c r="S873" s="9" t="str">
         <x:v>5155363</x:v>
       </x:c>
       <x:c r="T873" s="10" t="str">
@@ -53563,7 +53635,7 @@
       <x:c r="R874" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S874" s="9" t="n">
+      <x:c r="S874" s="9" t="str">
         <x:v>5155364</x:v>
       </x:c>
       <x:c r="T874" s="10" t="str">
@@ -53624,7 +53696,7 @@
       <x:c r="R875" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S875" s="9" t="n">
+      <x:c r="S875" s="9" t="str">
         <x:v>5155366</x:v>
       </x:c>
       <x:c r="T875" s="10" t="str">
@@ -53685,7 +53757,7 @@
       <x:c r="R876" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S876" s="9" t="n">
+      <x:c r="S876" s="9" t="str">
         <x:v>5155368</x:v>
       </x:c>
       <x:c r="T876" s="10" t="str">
@@ -53746,7 +53818,7 @@
       <x:c r="R877" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S877" s="9" t="n">
+      <x:c r="S877" s="9" t="str">
         <x:v>5155376</x:v>
       </x:c>
       <x:c r="T877" s="10" t="str">
@@ -53810,7 +53882,7 @@
       <x:c r="R878" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S878" s="9" t="n">
+      <x:c r="S878" s="9" t="str">
         <x:v>5155377</x:v>
       </x:c>
       <x:c r="T878" s="10" t="str">
@@ -53871,7 +53943,7 @@
       <x:c r="R879" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S879" s="9" t="n">
+      <x:c r="S879" s="9" t="str">
         <x:v>5155378</x:v>
       </x:c>
       <x:c r="T879" s="10" t="str">
@@ -53932,7 +54004,7 @@
       <x:c r="R880" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S880" s="9" t="n">
+      <x:c r="S880" s="9" t="str">
         <x:v>5155379</x:v>
       </x:c>
       <x:c r="T880" s="10" t="str">
@@ -53993,7 +54065,7 @@
       <x:c r="R881" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S881" s="9" t="n">
+      <x:c r="S881" s="9" t="str">
         <x:v>5155380</x:v>
       </x:c>
       <x:c r="T881" s="10" t="str">
@@ -54057,7 +54129,7 @@
       <x:c r="R882" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S882" s="9" t="n">
+      <x:c r="S882" s="9" t="str">
         <x:v>5155381</x:v>
       </x:c>
       <x:c r="T882" s="10" t="str">
@@ -54118,7 +54190,7 @@
       <x:c r="R883" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S883" s="9" t="n">
+      <x:c r="S883" s="9" t="str">
         <x:v>5155706</x:v>
       </x:c>
       <x:c r="T883" s="10" t="str">
@@ -54182,7 +54254,7 @@
       <x:c r="R884" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S884" s="9" t="n">
+      <x:c r="S884" s="9" t="str">
         <x:v>5156010</x:v>
       </x:c>
       <x:c r="T884" s="10" t="str">
@@ -54241,13 +54313,13 @@
         <x:v>A,B,D</x:v>
       </x:c>
       <x:c r="Q885" s="9" t="str">
-        <x:v>[图片: https://file.233.com/20210413/b2679912d8db4c37afce613cb8572e55] 
-综上，CE是属于代理的分类，不包括ABD，答案选ABD。</x:v>
+        <x:v>《民法典》规定，代理包括委托代理和法定代理。委托代理人按照被代理人的委托行使代理权，法定代理人依照法律规定行使代理权。
+申请代理、授权代理和指定代理不属于法定的代理分类。故本题选ABD。</x:v>
       </x:c>
       <x:c r="R885" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S885" s="9" t="n">
+      <x:c r="S885" s="9" t="str">
         <x:v>5155384</x:v>
       </x:c>
       <x:c r="T885" s="10" t="str">
@@ -54311,7 +54383,7 @@
       <x:c r="R886" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S886" s="9" t="n">
+      <x:c r="S886" s="9" t="str">
         <x:v>5155391</x:v>
       </x:c>
       <x:c r="T886" s="10" t="str">
@@ -54375,7 +54447,7 @@
       <x:c r="R887" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S887" s="9" t="n">
+      <x:c r="S887" s="9" t="str">
         <x:v>5151474</x:v>
       </x:c>
       <x:c r="T887" s="10" t="str">
@@ -54439,7 +54511,7 @@
       <x:c r="R888" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S888" s="9" t="n">
+      <x:c r="S888" s="9" t="str">
         <x:v>5155383</x:v>
       </x:c>
       <x:c r="T888" s="10" t="str">
@@ -54503,7 +54575,7 @@
       <x:c r="R889" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S889" s="9" t="n">
+      <x:c r="S889" s="9" t="str">
         <x:v>5155388</x:v>
       </x:c>
       <x:c r="T889" s="10" t="str">
@@ -54568,7 +54640,7 @@
       <x:c r="R890" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S890" s="9" t="n">
+      <x:c r="S890" s="9" t="str">
         <x:v>5155382</x:v>
       </x:c>
       <x:c r="T890" s="10" t="str">
@@ -54632,7 +54704,7 @@
       <x:c r="R891" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S891" s="9" t="n">
+      <x:c r="S891" s="9" t="str">
         <x:v>5155385</x:v>
       </x:c>
       <x:c r="T891" s="10" t="str">
@@ -54696,7 +54768,7 @@
       <x:c r="R892" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S892" s="9" t="n">
+      <x:c r="S892" s="9" t="str">
         <x:v>5155389</x:v>
       </x:c>
       <x:c r="T892" s="10" t="str">
@@ -54760,7 +54832,7 @@
       <x:c r="R893" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S893" s="9" t="n">
+      <x:c r="S893" s="9" t="str">
         <x:v>5155390</x:v>
       </x:c>
       <x:c r="T893" s="10" t="str">
@@ -54824,7 +54896,7 @@
       <x:c r="R894" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S894" s="9" t="n">
+      <x:c r="S894" s="9" t="str">
         <x:v>5155392</x:v>
       </x:c>
       <x:c r="T894" s="10" t="str">
@@ -54879,7 +54951,7 @@
       <x:c r="R895" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S895" s="9" t="n">
+      <x:c r="S895" s="9" t="str">
         <x:v>5151222</x:v>
       </x:c>
       <x:c r="T895" s="10" t="str">
@@ -54934,7 +55006,7 @@
       <x:c r="R896" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S896" s="9" t="n">
+      <x:c r="S896" s="9" t="str">
         <x:v>5155394</x:v>
       </x:c>
       <x:c r="T896" s="10" t="str">
@@ -54989,7 +55061,7 @@
       <x:c r="R897" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S897" s="9" t="n">
+      <x:c r="S897" s="9" t="str">
         <x:v>5155397</x:v>
       </x:c>
       <x:c r="T897" s="10" t="str">
@@ -55044,7 +55116,7 @@
       <x:c r="R898" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S898" s="9" t="n">
+      <x:c r="S898" s="9" t="str">
         <x:v>5376317</x:v>
       </x:c>
       <x:c r="T898" s="10" t="str">
@@ -55099,7 +55171,7 @@
       <x:c r="R899" s="9" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="S899" s="9" t="n">
+      <x:c r="S899" s="9" t="str">
         <x:v>5413580</x:v>
       </x:c>
       <x:c r="T899" s="10" t="str">
@@ -55154,7 +55226,7 @@
       <x:c r="R900" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S900" s="9" t="n">
+      <x:c r="S900" s="9" t="str">
         <x:v>5151610</x:v>
       </x:c>
       <x:c r="T900" s="10" t="str">
@@ -55209,7 +55281,7 @@
       <x:c r="R901" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S901" s="9" t="n">
+      <x:c r="S901" s="9" t="str">
         <x:v>5151729</x:v>
       </x:c>
       <x:c r="T901" s="10" t="str">
@@ -55264,7 +55336,7 @@
       <x:c r="R902" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S902" s="9" t="n">
+      <x:c r="S902" s="9" t="str">
         <x:v>5155395</x:v>
       </x:c>
       <x:c r="T902" s="10" t="str">
@@ -55319,7 +55391,7 @@
       <x:c r="R903" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S903" s="9" t="n">
+      <x:c r="S903" s="9" t="str">
         <x:v>5155396</x:v>
       </x:c>
       <x:c r="T903" s="10" t="str">
@@ -55374,7 +55446,7 @@
       <x:c r="R904" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S904" s="9" t="n">
+      <x:c r="S904" s="9" t="str">
         <x:v>5376383</x:v>
       </x:c>
       <x:c r="T904" s="10" t="str">
@@ -55429,7 +55501,7 @@
       <x:c r="R905" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S905" s="9" t="n">
+      <x:c r="S905" s="9" t="str">
         <x:v>5377710</x:v>
       </x:c>
       <x:c r="T905" s="10" t="str">
@@ -55484,7 +55556,7 @@
       <x:c r="R906" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S906" s="9" t="n">
+      <x:c r="S906" s="9" t="str">
         <x:v>5378023</x:v>
       </x:c>
       <x:c r="T906" s="10" t="str">
@@ -55539,7 +55611,7 @@
       <x:c r="R907" s="9" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S907" s="9" t="n">
+      <x:c r="S907" s="9" t="str">
         <x:v>5394927</x:v>
       </x:c>
       <x:c r="T907" s="10" t="str">
@@ -55594,7 +55666,7 @@
       <x:c r="R908" s="12" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
-      <x:c r="S908" s="12" t="n">
+      <x:c r="S908" s="12" t="str">
         <x:v>5418534</x:v>
       </x:c>
       <x:c r="T908" s="13" t="str">
@@ -55617,6 +55689,7 @@
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -55633,12 +55706,15 @@
         <x:v>预计题量</x:v>
       </x:c>
       <x:c r="E1" s="27" t="str">
+        <x:v>接口题量</x:v>
+      </x:c>
+      <x:c r="F1" s="27" t="str">
         <x:v>抓取题量</x:v>
       </x:c>
-      <x:c r="F1" s="27" t="str">
+      <x:c r="G1" s="27" t="str">
         <x:v>可查看</x:v>
       </x:c>
-      <x:c r="G1" s="28" t="str">
+      <x:c r="H1" s="28" t="str">
         <x:v>权限不足/收费题</x:v>
       </x:c>
     </x:row>
@@ -55649,19 +55725,22 @@
       <x:c r="B2" s="9" t="str">
         <x:v>第一章 个人贷款概述</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="n">
+      <x:c r="C2" s="9" t="str">
         <x:v>62417</x:v>
       </x:c>
-      <x:c r="D2" s="9" t="n">
+      <x:c r="D2" s="29" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E2" s="9" t="n">
+      <x:c r="E2" s="29" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="F2" s="9" t="n">
+      <x:c r="F2" s="29" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G2" s="29" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="n">
+      <x:c r="H2" s="30" t="n">
         <x:v>64</x:v>
       </x:c>
     </x:row>
@@ -55672,19 +55751,22 @@
       <x:c r="B3" s="9" t="str">
         <x:v>第二章 个人贷款管理</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="n">
+      <x:c r="C3" s="9" t="str">
         <x:v>62421</x:v>
       </x:c>
-      <x:c r="D3" s="9" t="n">
+      <x:c r="D3" s="29" t="n">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="E3" s="9" t="n">
+      <x:c r="E3" s="29" t="n">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="F3" s="9" t="n">
+      <x:c r="F3" s="29" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="G3" s="29" t="n">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G3" s="10" t="n">
+      <x:c r="H3" s="30" t="n">
         <x:v>79</x:v>
       </x:c>
     </x:row>
@@ -55695,19 +55777,22 @@
       <x:c r="B4" s="9" t="str">
         <x:v>第三章 个人住房贷款</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="n">
+      <x:c r="C4" s="9" t="str">
         <x:v>62428</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="n">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="n">
+      <x:c r="D4" s="29" t="n">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="F4" s="9" t="n">
+      <x:c r="E4" s="29" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F4" s="29" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="G4" s="29" t="n">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="n">
+      <x:c r="H4" s="30" t="n">
         <x:v>85</x:v>
       </x:c>
     </x:row>
@@ -55718,19 +55803,22 @@
       <x:c r="B5" s="9" t="str">
         <x:v>第四章 个人消费类贷款</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="n">
+      <x:c r="C5" s="9" t="str">
         <x:v>62433</x:v>
       </x:c>
-      <x:c r="D5" s="9" t="n">
+      <x:c r="D5" s="29" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="E5" s="9" t="n">
+      <x:c r="E5" s="29" t="n">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="F5" s="9" t="n">
+      <x:c r="F5" s="29" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="G5" s="29" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G5" s="10" t="n">
+      <x:c r="H5" s="30" t="n">
         <x:v>79</x:v>
       </x:c>
     </x:row>
@@ -55741,19 +55829,22 @@
       <x:c r="B6" s="9" t="str">
         <x:v>第五章 个人经营类贷款</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="n">
+      <x:c r="C6" s="9" t="str">
         <x:v>62434</x:v>
       </x:c>
-      <x:c r="D6" s="9" t="n">
+      <x:c r="D6" s="29" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="E6" s="9" t="n">
+      <x:c r="E6" s="29" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="F6" s="9" t="n">
+      <x:c r="F6" s="29" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G6" s="29" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G6" s="10" t="n">
+      <x:c r="H6" s="30" t="n">
         <x:v>54</x:v>
       </x:c>
     </x:row>
@@ -55764,19 +55855,22 @@
       <x:c r="B7" s="9" t="str">
         <x:v>第六章 信用卡业务</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="n">
+      <x:c r="C7" s="9" t="str">
         <x:v>62435</x:v>
       </x:c>
-      <x:c r="D7" s="9" t="n">
+      <x:c r="D7" s="29" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E7" s="9" t="n">
+      <x:c r="E7" s="29" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F7" s="9" t="n">
+      <x:c r="F7" s="29" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G7" s="29" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="n">
+      <x:c r="H7" s="30" t="n">
         <x:v>37</x:v>
       </x:c>
     </x:row>
@@ -55787,19 +55881,22 @@
       <x:c r="B8" s="9" t="str">
         <x:v>第七章 个人贷款新趋势（初级不考此章节）</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="n">
+      <x:c r="C8" s="9" t="str">
         <x:v>62436</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="n">
+      <x:c r="D8" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="n">
+      <x:c r="E8" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="n">
+      <x:c r="F8" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G8" s="10" t="n">
+      <x:c r="G8" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="30" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -55810,19 +55907,22 @@
       <x:c r="B9" s="9" t="str">
         <x:v>第八章 个人征信系统</x:v>
       </x:c>
-      <x:c r="C9" s="9" t="n">
+      <x:c r="C9" s="9" t="str">
         <x:v>62437</x:v>
       </x:c>
-      <x:c r="D9" s="9" t="n">
+      <x:c r="D9" s="29" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E9" s="9" t="n">
+      <x:c r="E9" s="29" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="n">
+      <x:c r="F9" s="29" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="G9" s="10" t="n">
+      <x:c r="H9" s="30" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -55833,38 +55933,44 @@
       <x:c r="B10" s="9" t="str">
         <x:v>附录</x:v>
       </x:c>
-      <x:c r="C10" s="9" t="n">
+      <x:c r="C10" s="9" t="str">
         <x:v>62613</x:v>
       </x:c>
-      <x:c r="D10" s="9" t="n">
+      <x:c r="D10" s="29" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E10" s="9" t="n">
+      <x:c r="E10" s="29" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="F10" s="9" t="n">
+      <x:c r="F10" s="29" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G10" s="10" t="n">
+      <x:c r="H10" s="30" t="n">
         <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str"/>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="A11" s="37" t="str"/>
+      <x:c r="B11" s="38" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str"/>
-      <x:c r="D11" s="12" t="n">
-        <x:v>908</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="n">
+      <x:c r="C11" s="38" t="str"/>
+      <x:c r="D11" s="39" t="n">
         <x:v>907</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="n">
+      <x:c r="E11" s="39" t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="F11" s="39" t="n">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="G11" s="39" t="n">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="n">
+      <x:c r="H11" s="39" t="n">
         <x:v>448</x:v>
       </x:c>
     </x:row>
@@ -55889,52 +55995,60 @@
         <x:v>内容</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="8" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="40" t="str">
         <x:v>科目</x:v>
       </x:c>
       <x:c r="B2" s="10" t="str">
         <x:v>银行从业初级个人贷款</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="40" t="str">
         <x:v>范围</x:v>
       </x:c>
       <x:c r="B3" s="10" t="str">
         <x:v>章节练习全量</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="40" t="str">
         <x:v>题目数量</x:v>
       </x:c>
       <x:c r="B4" s="10" t="n">
         <x:v>907</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="8" t="str">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="40" t="str">
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-08T22:32:58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="8" t="str">
+        <x:v>2026-09-10 00:15:37+08:00（本地时间）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="40" t="str">
         <x:v>来源链接</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
         <x:v>https://wx.233.com/center/study/tiku/chapter?domain=ccbp&amp;subjectId=751&amp;chapterType=1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="40" t="str">
+        <x:v>题量告警</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>无</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
+      <x:c r="A8" s="33" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="B7" s="13" t="str">
-        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目；第三章目录标注174题，练习接口实际返回173题，本表按接口实际返回收录。</x:v>
+      <x:c r="B8" s="13" t="str">
+        <x:v>权限不足/收费题已保留行并标注；案例材料题已展开为独立题目，材料文本放在题目前。 复用可信 Excel 中 1 道解析图片的既有文字；仅在来源题目 ID、题干、选项和答案均一致时复用。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/resources/topic/银行从业初级个人贷款_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级个人贷款_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R1388fef3d0b94d16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Re38ad42ad626401d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rd450ad67dab34db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R8b41546f12f74817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R1ea5ca26787d47f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R5c8a48b59e18401d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56024,7 +56024,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 00:15:37+08:00（本地时间）</x:v>
+        <x:v>2026-09-10 15:08:00+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">

--- a/resources/topic/银行从业初级个人贷款_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级个人贷款_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R8b41546f12f74817"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R1ea5ca26787d47f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R5c8a48b59e18401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R1e4c5ff746d94284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R5fb4582f08694f29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R60a581b5e0b9436f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56024,7 +56024,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 15:08:00+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 01:02:31+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
